--- a/Practice_file.xlsx
+++ b/Practice_file.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d58d4d655bee1e81/Desktop/Github/Practice_Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="81" documentId="11_F25DC773A252ABDACC1048BD89DC52D45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8924EA92-5618-4380-97B9-571D3E6224B9}"/>
+  <xr:revisionPtr revIDLastSave="116" documentId="11_F25DC773A252ABDACC1048BD89DC52D45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6AA74B8E-F6A0-4510-98E1-CC4DB79B52AF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SUMIF,AVGIF" sheetId="1" r:id="rId1"/>
     <sheet name="COUNTIF,IFs" sheetId="2" r:id="rId2"/>
-    <sheet name="V,H,XLOOKUP" sheetId="3" r:id="rId3"/>
+    <sheet name="V,HLOOKUP" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="90">
   <si>
     <t>Data for Practice</t>
   </si>
@@ -266,13 +266,58 @@
   </si>
   <si>
     <t>COUNTIFS followed by condition range1 followed by condition1 the condition range2 followed by condition2</t>
+  </si>
+  <si>
+    <t>Data For Practice (VLOOKUP)</t>
+  </si>
+  <si>
+    <t>Price</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Stock</t>
+  </si>
+  <si>
+    <t>Tablet</t>
+  </si>
+  <si>
+    <t>Smartphone</t>
+  </si>
+  <si>
+    <t>Monitor</t>
+  </si>
+  <si>
+    <t>Accessories</t>
+  </si>
+  <si>
+    <t>Smartphone Price</t>
+  </si>
+  <si>
+    <t>Tablet stock</t>
+  </si>
+  <si>
+    <t>Laptop Price</t>
+  </si>
+  <si>
+    <t>Laptop Category</t>
+  </si>
+  <si>
+    <t>Stock of Keyborad</t>
+  </si>
+  <si>
+    <t>HLOOKUP followed by the condition followed by the selection of table followed by return value row and 0 or 1</t>
+  </si>
+  <si>
+    <t>VLOOKUP followed by the condition followed by the selection of table followed by return value column and 0 or 1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -329,6 +374,28 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -380,7 +447,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="23">
+  <borders count="24">
     <border>
       <left/>
       <right/>
@@ -632,11 +699,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -687,19 +763,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -722,27 +786,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -755,8 +804,29 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -764,25 +834,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -803,11 +882,42 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1104,14 +1214,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="11" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="53"/>
+      <c r="F1" s="53"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
@@ -1273,17 +1383,17 @@
       <c r="F12" s="18"/>
     </row>
     <row r="15" spans="1:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
+      <c r="B15" s="53"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="53"/>
+      <c r="H15" s="53"/>
+      <c r="I15" s="53"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
@@ -1548,927 +1658,927 @@
   <dimension ref="A1:J51"/>
   <sheetFormatPr defaultColWidth="14" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="4" width="14" style="23"/>
-    <col min="5" max="7" width="12.21875" style="23" customWidth="1"/>
-    <col min="8" max="8" width="17.44140625" style="23" customWidth="1"/>
-    <col min="9" max="10" width="29.44140625" style="23" customWidth="1"/>
-    <col min="11" max="16384" width="14" style="23"/>
+    <col min="1" max="4" width="14" style="22"/>
+    <col min="5" max="7" width="12.21875" style="22" customWidth="1"/>
+    <col min="8" max="8" width="17.44140625" style="22" customWidth="1"/>
+    <col min="9" max="10" width="29.44140625" style="22" customWidth="1"/>
+    <col min="11" max="16384" width="14" style="22"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="65" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="27"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="67"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="28" t="s">
+      <c r="D2" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="E2" s="29"/>
-      <c r="F2" s="30" t="s">
+      <c r="E2" s="25"/>
+      <c r="F2" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="31" t="s">
+      <c r="G2" s="27" t="s">
         <v>43</v>
       </c>
-      <c r="H2" s="32"/>
+      <c r="H2" s="28"/>
     </row>
     <row r="3" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="33">
+      <c r="B3" s="29">
         <v>30</v>
       </c>
-      <c r="C3" s="33">
+      <c r="C3" s="29">
         <v>500</v>
       </c>
-      <c r="D3" s="33" t="s">
+      <c r="D3" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="29"/>
-      <c r="F3" s="34" t="s">
+      <c r="E3" s="25"/>
+      <c r="F3" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="35">
+      <c r="G3" s="31">
         <f>COUNT(B3:B12)</f>
         <v>8</v>
       </c>
-      <c r="H3" s="36" t="s">
+      <c r="H3" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="I3" s="23" t="s">
+      <c r="I3" s="22" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="33" t="s">
+      <c r="A4" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="33">
+      <c r="B4" s="29">
         <v>28</v>
       </c>
-      <c r="C4" s="33">
+      <c r="C4" s="29">
         <v>650</v>
       </c>
-      <c r="D4" s="33" t="s">
+      <c r="D4" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="E4" s="29"/>
-      <c r="F4" s="34" t="s">
+      <c r="E4" s="25"/>
+      <c r="F4" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="G4" s="35">
+      <c r="G4" s="31">
         <f>COUNTA(B3:B12)</f>
         <v>9</v>
       </c>
-      <c r="H4" s="36" t="s">
+      <c r="H4" s="32" t="s">
         <v>57</v>
       </c>
-      <c r="I4" s="23" t="s">
+      <c r="I4" s="22" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="33">
+      <c r="C5" s="29">
         <v>500</v>
       </c>
-      <c r="D5" s="33" t="s">
+      <c r="D5" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E5" s="29"/>
-      <c r="F5" s="34" t="s">
+      <c r="E5" s="25"/>
+      <c r="F5" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="35">
+      <c r="G5" s="31">
         <f>COUNTBLANK(B3:B12)</f>
         <v>1</v>
       </c>
-      <c r="H5" s="36" t="s">
+      <c r="H5" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="I5" s="23" t="s">
+      <c r="I5" s="22" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="33" t="s">
+      <c r="A6" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="33">
+      <c r="B6" s="29">
         <v>35</v>
       </c>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33" t="s">
+      <c r="C6" s="29"/>
+      <c r="D6" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="35" t="str">
+      <c r="E6" s="25"/>
+      <c r="F6" s="25"/>
+      <c r="G6" s="31" t="str">
         <f>IF(COUNTBLANK(C3:C12)&gt;0,"Data Missing","No Data Missing")</f>
         <v>Data Missing</v>
       </c>
-      <c r="H6" s="37" t="s">
+      <c r="H6" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="I6" s="23" t="s">
+      <c r="I6" s="22" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="33" t="s">
+      <c r="A7" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="33">
+      <c r="B7" s="29">
         <v>32</v>
       </c>
-      <c r="C7" s="33">
+      <c r="C7" s="29">
         <v>650</v>
       </c>
-      <c r="D7" s="33" t="s">
+      <c r="D7" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="38"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="23" t="s">
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="22" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="33" t="s">
+      <c r="A8" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="33">
+      <c r="B8" s="29">
         <v>29</v>
       </c>
-      <c r="C8" s="33">
+      <c r="C8" s="29">
         <v>700</v>
       </c>
-      <c r="D8" s="33" t="s">
+      <c r="D8" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="38"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="34"/>
     </row>
     <row r="9" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="33" t="s">
+      <c r="A9" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="33"/>
-      <c r="C9" s="33">
+      <c r="B9" s="29"/>
+      <c r="C9" s="29">
         <v>550</v>
       </c>
-      <c r="D9" s="33" t="s">
+      <c r="D9" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="38"/>
-      <c r="H9" s="39"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="35"/>
     </row>
     <row r="10" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="33" t="s">
+      <c r="A10" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="B10" s="33">
+      <c r="B10" s="29">
         <v>31</v>
       </c>
-      <c r="C10" s="33">
+      <c r="C10" s="29">
         <v>650</v>
       </c>
-      <c r="D10" s="33" t="s">
+      <c r="D10" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="38"/>
-      <c r="H10" s="39"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="34"/>
+      <c r="H10" s="35"/>
     </row>
     <row r="11" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="33" t="s">
+      <c r="A11" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="33">
+      <c r="B11" s="29">
         <v>40</v>
       </c>
-      <c r="C11" s="33">
+      <c r="C11" s="29">
         <v>800</v>
       </c>
-      <c r="D11" s="33" t="s">
+      <c r="D11" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="E11" s="29"/>
-      <c r="F11" s="29"/>
-      <c r="G11" s="38"/>
-      <c r="H11" s="39"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="34"/>
+      <c r="H11" s="35"/>
     </row>
     <row r="12" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="33" t="s">
+      <c r="A12" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="33">
+      <c r="B12" s="29">
         <v>34</v>
       </c>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33" t="s">
+      <c r="C12" s="29"/>
+      <c r="D12" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="E12" s="40"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="39"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="37"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="35"/>
     </row>
     <row r="15" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="16" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="24" t="s">
+      <c r="A16" s="65" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="25"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="51"/>
-      <c r="G16" s="51"/>
+      <c r="B16" s="66"/>
+      <c r="C16" s="66"/>
+      <c r="D16" s="66"/>
+      <c r="E16" s="66"/>
+      <c r="F16" s="77"/>
+      <c r="G16" s="77"/>
     </row>
     <row r="17" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="28" t="s">
+      <c r="A17" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B17" s="28" t="s">
+      <c r="B17" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="28" t="s">
+      <c r="C17" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="D17" s="28" t="s">
+      <c r="D17" s="24" t="s">
         <v>42</v>
       </c>
-      <c r="E17" s="49" t="s">
+      <c r="E17" s="41" t="s">
         <v>53</v>
       </c>
-      <c r="F17" s="52" t="s">
+      <c r="F17" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="G17" s="53" t="s">
+      <c r="G17" s="44" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="33" t="s">
+      <c r="A18" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="B18" s="33">
+      <c r="B18" s="29">
         <v>30</v>
       </c>
-      <c r="C18" s="33">
+      <c r="C18" s="29">
         <v>500</v>
       </c>
-      <c r="D18" s="33" t="s">
+      <c r="D18" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E18" s="50" t="s">
+      <c r="E18" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="F18" s="54" t="s">
+      <c r="F18" s="45" t="s">
         <v>6</v>
       </c>
-      <c r="G18" s="55">
+      <c r="G18" s="46">
         <f>COUNTIF(B18:B27,"&gt;30")</f>
         <v>6</v>
       </c>
-      <c r="H18" s="61" t="s">
+      <c r="H18" s="59" t="s">
         <v>70</v>
       </c>
-      <c r="I18" s="62"/>
+      <c r="I18" s="60"/>
     </row>
     <row r="19" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="33" t="s">
+      <c r="A19" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="33">
+      <c r="B19" s="29">
         <v>28</v>
       </c>
-      <c r="C19" s="33">
+      <c r="C19" s="29">
         <v>650</v>
       </c>
-      <c r="D19" s="33" t="s">
+      <c r="D19" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="E19" s="50" t="s">
+      <c r="E19" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="F19" s="54" t="s">
+      <c r="F19" s="45" t="s">
         <v>8</v>
       </c>
-      <c r="G19" s="55">
+      <c r="G19" s="46">
         <f>COUNTIF(E18:E27,"Male")</f>
         <v>5</v>
       </c>
-      <c r="H19" s="61" t="s">
+      <c r="H19" s="59" t="s">
         <v>71</v>
       </c>
-      <c r="I19" s="62"/>
+      <c r="I19" s="60"/>
     </row>
     <row r="20" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="33" t="s">
+      <c r="A20" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="33">
+      <c r="B20" s="29">
         <v>35</v>
       </c>
-      <c r="C20" s="33">
+      <c r="C20" s="29">
         <v>500</v>
       </c>
-      <c r="D20" s="33" t="s">
+      <c r="D20" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E20" s="50" t="s">
+      <c r="E20" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="F20" s="56"/>
-      <c r="G20" s="57"/>
+      <c r="F20" s="47"/>
+      <c r="G20" s="48"/>
     </row>
     <row r="21" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="33" t="s">
+      <c r="A21" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="B21" s="33">
+      <c r="B21" s="29">
         <v>40</v>
       </c>
-      <c r="C21" s="33">
+      <c r="C21" s="29">
         <v>750</v>
       </c>
-      <c r="D21" s="33" t="s">
+      <c r="D21" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="E21" s="50" t="s">
+      <c r="E21" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="F21" s="56"/>
-      <c r="G21" s="57"/>
+      <c r="F21" s="47"/>
+      <c r="G21" s="48"/>
     </row>
     <row r="22" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="33" t="s">
+      <c r="A22" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="B22" s="33">
+      <c r="B22" s="29">
         <v>32</v>
       </c>
-      <c r="C22" s="33">
+      <c r="C22" s="29">
         <v>650</v>
       </c>
-      <c r="D22" s="33" t="s">
+      <c r="D22" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="E22" s="50" t="s">
+      <c r="E22" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="F22" s="56"/>
-      <c r="G22" s="57"/>
+      <c r="F22" s="47"/>
+      <c r="G22" s="48"/>
     </row>
     <row r="23" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="33" t="s">
+      <c r="A23" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="B23" s="33">
+      <c r="B23" s="29">
         <v>29</v>
       </c>
-      <c r="C23" s="33">
+      <c r="C23" s="29">
         <v>700</v>
       </c>
-      <c r="D23" s="33" t="s">
+      <c r="D23" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="E23" s="50" t="s">
+      <c r="E23" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="F23" s="56"/>
-      <c r="G23" s="57"/>
+      <c r="F23" s="47"/>
+      <c r="G23" s="48"/>
     </row>
     <row r="24" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="33" t="s">
+      <c r="A24" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="B24" s="33">
+      <c r="B24" s="29">
         <v>31</v>
       </c>
-      <c r="C24" s="33">
+      <c r="C24" s="29">
         <v>550</v>
       </c>
-      <c r="D24" s="33" t="s">
+      <c r="D24" s="29" t="s">
         <v>45</v>
       </c>
-      <c r="E24" s="50" t="s">
+      <c r="E24" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="F24" s="56"/>
-      <c r="G24" s="57"/>
+      <c r="F24" s="47"/>
+      <c r="G24" s="48"/>
     </row>
     <row r="25" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="33" t="s">
+      <c r="A25" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="B25" s="33">
+      <c r="B25" s="29">
         <v>27</v>
       </c>
-      <c r="C25" s="33">
+      <c r="C25" s="29">
         <v>650</v>
       </c>
-      <c r="D25" s="33" t="s">
+      <c r="D25" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="E25" s="50" t="s">
+      <c r="E25" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="F25" s="56"/>
-      <c r="G25" s="57"/>
+      <c r="F25" s="47"/>
+      <c r="G25" s="48"/>
     </row>
     <row r="26" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="33" t="s">
+      <c r="A26" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="B26" s="33">
+      <c r="B26" s="29">
         <v>45</v>
       </c>
-      <c r="C26" s="33">
+      <c r="C26" s="29">
         <v>800</v>
       </c>
-      <c r="D26" s="33" t="s">
+      <c r="D26" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="E26" s="50" t="s">
+      <c r="E26" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="F26" s="56"/>
-      <c r="G26" s="57"/>
+      <c r="F26" s="47"/>
+      <c r="G26" s="48"/>
     </row>
     <row r="27" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="33" t="s">
+      <c r="A27" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="33">
+      <c r="B27" s="29">
         <v>34</v>
       </c>
-      <c r="C27" s="33">
+      <c r="C27" s="29">
         <v>700</v>
       </c>
-      <c r="D27" s="33" t="s">
+      <c r="D27" s="29" t="s">
         <v>44</v>
       </c>
-      <c r="E27" s="50" t="s">
+      <c r="E27" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="F27" s="58"/>
-      <c r="G27" s="59"/>
+      <c r="F27" s="49"/>
+      <c r="G27" s="50"/>
     </row>
     <row r="30" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="31" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="43" t="s">
+      <c r="A31" s="68" t="s">
         <v>60</v>
       </c>
-      <c r="B31" s="44"/>
-      <c r="C31" s="44"/>
-      <c r="D31" s="44"/>
-      <c r="E31" s="44"/>
-      <c r="F31" s="44"/>
-      <c r="G31" s="44"/>
-      <c r="H31" s="45"/>
+      <c r="B31" s="69"/>
+      <c r="C31" s="69"/>
+      <c r="D31" s="69"/>
+      <c r="E31" s="69"/>
+      <c r="F31" s="69"/>
+      <c r="G31" s="69"/>
+      <c r="H31" s="70"/>
     </row>
     <row r="32" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="46" t="s">
+      <c r="A32" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="B32" s="46" t="s">
+      <c r="B32" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="C32" s="46" t="s">
+      <c r="C32" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="D32" s="46" t="s">
+      <c r="D32" s="39" t="s">
         <v>62</v>
       </c>
-      <c r="E32" s="47"/>
-      <c r="F32" s="67"/>
-      <c r="G32" s="68"/>
-      <c r="H32" s="69"/>
+      <c r="E32" s="40"/>
+      <c r="F32" s="61"/>
+      <c r="G32" s="62"/>
+      <c r="H32" s="63"/>
     </row>
     <row r="33" spans="1:10" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="33" t="s">
+      <c r="A33" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="B33" s="33" t="s">
+      <c r="B33" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="C33" s="33">
+      <c r="C33" s="29">
         <v>3</v>
       </c>
-      <c r="D33" s="50" t="s">
+      <c r="D33" s="42" t="s">
         <v>64</v>
       </c>
-      <c r="E33" s="76">
+      <c r="E33" s="51">
         <f>COUNTIF(D33:D51,"Pending")</f>
         <v>7</v>
       </c>
-      <c r="F33" s="70" t="s">
+      <c r="F33" s="71" t="s">
         <v>69</v>
       </c>
-      <c r="G33" s="71"/>
-      <c r="H33" s="72"/>
-      <c r="I33" s="66" t="s">
+      <c r="G33" s="72"/>
+      <c r="H33" s="73"/>
+      <c r="I33" s="64" t="s">
         <v>72</v>
       </c>
-      <c r="J33" s="62"/>
+      <c r="J33" s="60"/>
     </row>
     <row r="34" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="33" t="s">
+      <c r="A34" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="B34" s="33" t="s">
+      <c r="B34" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="C34" s="33">
+      <c r="C34" s="29">
         <v>5</v>
       </c>
-      <c r="D34" s="50" t="s">
+      <c r="D34" s="42" t="s">
         <v>66</v>
       </c>
-      <c r="E34" s="77">
+      <c r="E34" s="52">
         <f>COUNTIFS(B33:B51,"West",D33:D51,"Delivered")</f>
         <v>3</v>
       </c>
-      <c r="F34" s="73" t="s">
+      <c r="F34" s="74" t="s">
         <v>73</v>
       </c>
-      <c r="G34" s="74"/>
-      <c r="H34" s="75"/>
-      <c r="I34" s="64" t="s">
+      <c r="G34" s="75"/>
+      <c r="H34" s="76"/>
+      <c r="I34" s="56" t="s">
         <v>74</v>
       </c>
-      <c r="J34" s="64"/>
+      <c r="J34" s="56"/>
     </row>
     <row r="35" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="33" t="s">
+      <c r="A35" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="B35" s="33" t="s">
+      <c r="B35" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="C35" s="33">
+      <c r="C35" s="29">
         <v>2</v>
       </c>
-      <c r="D35" s="33" t="s">
+      <c r="D35" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="E35" s="29"/>
-      <c r="F35" s="48"/>
-      <c r="G35" s="48"/>
-      <c r="H35" s="48"/>
-      <c r="I35" s="63"/>
-      <c r="J35" s="64"/>
+      <c r="E35" s="25"/>
+      <c r="F35" s="58"/>
+      <c r="G35" s="58"/>
+      <c r="H35" s="58"/>
+      <c r="I35" s="57"/>
+      <c r="J35" s="56"/>
     </row>
     <row r="36" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="33" t="s">
+      <c r="A36" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="B36" s="33" t="s">
+      <c r="B36" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="C36" s="33">
+      <c r="C36" s="29">
         <v>4</v>
       </c>
-      <c r="D36" s="33" t="s">
+      <c r="D36" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="E36" s="29"/>
-      <c r="F36" s="48"/>
-      <c r="G36" s="48"/>
-      <c r="H36" s="48"/>
-      <c r="I36" s="65"/>
-      <c r="J36" s="60"/>
+      <c r="E36" s="25"/>
+      <c r="F36" s="58"/>
+      <c r="G36" s="58"/>
+      <c r="H36" s="58"/>
+      <c r="I36" s="54"/>
+      <c r="J36" s="55"/>
     </row>
     <row r="37" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="33" t="s">
+      <c r="A37" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="B37" s="33" t="s">
+      <c r="B37" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="C37" s="33">
+      <c r="C37" s="29">
         <v>6</v>
       </c>
-      <c r="D37" s="33" t="s">
+      <c r="D37" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="E37" s="29"/>
-      <c r="F37" s="48"/>
-      <c r="G37" s="48"/>
-      <c r="H37" s="48"/>
-      <c r="I37" s="65"/>
-      <c r="J37" s="60"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="58"/>
+      <c r="G37" s="58"/>
+      <c r="H37" s="58"/>
+      <c r="I37" s="54"/>
+      <c r="J37" s="55"/>
     </row>
     <row r="38" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="33" t="s">
+      <c r="A38" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="B38" s="33" t="s">
+      <c r="B38" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="C38" s="33">
+      <c r="C38" s="29">
         <v>3</v>
       </c>
-      <c r="D38" s="33" t="s">
+      <c r="D38" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="E38" s="29"/>
-      <c r="F38" s="48"/>
-      <c r="G38" s="48"/>
-      <c r="H38" s="48"/>
-      <c r="I38" s="65"/>
-      <c r="J38" s="60"/>
+      <c r="E38" s="25"/>
+      <c r="F38" s="58"/>
+      <c r="G38" s="58"/>
+      <c r="H38" s="58"/>
+      <c r="I38" s="54"/>
+      <c r="J38" s="55"/>
     </row>
     <row r="39" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A39" s="33" t="s">
+      <c r="A39" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="B39" s="33" t="s">
+      <c r="B39" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="C39" s="33">
+      <c r="C39" s="29">
         <v>1</v>
       </c>
-      <c r="D39" s="33" t="s">
+      <c r="D39" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="E39" s="29"/>
-      <c r="F39" s="48"/>
-      <c r="G39" s="48"/>
-      <c r="H39" s="48"/>
-      <c r="I39" s="65"/>
-      <c r="J39" s="60"/>
+      <c r="E39" s="25"/>
+      <c r="F39" s="58"/>
+      <c r="G39" s="58"/>
+      <c r="H39" s="58"/>
+      <c r="I39" s="54"/>
+      <c r="J39" s="55"/>
     </row>
     <row r="40" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A40" s="33" t="s">
+      <c r="A40" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="B40" s="33" t="s">
+      <c r="B40" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="C40" s="33">
+      <c r="C40" s="29">
         <v>5</v>
       </c>
-      <c r="D40" s="33" t="s">
+      <c r="D40" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="E40" s="29"/>
-      <c r="F40" s="48"/>
-      <c r="G40" s="48"/>
-      <c r="H40" s="48"/>
-      <c r="I40" s="65"/>
-      <c r="J40" s="60"/>
+      <c r="E40" s="25"/>
+      <c r="F40" s="58"/>
+      <c r="G40" s="58"/>
+      <c r="H40" s="58"/>
+      <c r="I40" s="54"/>
+      <c r="J40" s="55"/>
     </row>
     <row r="41" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A41" s="33" t="s">
+      <c r="A41" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="B41" s="33" t="s">
+      <c r="B41" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="C41" s="33">
+      <c r="C41" s="29">
         <v>2</v>
       </c>
-      <c r="D41" s="33" t="s">
+      <c r="D41" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="E41" s="29"/>
-      <c r="F41" s="48"/>
-      <c r="G41" s="48"/>
-      <c r="H41" s="48"/>
-      <c r="I41" s="65"/>
-      <c r="J41" s="60"/>
+      <c r="E41" s="25"/>
+      <c r="F41" s="58"/>
+      <c r="G41" s="58"/>
+      <c r="H41" s="58"/>
+      <c r="I41" s="54"/>
+      <c r="J41" s="55"/>
     </row>
     <row r="42" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="33" t="s">
+      <c r="A42" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="B42" s="33" t="s">
+      <c r="B42" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="33">
+      <c r="C42" s="29">
         <v>4</v>
       </c>
-      <c r="D42" s="33" t="s">
+      <c r="D42" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="E42" s="29"/>
-      <c r="F42" s="48"/>
-      <c r="G42" s="48"/>
-      <c r="H42" s="48"/>
-      <c r="I42" s="65"/>
-      <c r="J42" s="60"/>
+      <c r="E42" s="25"/>
+      <c r="F42" s="58"/>
+      <c r="G42" s="58"/>
+      <c r="H42" s="58"/>
+      <c r="I42" s="54"/>
+      <c r="J42" s="55"/>
     </row>
     <row r="43" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="33" t="s">
+      <c r="A43" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="B43" s="33" t="s">
+      <c r="B43" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="C43" s="33">
+      <c r="C43" s="29">
         <v>3</v>
       </c>
-      <c r="D43" s="33" t="s">
+      <c r="D43" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="E43" s="29"/>
-      <c r="F43" s="48"/>
-      <c r="G43" s="48"/>
-      <c r="H43" s="48"/>
-      <c r="I43" s="65"/>
-      <c r="J43" s="60"/>
+      <c r="E43" s="25"/>
+      <c r="F43" s="58"/>
+      <c r="G43" s="58"/>
+      <c r="H43" s="58"/>
+      <c r="I43" s="54"/>
+      <c r="J43" s="55"/>
     </row>
     <row r="44" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="33" t="s">
+      <c r="A44" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="B44" s="33" t="s">
+      <c r="B44" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="C44" s="33">
+      <c r="C44" s="29">
         <v>2</v>
       </c>
-      <c r="D44" s="33" t="s">
+      <c r="D44" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="E44" s="29"/>
-      <c r="F44" s="48"/>
-      <c r="G44" s="48"/>
-      <c r="H44" s="48"/>
-      <c r="I44" s="65"/>
-      <c r="J44" s="60"/>
+      <c r="E44" s="25"/>
+      <c r="F44" s="58"/>
+      <c r="G44" s="58"/>
+      <c r="H44" s="58"/>
+      <c r="I44" s="54"/>
+      <c r="J44" s="55"/>
     </row>
     <row r="45" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="33" t="s">
+      <c r="A45" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="B45" s="33" t="s">
+      <c r="B45" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="C45" s="33">
+      <c r="C45" s="29">
         <v>1</v>
       </c>
-      <c r="D45" s="33" t="s">
+      <c r="D45" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="E45" s="29"/>
-      <c r="F45" s="48"/>
-      <c r="G45" s="48"/>
-      <c r="H45" s="48"/>
+      <c r="E45" s="25"/>
+      <c r="F45" s="58"/>
+      <c r="G45" s="58"/>
+      <c r="H45" s="58"/>
     </row>
     <row r="46" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="33" t="s">
+      <c r="A46" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="B46" s="33" t="s">
+      <c r="B46" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="C46" s="33">
+      <c r="C46" s="29">
         <v>6</v>
       </c>
-      <c r="D46" s="33" t="s">
+      <c r="D46" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="E46" s="29"/>
-      <c r="F46" s="48"/>
-      <c r="G46" s="48"/>
-      <c r="H46" s="48"/>
+      <c r="E46" s="25"/>
+      <c r="F46" s="58"/>
+      <c r="G46" s="58"/>
+      <c r="H46" s="58"/>
     </row>
     <row r="47" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="33" t="s">
+      <c r="A47" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="B47" s="33" t="s">
+      <c r="B47" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="C47" s="33">
+      <c r="C47" s="29">
         <v>4</v>
       </c>
-      <c r="D47" s="33" t="s">
+      <c r="D47" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="E47" s="29"/>
-      <c r="F47" s="48"/>
-      <c r="G47" s="48"/>
-      <c r="H47" s="48"/>
+      <c r="E47" s="25"/>
+      <c r="F47" s="58"/>
+      <c r="G47" s="58"/>
+      <c r="H47" s="58"/>
     </row>
     <row r="48" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="33" t="s">
+      <c r="A48" s="29" t="s">
         <v>68</v>
       </c>
-      <c r="B48" s="33" t="s">
+      <c r="B48" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="C48" s="33">
+      <c r="C48" s="29">
         <v>3</v>
       </c>
-      <c r="D48" s="33" t="s">
+      <c r="D48" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="E48" s="29"/>
-      <c r="F48" s="48"/>
-      <c r="G48" s="48"/>
-      <c r="H48" s="48"/>
+      <c r="E48" s="25"/>
+      <c r="F48" s="58"/>
+      <c r="G48" s="58"/>
+      <c r="H48" s="58"/>
     </row>
     <row r="49" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="33" t="s">
+      <c r="A49" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="B49" s="33" t="s">
+      <c r="B49" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="C49" s="33">
+      <c r="C49" s="29">
         <v>5</v>
       </c>
-      <c r="D49" s="33" t="s">
+      <c r="D49" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="E49" s="29"/>
-      <c r="F49" s="48"/>
-      <c r="G49" s="48"/>
-      <c r="H49" s="48"/>
+      <c r="E49" s="25"/>
+      <c r="F49" s="58"/>
+      <c r="G49" s="58"/>
+      <c r="H49" s="58"/>
     </row>
     <row r="50" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="33" t="s">
+      <c r="A50" s="29" t="s">
         <v>65</v>
       </c>
-      <c r="B50" s="33" t="s">
+      <c r="B50" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="C50" s="33">
+      <c r="C50" s="29">
         <v>2</v>
       </c>
-      <c r="D50" s="33" t="s">
+      <c r="D50" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="E50" s="29"/>
-      <c r="F50" s="48"/>
-      <c r="G50" s="48"/>
-      <c r="H50" s="48"/>
+      <c r="E50" s="25"/>
+      <c r="F50" s="58"/>
+      <c r="G50" s="58"/>
+      <c r="H50" s="58"/>
     </row>
     <row r="51" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A51" s="33" t="s">
+      <c r="A51" s="29" t="s">
         <v>67</v>
       </c>
-      <c r="B51" s="33" t="s">
+      <c r="B51" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="C51" s="33">
+      <c r="C51" s="29">
         <v>2</v>
       </c>
-      <c r="D51" s="33" t="s">
+      <c r="D51" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="E51" s="29"/>
-      <c r="F51" s="48"/>
-      <c r="G51" s="48"/>
-      <c r="H51" s="48"/>
+      <c r="E51" s="25"/>
+      <c r="F51" s="58"/>
+      <c r="G51" s="58"/>
+      <c r="H51" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="I34:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="A16:G16"/>
     <mergeCell ref="F48:H48"/>
     <mergeCell ref="F49:H49"/>
     <mergeCell ref="F50:H50"/>
@@ -2485,16 +2595,16 @@
     <mergeCell ref="F47:H47"/>
     <mergeCell ref="F36:H36"/>
     <mergeCell ref="F37:H37"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="I34:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2503,9 +2613,314 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECB6F217-8C78-44CE-86A6-18C085457C6F}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <dimension ref="A1:T13"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.5546875" style="93" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10" style="93" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.77734375" style="93" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="11" style="93" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.88671875" style="93" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10" style="93" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.88671875" style="93"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="90" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" s="91"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="91"/>
+      <c r="F1" s="92"/>
+    </row>
+    <row r="2" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="83" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="83" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" s="83" t="s">
+        <v>77</v>
+      </c>
+      <c r="D2" s="83" t="s">
+        <v>78</v>
+      </c>
+      <c r="E2" s="84"/>
+      <c r="F2" s="85" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="86" t="s">
+        <v>63</v>
+      </c>
+      <c r="B3" s="86">
+        <v>1000</v>
+      </c>
+      <c r="C3" s="86" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="86">
+        <v>20</v>
+      </c>
+      <c r="E3" s="84"/>
+      <c r="F3" s="87"/>
+    </row>
+    <row r="4" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="86" t="s">
+        <v>79</v>
+      </c>
+      <c r="B4" s="86">
+        <v>600</v>
+      </c>
+      <c r="C4" s="86" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="86">
+        <v>15</v>
+      </c>
+      <c r="E4" s="84"/>
+      <c r="F4" s="87">
+        <f>VLOOKUP("Tablet",A2:D7,4,0)</f>
+        <v>15</v>
+      </c>
+      <c r="G4" s="93" t="s">
+        <v>84</v>
+      </c>
+      <c r="H4" s="94" t="s">
+        <v>89</v>
+      </c>
+      <c r="I4" s="94"/>
+      <c r="J4" s="94"/>
+      <c r="K4" s="94"/>
+      <c r="L4" s="94"/>
+      <c r="M4" s="94"/>
+      <c r="N4" s="94"/>
+      <c r="O4" s="94"/>
+      <c r="P4" s="94"/>
+      <c r="Q4" s="94"/>
+      <c r="R4" s="94"/>
+      <c r="S4" s="94"/>
+    </row>
+    <row r="5" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="86" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" s="86">
+        <v>800</v>
+      </c>
+      <c r="C5" s="86" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="86">
+        <v>30</v>
+      </c>
+      <c r="E5" s="84"/>
+      <c r="F5" s="87">
+        <f>VLOOKUP("Smartphone",A2:D7,2,0)</f>
+        <v>800</v>
+      </c>
+      <c r="G5" s="93" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="86" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" s="86">
+        <v>300</v>
+      </c>
+      <c r="C6" s="86" t="s">
+        <v>82</v>
+      </c>
+      <c r="D6" s="86">
+        <v>25</v>
+      </c>
+      <c r="E6" s="84"/>
+      <c r="F6" s="87"/>
+    </row>
+    <row r="7" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="86" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="86">
+        <v>50</v>
+      </c>
+      <c r="C7" s="86" t="s">
+        <v>82</v>
+      </c>
+      <c r="D7" s="86">
+        <v>50</v>
+      </c>
+      <c r="E7" s="88"/>
+      <c r="F7" s="89"/>
+    </row>
+    <row r="9" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="10" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="79" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="79" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="79" t="s">
+        <v>79</v>
+      </c>
+      <c r="D10" s="79" t="s">
+        <v>80</v>
+      </c>
+      <c r="E10" s="79" t="s">
+        <v>81</v>
+      </c>
+      <c r="F10" s="79" t="s">
+        <v>67</v>
+      </c>
+      <c r="G10" s="95"/>
+      <c r="H10" s="78" t="s">
+        <v>8</v>
+      </c>
+      <c r="I10" s="94" t="s">
+        <v>88</v>
+      </c>
+      <c r="J10" s="94"/>
+      <c r="K10" s="94"/>
+      <c r="L10" s="94"/>
+      <c r="M10" s="94"/>
+      <c r="N10" s="94"/>
+      <c r="O10" s="94"/>
+      <c r="P10" s="94"/>
+      <c r="Q10" s="94"/>
+      <c r="R10" s="94"/>
+      <c r="S10" s="94"/>
+      <c r="T10" s="94"/>
+    </row>
+    <row r="11" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="79" t="s">
+        <v>76</v>
+      </c>
+      <c r="B11" s="79">
+        <v>1000</v>
+      </c>
+      <c r="C11" s="79">
+        <v>600</v>
+      </c>
+      <c r="D11" s="79">
+        <v>800</v>
+      </c>
+      <c r="E11" s="79">
+        <v>300</v>
+      </c>
+      <c r="F11" s="79">
+        <v>50</v>
+      </c>
+      <c r="G11" s="96"/>
+      <c r="H11" s="80">
+        <f>HLOOKUP("Laptop",A10:F13,2,0)</f>
+        <v>1000</v>
+      </c>
+      <c r="I11" s="97" t="s">
+        <v>85</v>
+      </c>
+      <c r="J11" s="94"/>
+      <c r="K11" s="94"/>
+      <c r="L11" s="94"/>
+      <c r="M11" s="94"/>
+      <c r="N11" s="94"/>
+      <c r="O11" s="94"/>
+      <c r="P11" s="94"/>
+      <c r="Q11" s="94"/>
+      <c r="R11" s="94"/>
+      <c r="S11" s="94"/>
+    </row>
+    <row r="12" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="79" t="s">
+        <v>77</v>
+      </c>
+      <c r="B12" s="79" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="79" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="79" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" s="79" t="s">
+        <v>82</v>
+      </c>
+      <c r="F12" s="79" t="s">
+        <v>82</v>
+      </c>
+      <c r="G12" s="96"/>
+      <c r="H12" s="80" t="str">
+        <f>HLOOKUP("Tablet",A10:F13,3,0)</f>
+        <v>Electronics</v>
+      </c>
+      <c r="I12" s="97" t="s">
+        <v>86</v>
+      </c>
+      <c r="J12" s="94"/>
+      <c r="K12" s="94"/>
+      <c r="L12" s="94"/>
+      <c r="M12" s="94"/>
+      <c r="N12" s="94"/>
+      <c r="O12" s="94"/>
+      <c r="P12" s="94"/>
+      <c r="Q12" s="94"/>
+      <c r="R12" s="94"/>
+      <c r="S12" s="94"/>
+    </row>
+    <row r="13" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="79" t="s">
+        <v>78</v>
+      </c>
+      <c r="B13" s="79">
+        <v>20</v>
+      </c>
+      <c r="C13" s="79">
+        <v>15</v>
+      </c>
+      <c r="D13" s="79">
+        <v>30</v>
+      </c>
+      <c r="E13" s="79">
+        <v>25</v>
+      </c>
+      <c r="F13" s="79">
+        <v>50</v>
+      </c>
+      <c r="G13" s="81"/>
+      <c r="H13" s="82">
+        <f>HLOOKUP("Keyboard",A10:F13,4,0)</f>
+        <v>50</v>
+      </c>
+      <c r="I13" s="97" t="s">
+        <v>87</v>
+      </c>
+      <c r="J13" s="94"/>
+      <c r="K13" s="94"/>
+      <c r="L13" s="94"/>
+      <c r="M13" s="94"/>
+      <c r="N13" s="94"/>
+      <c r="O13" s="94"/>
+      <c r="P13" s="94"/>
+      <c r="Q13" s="94"/>
+      <c r="R13" s="94"/>
+      <c r="S13" s="94"/>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="H4:S4"/>
+    <mergeCell ref="I11:S11"/>
+    <mergeCell ref="I12:S12"/>
+    <mergeCell ref="I13:S13"/>
+    <mergeCell ref="I10:T10"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Practice_file.xlsx
+++ b/Practice_file.xlsx
@@ -8,15 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d58d4d655bee1e81/Desktop/Github/Practice_Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="174" documentId="11_F25DC773A252ABDACC1048BD89DC52D45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{861B0006-7223-4AA4-8A2B-116CAB55E18D}"/>
+  <xr:revisionPtr revIDLastSave="204" documentId="11_F25DC773A252ABDACC1048BD89DC52D45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F3C7770-62F2-4343-B1FB-37879EF43E67}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SUMIF,AVGIF" sheetId="1" r:id="rId1"/>
     <sheet name="COUNTIF,IFs" sheetId="2" r:id="rId2"/>
     <sheet name="V,HLOOKUP" sheetId="3" r:id="rId3"/>
     <sheet name="X,INDEX,MATCH" sheetId="4" r:id="rId4"/>
+    <sheet name="Practice SUMIF" sheetId="5" r:id="rId5"/>
+    <sheet name="COUNTIF" sheetId="6" r:id="rId6"/>
+    <sheet name="VLOOKUP" sheetId="7" r:id="rId7"/>
+    <sheet name="HLOOKUP" sheetId="8" r:id="rId8"/>
+    <sheet name="INDEXMATCH" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -64,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="306">
   <si>
     <t>Data for Practice</t>
   </si>
@@ -439,13 +444,559 @@
   </si>
   <si>
     <t>INDIRECT followed by the cell number</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Account Category</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>Payment Method</t>
+  </si>
+  <si>
+    <t>Problem #</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Travel</t>
+  </si>
+  <si>
+    <t>Credit Card</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Total Travel expenses across all departments</t>
+  </si>
+  <si>
+    <t>Software</t>
+  </si>
+  <si>
+    <t>Bank Transfer</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Total expenses for the Sales department</t>
+  </si>
+  <si>
+    <t>Salaries</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Total Utilities expenses in the East region</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Total expenses paid via Credit Card</t>
+  </si>
+  <si>
+    <t>Operations</t>
+  </si>
+  <si>
+    <t>Utilities</t>
+  </si>
+  <si>
+    <t>Cash</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Total Salaries for the HR department</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>Total Software expenses in January 2025</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>Total Travel expenses in West region using Credit Card</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>Total expenses for IT department in February 2025</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>Total Office Supplies in North region</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Total Utilities expenses paid via Bank Transfer</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Total expenses between 01-Jan-2025 and 31-Jan-2025 for the East region</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>Total Salaries in the East region in February 2025</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Total Travel expenses for Sales department in January 2025</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>Total Software expenses in South region for all months</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>Total Office Supplies in January 2025 paid by Credit Card</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>Total Utilities in East region for Feb 2025 only</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>Total expenses for Marketing department excluding Travel</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>Total Salaries for any department in North region</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>Total expenses in Feb 2025 for all Bank Transfer payments</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>Total expenses in Feb 2025 for Sales and IT combined</t>
+  </si>
+  <si>
+    <t>https://pivotxl.com/sumifs-practice-problems/</t>
+  </si>
+  <si>
+    <t>Count how many customers are from South region AND Due in March 2025</t>
+  </si>
+  <si>
+    <t>Count Paid accounts with Amount ≥ 450 and ≤ 700</t>
+  </si>
+  <si>
+    <t>Count accounts due before February 2025</t>
+  </si>
+  <si>
+    <t>Count customers whose name has exactly 4 letters</t>
+  </si>
+  <si>
+    <t>Count customers whose name starts with 'S'</t>
+  </si>
+  <si>
+    <t>Count Paid accounts from North or South</t>
+  </si>
+  <si>
+    <t>Count Overdue accounts not from the South</t>
+  </si>
+  <si>
+    <t>Count customers with Amount between 400 and 600</t>
+  </si>
+  <si>
+    <t>Count Paid accounts with Due Date in March 2025</t>
+  </si>
+  <si>
+    <t>Count accounts with Due Date in February 2025</t>
+  </si>
+  <si>
+    <t>Count accounts from East region with Amount &gt; 400</t>
+  </si>
+  <si>
+    <t>Count Paid accounts with Amount &lt; 500</t>
+  </si>
+  <si>
+    <t>18-Mar-25</t>
+  </si>
+  <si>
+    <t>Overdue</t>
+  </si>
+  <si>
+    <t>Paul</t>
+  </si>
+  <si>
+    <t>Count Overdue accounts with Amount &gt; 500</t>
+  </si>
+  <si>
+    <t>12-Mar-25</t>
+  </si>
+  <si>
+    <t>Paid</t>
+  </si>
+  <si>
+    <t>Leo</t>
+  </si>
+  <si>
+    <t>Count Paid accounts in the South region</t>
+  </si>
+  <si>
+    <t>10-Jan-25</t>
+  </si>
+  <si>
+    <t>Sara</t>
+  </si>
+  <si>
+    <t>Count Overdue accounts in the North region</t>
+  </si>
+  <si>
+    <t>05-Feb-25</t>
+  </si>
+  <si>
+    <t>Count customers with Amount less than 400</t>
+  </si>
+  <si>
+    <t>25-Mar-25</t>
+  </si>
+  <si>
+    <t>Nina</t>
+  </si>
+  <si>
+    <t>Count customers with Amount greater than 500</t>
+  </si>
+  <si>
+    <t>20-Feb-25</t>
+  </si>
+  <si>
+    <t>Alex</t>
+  </si>
+  <si>
+    <t>Count how many customers are from the North region</t>
+  </si>
+  <si>
+    <t>15-Mar-25</t>
+  </si>
+  <si>
+    <t>Rita</t>
+  </si>
+  <si>
+    <t>Count how many accounts are Paid</t>
+  </si>
+  <si>
+    <t>10-Feb-25</t>
+  </si>
+  <si>
+    <t>Sam</t>
+  </si>
+  <si>
+    <t>Count how many accounts are Overdue</t>
+  </si>
+  <si>
+    <t>05-Jan-25</t>
+  </si>
+  <si>
+    <t>Formula</t>
+  </si>
+  <si>
+    <t>Problem</t>
+  </si>
+  <si>
+    <t>01-Jan-25</t>
+  </si>
+  <si>
+    <t>Practice Problems &amp; Solutions</t>
+  </si>
+  <si>
+    <t>Due Date</t>
+  </si>
+  <si>
+    <t>Customer</t>
+  </si>
+  <si>
+    <t>https://pivotxl.com/countif-countifs-excel-practice-problems/</t>
+  </si>
+  <si>
+    <t>EmpID</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Salary</t>
+  </si>
+  <si>
+    <t>Bonus %</t>
+  </si>
+  <si>
+    <t>Solution</t>
+  </si>
+  <si>
+    <t>Alice Wong</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>1. Find the Name of the employee with EmpID = 104.</t>
+  </si>
+  <si>
+    <t>Bob Smith</t>
+  </si>
+  <si>
+    <t>Chicago</t>
+  </si>
+  <si>
+    <t>2. Find the Department of employee 106.</t>
+  </si>
+  <si>
+    <t>Carol Jones</t>
+  </si>
+  <si>
+    <t>San Diego</t>
+  </si>
+  <si>
+    <t>3. Find the Salary of employee 102.</t>
+  </si>
+  <si>
+    <t>David Chen</t>
+  </si>
+  <si>
+    <t>4. Retrieve the Bonus % for EmpID = 109.</t>
+  </si>
+  <si>
+    <t>Emily Davis</t>
+  </si>
+  <si>
+    <t>5. Find the Location of employee 101.</t>
+  </si>
+  <si>
+    <t>Frank Lee</t>
+  </si>
+  <si>
+    <t>Boston</t>
+  </si>
+  <si>
+    <t>6. Using EmpID, get the Salary of 110.</t>
+  </si>
+  <si>
+    <t>Grace Hall</t>
+  </si>
+  <si>
+    <t>7. Retrieve the Department of 103.</t>
+  </si>
+  <si>
+    <t>Henry Adams</t>
+  </si>
+  <si>
+    <t>8. Find the Name of the employee who earns 62,000.</t>
+  </si>
+  <si>
+    <t>Irene Scott</t>
+  </si>
+  <si>
+    <t>9. Find the Salary of 105 and add the Bonus % to compute total compensation.</t>
+  </si>
+  <si>
+    <t>Jack White</t>
+  </si>
+  <si>
+    <t>10. Lookup the Location of 107.</t>
+  </si>
+  <si>
+    <t>11. Find the Bonus % of 102 and calculate the Bonus Amount.</t>
+  </si>
+  <si>
+    <t>12. Return the Department for employee 108.</t>
+  </si>
+  <si>
+    <t>13. Get the Name of employee 109.</t>
+  </si>
+  <si>
+    <t>14. Find the Salary of the employee in Boston (Finance).</t>
+  </si>
+  <si>
+    <t>15. Retrieve the Department of 101.</t>
+  </si>
+  <si>
+    <t>16. Find the Bonus % of the highest-salary employee (EmpID 110).</t>
+  </si>
+  <si>
+    <t>17. Lookup the Salary for 103 and apply a 5% increment.</t>
+  </si>
+  <si>
+    <t>18. Find the Location of 105.</t>
+  </si>
+  <si>
+    <t>19. Return the Name of employee 106.</t>
+  </si>
+  <si>
+    <t>20. For EmpID 107, calculate Salary + (Salary * Bonus %).</t>
+  </si>
+  <si>
+    <t>https://pivotxl.com/vlookup-practice-exercises/</t>
+  </si>
+  <si>
+    <t>HLOOKUP Practice Data</t>
+  </si>
+  <si>
+    <t>Record1</t>
+  </si>
+  <si>
+    <t>Record2</t>
+  </si>
+  <si>
+    <t>Record3</t>
+  </si>
+  <si>
+    <t>Record4</t>
+  </si>
+  <si>
+    <t>Record5</t>
+  </si>
+  <si>
+    <t>Record6</t>
+  </si>
+  <si>
+    <t>Record7</t>
+  </si>
+  <si>
+    <t>Record8</t>
+  </si>
+  <si>
+    <t>Record9</t>
+  </si>
+  <si>
+    <t>Record10</t>
+  </si>
+  <si>
+    <t>1. Use HLOOKUP to find the Name of EmpID 104.</t>
+  </si>
+  <si>
+    <t>2. Retrieve the Department of EmpID 106.</t>
+  </si>
+  <si>
+    <t>3. Find the Salary of EmpID 102.</t>
+  </si>
+  <si>
+    <t>4. Get the Bonus % for EmpID 109.</t>
+  </si>
+  <si>
+    <t>5. Find the Location of EmpID 101.</t>
+  </si>
+  <si>
+    <t>6. Use HLOOKUP to return the Salary of EmpID 110.</t>
+  </si>
+  <si>
+    <t>7. Retrieve the Department of EmpID 103.</t>
+  </si>
+  <si>
+    <t>8. Find the Name of the employee with Salary 62,000 (needs MATCH).</t>
+  </si>
+  <si>
+    <t>Requires INDEX/MATCH combo → Emily Davis</t>
+  </si>
+  <si>
+    <t>9. Compute total compensation for EmpID 105 (Salary + Bonus).</t>
+  </si>
+  <si>
+    <t>10. Get the Location of EmpID 107.</t>
+  </si>
+  <si>
+    <t>https://pivotxl.com/hlookup-practice-exercises-xls-download/</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>Chair</t>
+  </si>
+  <si>
+    <t>Furniture</t>
+  </si>
+  <si>
+    <t>Desk</t>
+  </si>
+  <si>
+    <t>INDEX MATCH Practice Problems &amp; Solutions</t>
+  </si>
+  <si>
+    <t>Find the sales of 'Phone'</t>
+  </si>
+  <si>
+    <t>Get the Region for Product ID 104</t>
+  </si>
+  <si>
+    <t>Find the Category of 'Monitor'</t>
+  </si>
+  <si>
+    <t>Lookup Sales for Product ID 101</t>
+  </si>
+  <si>
+    <t>Find the Product Name sold in the East region</t>
+  </si>
+  <si>
+    <t>Return the Region for Product Name = Chair</t>
+  </si>
+  <si>
+    <t>Find Sales where Product ID = 105</t>
+  </si>
+  <si>
+    <t>Get Category for Product ID 102</t>
+  </si>
+  <si>
+    <t>Find Product Name for Sales = 2500</t>
+  </si>
+  <si>
+    <t>Lookup Region for Product Name = Laptop</t>
+  </si>
+  <si>
+    <t>https://pivotxl.com/index-match-practice-exercises-xls-download/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="m/d/yy;@"/>
+  </numFmts>
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -524,6 +1075,30 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="10">
     <fill>
@@ -581,7 +1156,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -892,11 +1467,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="126">
+  <cellXfs count="134">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1013,96 +1600,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1111,15 +1608,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1128,6 +1616,124 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1137,42 +1743,42 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1466,14 +2072,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="11" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="88" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
+      <c r="B1" s="88"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="88"/>
+      <c r="E1" s="88"/>
+      <c r="F1" s="88"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
@@ -1635,17 +2241,17 @@
       <c r="F12" s="18"/>
     </row>
     <row r="15" spans="1:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="68" t="s">
+      <c r="A15" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="68"/>
-      <c r="C15" s="68"/>
-      <c r="D15" s="68"/>
-      <c r="E15" s="68"/>
-      <c r="F15" s="68"/>
-      <c r="G15" s="68"/>
-      <c r="H15" s="68"/>
-      <c r="I15" s="68"/>
+      <c r="B15" s="88"/>
+      <c r="C15" s="88"/>
+      <c r="D15" s="88"/>
+      <c r="E15" s="88"/>
+      <c r="F15" s="88"/>
+      <c r="G15" s="88"/>
+      <c r="H15" s="88"/>
+      <c r="I15" s="88"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
@@ -1918,15 +2524,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="90" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="72"/>
+      <c r="B1" s="91"/>
+      <c r="C1" s="91"/>
+      <c r="D1" s="91"/>
+      <c r="E1" s="91"/>
+      <c r="F1" s="91"/>
+      <c r="G1" s="92"/>
       <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2167,15 +2773,15 @@
     </row>
     <row r="15" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="16" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="70" t="s">
+      <c r="A16" s="90" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="71"/>
-      <c r="C16" s="71"/>
-      <c r="D16" s="71"/>
-      <c r="E16" s="71"/>
-      <c r="F16" s="82"/>
-      <c r="G16" s="82"/>
+      <c r="B16" s="91"/>
+      <c r="C16" s="91"/>
+      <c r="D16" s="91"/>
+      <c r="E16" s="91"/>
+      <c r="F16" s="102"/>
+      <c r="G16" s="102"/>
     </row>
     <row r="17" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="24" t="s">
@@ -2223,10 +2829,10 @@
         <f>COUNTIF(B18:B27,"&gt;30")</f>
         <v>6</v>
       </c>
-      <c r="H18" s="83" t="s">
+      <c r="H18" s="103" t="s">
         <v>70</v>
       </c>
-      <c r="I18" s="84"/>
+      <c r="I18" s="104"/>
     </row>
     <row r="19" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="29" t="s">
@@ -2251,10 +2857,10 @@
         <f>COUNTIF(E18:E27,"Male")</f>
         <v>5</v>
       </c>
-      <c r="H19" s="83" t="s">
+      <c r="H19" s="103" t="s">
         <v>71</v>
       </c>
-      <c r="I19" s="84"/>
+      <c r="I19" s="104"/>
     </row>
     <row r="20" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="29" t="s">
@@ -2410,16 +3016,16 @@
     </row>
     <row r="30" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="31" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="73" t="s">
+      <c r="A31" s="93" t="s">
         <v>60</v>
       </c>
-      <c r="B31" s="74"/>
-      <c r="C31" s="74"/>
-      <c r="D31" s="74"/>
-      <c r="E31" s="74"/>
-      <c r="F31" s="74"/>
-      <c r="G31" s="74"/>
-      <c r="H31" s="75"/>
+      <c r="B31" s="94"/>
+      <c r="C31" s="94"/>
+      <c r="D31" s="94"/>
+      <c r="E31" s="94"/>
+      <c r="F31" s="94"/>
+      <c r="G31" s="94"/>
+      <c r="H31" s="95"/>
     </row>
     <row r="32" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="39" t="s">
@@ -2435,9 +3041,9 @@
         <v>62</v>
       </c>
       <c r="E32" s="40"/>
-      <c r="F32" s="85"/>
-      <c r="G32" s="86"/>
-      <c r="H32" s="87"/>
+      <c r="F32" s="105"/>
+      <c r="G32" s="106"/>
+      <c r="H32" s="107"/>
     </row>
     <row r="33" spans="1:10" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="29" t="s">
@@ -2456,15 +3062,15 @@
         <f>COUNTIF(D33:D51,"Pending")</f>
         <v>7</v>
       </c>
-      <c r="F33" s="76" t="s">
+      <c r="F33" s="96" t="s">
         <v>69</v>
       </c>
-      <c r="G33" s="77"/>
-      <c r="H33" s="78"/>
-      <c r="I33" s="88" t="s">
+      <c r="G33" s="97"/>
+      <c r="H33" s="98"/>
+      <c r="I33" s="108" t="s">
         <v>72</v>
       </c>
-      <c r="J33" s="84"/>
+      <c r="J33" s="104"/>
     </row>
     <row r="34" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="29" t="s">
@@ -2483,15 +3089,15 @@
         <f>COUNTIFS(B33:B51,"West",D33:D51,"Delivered")</f>
         <v>3</v>
       </c>
-      <c r="F34" s="79" t="s">
+      <c r="F34" s="99" t="s">
         <v>73</v>
       </c>
-      <c r="G34" s="80"/>
-      <c r="H34" s="81"/>
-      <c r="I34" s="91" t="s">
+      <c r="G34" s="100"/>
+      <c r="H34" s="101"/>
+      <c r="I34" s="111" t="s">
         <v>74</v>
       </c>
-      <c r="J34" s="91"/>
+      <c r="J34" s="111"/>
     </row>
     <row r="35" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="29" t="s">
@@ -2507,11 +3113,11 @@
         <v>64</v>
       </c>
       <c r="E35" s="25"/>
-      <c r="F35" s="69"/>
-      <c r="G35" s="69"/>
-      <c r="H35" s="69"/>
-      <c r="I35" s="92"/>
-      <c r="J35" s="91"/>
+      <c r="F35" s="89"/>
+      <c r="G35" s="89"/>
+      <c r="H35" s="89"/>
+      <c r="I35" s="112"/>
+      <c r="J35" s="111"/>
     </row>
     <row r="36" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="29" t="s">
@@ -2527,11 +3133,11 @@
         <v>64</v>
       </c>
       <c r="E36" s="25"/>
-      <c r="F36" s="69"/>
-      <c r="G36" s="69"/>
-      <c r="H36" s="69"/>
-      <c r="I36" s="89"/>
-      <c r="J36" s="90"/>
+      <c r="F36" s="89"/>
+      <c r="G36" s="89"/>
+      <c r="H36" s="89"/>
+      <c r="I36" s="109"/>
+      <c r="J36" s="110"/>
     </row>
     <row r="37" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="29" t="s">
@@ -2547,11 +3153,11 @@
         <v>66</v>
       </c>
       <c r="E37" s="25"/>
-      <c r="F37" s="69"/>
-      <c r="G37" s="69"/>
-      <c r="H37" s="69"/>
-      <c r="I37" s="89"/>
-      <c r="J37" s="90"/>
+      <c r="F37" s="89"/>
+      <c r="G37" s="89"/>
+      <c r="H37" s="89"/>
+      <c r="I37" s="109"/>
+      <c r="J37" s="110"/>
     </row>
     <row r="38" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="29" t="s">
@@ -2567,11 +3173,11 @@
         <v>64</v>
       </c>
       <c r="E38" s="25"/>
-      <c r="F38" s="69"/>
-      <c r="G38" s="69"/>
-      <c r="H38" s="69"/>
-      <c r="I38" s="89"/>
-      <c r="J38" s="90"/>
+      <c r="F38" s="89"/>
+      <c r="G38" s="89"/>
+      <c r="H38" s="89"/>
+      <c r="I38" s="109"/>
+      <c r="J38" s="110"/>
     </row>
     <row r="39" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="29" t="s">
@@ -2587,11 +3193,11 @@
         <v>64</v>
       </c>
       <c r="E39" s="25"/>
-      <c r="F39" s="69"/>
-      <c r="G39" s="69"/>
-      <c r="H39" s="69"/>
-      <c r="I39" s="89"/>
-      <c r="J39" s="90"/>
+      <c r="F39" s="89"/>
+      <c r="G39" s="89"/>
+      <c r="H39" s="89"/>
+      <c r="I39" s="109"/>
+      <c r="J39" s="110"/>
     </row>
     <row r="40" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="29" t="s">
@@ -2607,11 +3213,11 @@
         <v>66</v>
       </c>
       <c r="E40" s="25"/>
-      <c r="F40" s="69"/>
-      <c r="G40" s="69"/>
-      <c r="H40" s="69"/>
-      <c r="I40" s="89"/>
-      <c r="J40" s="90"/>
+      <c r="F40" s="89"/>
+      <c r="G40" s="89"/>
+      <c r="H40" s="89"/>
+      <c r="I40" s="109"/>
+      <c r="J40" s="110"/>
     </row>
     <row r="41" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="29" t="s">
@@ -2627,11 +3233,11 @@
         <v>64</v>
       </c>
       <c r="E41" s="25"/>
-      <c r="F41" s="69"/>
-      <c r="G41" s="69"/>
-      <c r="H41" s="69"/>
-      <c r="I41" s="89"/>
-      <c r="J41" s="90"/>
+      <c r="F41" s="89"/>
+      <c r="G41" s="89"/>
+      <c r="H41" s="89"/>
+      <c r="I41" s="109"/>
+      <c r="J41" s="110"/>
     </row>
     <row r="42" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="29" t="s">
@@ -2647,11 +3253,11 @@
         <v>66</v>
       </c>
       <c r="E42" s="25"/>
-      <c r="F42" s="69"/>
-      <c r="G42" s="69"/>
-      <c r="H42" s="69"/>
-      <c r="I42" s="89"/>
-      <c r="J42" s="90"/>
+      <c r="F42" s="89"/>
+      <c r="G42" s="89"/>
+      <c r="H42" s="89"/>
+      <c r="I42" s="109"/>
+      <c r="J42" s="110"/>
     </row>
     <row r="43" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="29" t="s">
@@ -2667,11 +3273,11 @@
         <v>64</v>
       </c>
       <c r="E43" s="25"/>
-      <c r="F43" s="69"/>
-      <c r="G43" s="69"/>
-      <c r="H43" s="69"/>
-      <c r="I43" s="89"/>
-      <c r="J43" s="90"/>
+      <c r="F43" s="89"/>
+      <c r="G43" s="89"/>
+      <c r="H43" s="89"/>
+      <c r="I43" s="109"/>
+      <c r="J43" s="110"/>
     </row>
     <row r="44" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="29" t="s">
@@ -2687,11 +3293,11 @@
         <v>64</v>
       </c>
       <c r="E44" s="25"/>
-      <c r="F44" s="69"/>
-      <c r="G44" s="69"/>
-      <c r="H44" s="69"/>
-      <c r="I44" s="89"/>
-      <c r="J44" s="90"/>
+      <c r="F44" s="89"/>
+      <c r="G44" s="89"/>
+      <c r="H44" s="89"/>
+      <c r="I44" s="109"/>
+      <c r="J44" s="110"/>
     </row>
     <row r="45" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="29" t="s">
@@ -2707,9 +3313,9 @@
         <v>66</v>
       </c>
       <c r="E45" s="25"/>
-      <c r="F45" s="69"/>
-      <c r="G45" s="69"/>
-      <c r="H45" s="69"/>
+      <c r="F45" s="89"/>
+      <c r="G45" s="89"/>
+      <c r="H45" s="89"/>
     </row>
     <row r="46" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="29" t="s">
@@ -2725,9 +3331,9 @@
         <v>64</v>
       </c>
       <c r="E46" s="25"/>
-      <c r="F46" s="69"/>
-      <c r="G46" s="69"/>
-      <c r="H46" s="69"/>
+      <c r="F46" s="89"/>
+      <c r="G46" s="89"/>
+      <c r="H46" s="89"/>
     </row>
     <row r="47" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="29" t="s">
@@ -2743,9 +3349,9 @@
         <v>66</v>
       </c>
       <c r="E47" s="25"/>
-      <c r="F47" s="69"/>
-      <c r="G47" s="69"/>
-      <c r="H47" s="69"/>
+      <c r="F47" s="89"/>
+      <c r="G47" s="89"/>
+      <c r="H47" s="89"/>
     </row>
     <row r="48" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="29" t="s">
@@ -2761,9 +3367,9 @@
         <v>64</v>
       </c>
       <c r="E48" s="25"/>
-      <c r="F48" s="69"/>
-      <c r="G48" s="69"/>
-      <c r="H48" s="69"/>
+      <c r="F48" s="89"/>
+      <c r="G48" s="89"/>
+      <c r="H48" s="89"/>
     </row>
     <row r="49" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="29" t="s">
@@ -2779,9 +3385,9 @@
         <v>64</v>
       </c>
       <c r="E49" s="25"/>
-      <c r="F49" s="69"/>
-      <c r="G49" s="69"/>
-      <c r="H49" s="69"/>
+      <c r="F49" s="89"/>
+      <c r="G49" s="89"/>
+      <c r="H49" s="89"/>
     </row>
     <row r="50" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="29" t="s">
@@ -2797,9 +3403,9 @@
         <v>66</v>
       </c>
       <c r="E50" s="25"/>
-      <c r="F50" s="69"/>
-      <c r="G50" s="69"/>
-      <c r="H50" s="69"/>
+      <c r="F50" s="89"/>
+      <c r="G50" s="89"/>
+      <c r="H50" s="89"/>
     </row>
     <row r="51" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="29" t="s">
@@ -2815,9 +3421,9 @@
         <v>64</v>
       </c>
       <c r="E51" s="25"/>
-      <c r="F51" s="69"/>
-      <c r="G51" s="69"/>
-      <c r="H51" s="69"/>
+      <c r="F51" s="89"/>
+      <c r="G51" s="89"/>
+      <c r="H51" s="89"/>
     </row>
   </sheetData>
   <mergeCells count="36">
@@ -2878,14 +3484,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="93" t="s">
+      <c r="A1" s="113" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="95"/>
+      <c r="B1" s="114"/>
+      <c r="C1" s="114"/>
+      <c r="D1" s="114"/>
+      <c r="E1" s="114"/>
+      <c r="F1" s="115"/>
     </row>
     <row r="2" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="58" t="s">
@@ -2942,20 +3548,20 @@
       <c r="G4" s="65" t="s">
         <v>84</v>
       </c>
-      <c r="H4" s="96" t="s">
+      <c r="H4" s="116" t="s">
         <v>89</v>
       </c>
-      <c r="I4" s="96"/>
-      <c r="J4" s="96"/>
-      <c r="K4" s="96"/>
-      <c r="L4" s="96"/>
-      <c r="M4" s="96"/>
-      <c r="N4" s="96"/>
-      <c r="O4" s="96"/>
-      <c r="P4" s="96"/>
-      <c r="Q4" s="96"/>
-      <c r="R4" s="96"/>
-      <c r="S4" s="96"/>
+      <c r="I4" s="116"/>
+      <c r="J4" s="116"/>
+      <c r="K4" s="116"/>
+      <c r="L4" s="116"/>
+      <c r="M4" s="116"/>
+      <c r="N4" s="116"/>
+      <c r="O4" s="116"/>
+      <c r="P4" s="116"/>
+      <c r="Q4" s="116"/>
+      <c r="R4" s="116"/>
+      <c r="S4" s="116"/>
     </row>
     <row r="5" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="61" t="s">
@@ -3035,20 +3641,20 @@
       <c r="H10" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="I10" s="96" t="s">
+      <c r="I10" s="116" t="s">
         <v>88</v>
       </c>
-      <c r="J10" s="96"/>
-      <c r="K10" s="96"/>
-      <c r="L10" s="96"/>
-      <c r="M10" s="96"/>
-      <c r="N10" s="96"/>
-      <c r="O10" s="96"/>
-      <c r="P10" s="96"/>
-      <c r="Q10" s="96"/>
-      <c r="R10" s="96"/>
-      <c r="S10" s="96"/>
-      <c r="T10" s="96"/>
+      <c r="J10" s="116"/>
+      <c r="K10" s="116"/>
+      <c r="L10" s="116"/>
+      <c r="M10" s="116"/>
+      <c r="N10" s="116"/>
+      <c r="O10" s="116"/>
+      <c r="P10" s="116"/>
+      <c r="Q10" s="116"/>
+      <c r="R10" s="116"/>
+      <c r="S10" s="116"/>
+      <c r="T10" s="116"/>
     </row>
     <row r="11" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="54" t="s">
@@ -3074,19 +3680,19 @@
         <f>HLOOKUP("Laptop",A10:F13,2,0)</f>
         <v>1000</v>
       </c>
-      <c r="I11" s="97" t="s">
+      <c r="I11" s="117" t="s">
         <v>85</v>
       </c>
-      <c r="J11" s="96"/>
-      <c r="K11" s="96"/>
-      <c r="L11" s="96"/>
-      <c r="M11" s="96"/>
-      <c r="N11" s="96"/>
-      <c r="O11" s="96"/>
-      <c r="P11" s="96"/>
-      <c r="Q11" s="96"/>
-      <c r="R11" s="96"/>
-      <c r="S11" s="96"/>
+      <c r="J11" s="116"/>
+      <c r="K11" s="116"/>
+      <c r="L11" s="116"/>
+      <c r="M11" s="116"/>
+      <c r="N11" s="116"/>
+      <c r="O11" s="116"/>
+      <c r="P11" s="116"/>
+      <c r="Q11" s="116"/>
+      <c r="R11" s="116"/>
+      <c r="S11" s="116"/>
     </row>
     <row r="12" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="54" t="s">
@@ -3112,19 +3718,19 @@
         <f>HLOOKUP("Tablet",A10:F13,3,0)</f>
         <v>Electronics</v>
       </c>
-      <c r="I12" s="97" t="s">
+      <c r="I12" s="117" t="s">
         <v>86</v>
       </c>
-      <c r="J12" s="96"/>
-      <c r="K12" s="96"/>
-      <c r="L12" s="96"/>
-      <c r="M12" s="96"/>
-      <c r="N12" s="96"/>
-      <c r="O12" s="96"/>
-      <c r="P12" s="96"/>
-      <c r="Q12" s="96"/>
-      <c r="R12" s="96"/>
-      <c r="S12" s="96"/>
+      <c r="J12" s="116"/>
+      <c r="K12" s="116"/>
+      <c r="L12" s="116"/>
+      <c r="M12" s="116"/>
+      <c r="N12" s="116"/>
+      <c r="O12" s="116"/>
+      <c r="P12" s="116"/>
+      <c r="Q12" s="116"/>
+      <c r="R12" s="116"/>
+      <c r="S12" s="116"/>
     </row>
     <row r="13" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="54" t="s">
@@ -3150,19 +3756,19 @@
         <f>HLOOKUP("Keyboard",A10:F13,4,0)</f>
         <v>50</v>
       </c>
-      <c r="I13" s="97" t="s">
+      <c r="I13" s="117" t="s">
         <v>87</v>
       </c>
-      <c r="J13" s="96"/>
-      <c r="K13" s="96"/>
-      <c r="L13" s="96"/>
-      <c r="M13" s="96"/>
-      <c r="N13" s="96"/>
-      <c r="O13" s="96"/>
-      <c r="P13" s="96"/>
-      <c r="Q13" s="96"/>
-      <c r="R13" s="96"/>
-      <c r="S13" s="96"/>
+      <c r="J13" s="116"/>
+      <c r="K13" s="116"/>
+      <c r="L13" s="116"/>
+      <c r="M13" s="116"/>
+      <c r="N13" s="116"/>
+      <c r="O13" s="116"/>
+      <c r="P13" s="116"/>
+      <c r="Q13" s="116"/>
+      <c r="R13" s="116"/>
+      <c r="S13" s="116"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -3188,271 +3794,271 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="111" t="s">
+      <c r="A1" s="118" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="112"/>
-      <c r="C1" s="112"/>
-      <c r="D1" s="112"/>
-      <c r="E1" s="112"/>
-      <c r="F1" s="112"/>
-      <c r="G1" s="113"/>
+      <c r="B1" s="119"/>
+      <c r="C1" s="119"/>
+      <c r="D1" s="119"/>
+      <c r="E1" s="119"/>
+      <c r="F1" s="119"/>
+      <c r="G1" s="120"/>
     </row>
     <row r="2" spans="1:14" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="110" t="s">
+      <c r="A2" s="77" t="s">
         <v>91</v>
       </c>
-      <c r="B2" s="110" t="s">
+      <c r="B2" s="77" t="s">
         <v>92</v>
       </c>
-      <c r="C2" s="110" t="s">
+      <c r="C2" s="77" t="s">
         <v>93</v>
       </c>
-      <c r="D2" s="114" t="s">
+      <c r="D2" s="78" t="s">
         <v>76</v>
       </c>
-      <c r="E2" s="116"/>
-      <c r="F2" s="123" t="s">
+      <c r="E2" s="80"/>
+      <c r="F2" s="85" t="s">
         <v>122</v>
       </c>
-      <c r="G2" s="117"/>
+      <c r="G2" s="81"/>
     </row>
     <row r="3" spans="1:14" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="99" t="s">
+      <c r="A3" s="69" t="s">
         <v>94</v>
       </c>
-      <c r="B3" s="99" t="s">
+      <c r="B3" s="69" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="99">
+      <c r="C3" s="69">
         <v>150</v>
       </c>
-      <c r="D3" s="115">
+      <c r="D3" s="79">
         <v>75000</v>
       </c>
-      <c r="E3" s="122">
+      <c r="E3" s="84">
         <f>_xlfn.XLOOKUP("P102",A3:A12,D3:D12)</f>
         <v>1500</v>
       </c>
-      <c r="F3" s="120" t="s">
+      <c r="F3" s="124" t="s">
         <v>109</v>
       </c>
-      <c r="G3" s="118"/>
+      <c r="G3" s="125"/>
       <c r="H3" s="65" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="4" spans="1:14" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="99" t="s">
+      <c r="A4" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="B4" s="99" t="s">
+      <c r="B4" s="69" t="s">
         <v>65</v>
       </c>
-      <c r="C4" s="99">
+      <c r="C4" s="69">
         <v>300</v>
       </c>
-      <c r="D4" s="115">
+      <c r="D4" s="79">
         <v>500</v>
       </c>
-      <c r="E4" s="122" t="str">
+      <c r="E4" s="84" t="str">
         <f>_xlfn.XLOOKUP("P999",A3:A12,C3:C12,"Not Found")</f>
         <v>Not Found</v>
       </c>
-      <c r="F4" s="120" t="s">
+      <c r="F4" s="124" t="s">
         <v>110</v>
       </c>
-      <c r="G4" s="118"/>
+      <c r="G4" s="125"/>
       <c r="H4" s="65" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="99" t="s">
+      <c r="A5" s="69" t="s">
         <v>96</v>
       </c>
-      <c r="B5" s="99" t="s">
+      <c r="B5" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="C5" s="124">
+      <c r="C5" s="86">
         <v>200</v>
       </c>
-      <c r="D5" s="115">
+      <c r="D5" s="79">
         <v>1500</v>
       </c>
-      <c r="E5" s="122" t="str">
+      <c r="E5" s="84" t="str">
         <f>INDEX(A3:D12,3,2)</f>
         <v>Keyboard</v>
       </c>
-      <c r="F5" s="120" t="s">
+      <c r="F5" s="124" t="s">
         <v>112</v>
       </c>
-      <c r="G5" s="118"/>
+      <c r="G5" s="125"/>
       <c r="H5" s="65" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="99" t="s">
+      <c r="A6" s="69" t="s">
         <v>97</v>
       </c>
-      <c r="B6" s="99" t="s">
+      <c r="B6" s="69" t="s">
         <v>81</v>
       </c>
-      <c r="C6" s="99">
+      <c r="C6" s="69">
         <v>120</v>
       </c>
-      <c r="D6" s="115">
+      <c r="D6" s="79">
         <v>10000</v>
       </c>
-      <c r="E6" s="122">
+      <c r="E6" s="84">
         <f>MATCH("Laptop",B3:B12,0)</f>
         <v>1</v>
       </c>
-      <c r="F6" s="120" t="s">
+      <c r="F6" s="124" t="s">
         <v>114</v>
       </c>
-      <c r="G6" s="118"/>
+      <c r="G6" s="125"/>
       <c r="H6" s="65" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="99" t="s">
+      <c r="A7" s="69" t="s">
         <v>98</v>
       </c>
-      <c r="B7" s="99" t="s">
+      <c r="B7" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="C7" s="99">
+      <c r="C7" s="69">
         <v>180</v>
       </c>
-      <c r="D7" s="115">
+      <c r="D7" s="79">
         <v>2500</v>
       </c>
-      <c r="E7" s="122">
+      <c r="E7" s="84">
         <f>INDEX(D3:D12,MATCH("Monitor",B3:B12,0))</f>
         <v>10000</v>
       </c>
-      <c r="F7" s="120" t="s">
+      <c r="F7" s="124" t="s">
         <v>115</v>
       </c>
-      <c r="G7" s="118"/>
+      <c r="G7" s="125"/>
       <c r="H7" s="65" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:14" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="99" t="s">
+      <c r="A8" s="69" t="s">
         <v>100</v>
       </c>
-      <c r="B8" s="99" t="s">
+      <c r="B8" s="69" t="s">
         <v>101</v>
       </c>
-      <c r="C8" s="99">
+      <c r="C8" s="69">
         <v>90</v>
       </c>
-      <c r="D8" s="115">
+      <c r="D8" s="79">
         <v>4000</v>
       </c>
-      <c r="E8" s="122"/>
-      <c r="F8" s="120"/>
-      <c r="G8" s="118"/>
-      <c r="I8" s="96" t="s">
+      <c r="E8" s="84"/>
+      <c r="F8" s="124"/>
+      <c r="G8" s="125"/>
+      <c r="I8" s="116" t="s">
         <v>113</v>
       </c>
-      <c r="J8" s="96"/>
-      <c r="K8" s="96"/>
-      <c r="L8" s="96"/>
-      <c r="M8" s="96"/>
-      <c r="N8" s="96"/>
+      <c r="J8" s="116"/>
+      <c r="K8" s="116"/>
+      <c r="L8" s="116"/>
+      <c r="M8" s="116"/>
+      <c r="N8" s="116"/>
     </row>
     <row r="9" spans="1:14" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="99" t="s">
+      <c r="A9" s="69" t="s">
         <v>102</v>
       </c>
-      <c r="B9" s="99" t="s">
+      <c r="B9" s="69" t="s">
         <v>103</v>
       </c>
-      <c r="C9" s="99">
+      <c r="C9" s="69">
         <v>210</v>
       </c>
-      <c r="D9" s="115">
+      <c r="D9" s="79">
         <v>1200</v>
       </c>
-      <c r="E9" s="122" t="str">
+      <c r="E9" s="84" t="str">
         <f ca="1">OFFSET(A2,5,1)</f>
         <v>Speaker</v>
       </c>
-      <c r="F9" s="120" t="s">
+      <c r="F9" s="124" t="s">
         <v>120</v>
       </c>
-      <c r="G9" s="118"/>
+      <c r="G9" s="125"/>
       <c r="H9" s="65" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="99" t="s">
+      <c r="A10" s="69" t="s">
         <v>104</v>
       </c>
-      <c r="B10" s="99" t="s">
+      <c r="B10" s="69" t="s">
         <v>79</v>
       </c>
-      <c r="C10" s="99">
+      <c r="C10" s="69">
         <v>80</v>
       </c>
-      <c r="D10" s="115">
+      <c r="D10" s="79">
         <v>30000</v>
       </c>
-      <c r="E10" s="122"/>
-      <c r="F10" s="120"/>
-      <c r="G10" s="118"/>
+      <c r="E10" s="84"/>
+      <c r="F10" s="124"/>
+      <c r="G10" s="125"/>
     </row>
     <row r="11" spans="1:14" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="99" t="s">
+      <c r="A11" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="B11" s="99" t="s">
+      <c r="B11" s="69" t="s">
         <v>106</v>
       </c>
-      <c r="C11" s="99">
+      <c r="C11" s="69">
         <v>160</v>
       </c>
-      <c r="D11" s="115">
+      <c r="D11" s="79">
         <v>3500</v>
       </c>
-      <c r="E11" s="125" cm="1">
+      <c r="E11" s="87" cm="1">
         <f t="array" aca="1" ref="E11" ca="1">INDIRECT(F2)</f>
         <v>200</v>
       </c>
-      <c r="F11" s="120" t="s">
+      <c r="F11" s="124" t="s">
         <v>123</v>
       </c>
-      <c r="G11" s="118"/>
+      <c r="G11" s="125"/>
       <c r="H11" s="65" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="12" spans="1:14" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="99" t="s">
+      <c r="A12" s="69" t="s">
         <v>107</v>
       </c>
-      <c r="B12" s="99" t="s">
+      <c r="B12" s="69" t="s">
         <v>108</v>
       </c>
-      <c r="C12" s="99">
+      <c r="C12" s="69">
         <v>400</v>
       </c>
-      <c r="D12" s="115">
+      <c r="D12" s="79">
         <v>800</v>
       </c>
-      <c r="E12" s="121"/>
-      <c r="F12" s="121"/>
-      <c r="G12" s="119"/>
+      <c r="E12" s="83"/>
+      <c r="F12" s="83"/>
+      <c r="G12" s="82"/>
     </row>
     <row r="13" spans="1:14" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="102"/>
+      <c r="A13" s="72"/>
       <c r="B13" s="59"/>
       <c r="C13" s="59"/>
       <c r="D13" s="59"/>
@@ -3461,15 +4067,15 @@
       <c r="G13" s="59"/>
     </row>
     <row r="14" spans="1:14" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="103" t="s">
+      <c r="A14" s="121" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="104"/>
-      <c r="C14" s="104"/>
-      <c r="D14" s="104"/>
-      <c r="E14" s="104"/>
-      <c r="F14" s="104"/>
-      <c r="G14" s="105"/>
+      <c r="B14" s="122"/>
+      <c r="C14" s="122"/>
+      <c r="D14" s="122"/>
+      <c r="E14" s="122"/>
+      <c r="F14" s="122"/>
+      <c r="G14" s="123"/>
     </row>
     <row r="15" spans="1:14" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="58" t="s">
@@ -3484,11 +4090,11 @@
       <c r="D15" s="58" t="s">
         <v>78</v>
       </c>
-      <c r="E15" s="106"/>
-      <c r="F15" s="107" t="s">
+      <c r="E15" s="73"/>
+      <c r="F15" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="108" t="s">
+      <c r="G15" s="75" t="s">
         <v>43</v>
       </c>
     </row>
@@ -3506,7 +4112,7 @@
         <v>25</v>
       </c>
       <c r="E16" s="59"/>
-      <c r="F16" s="109" t="s">
+      <c r="F16" s="76" t="s">
         <v>6</v>
       </c>
       <c r="G16" s="62"/>
@@ -3525,7 +4131,7 @@
         <v>30</v>
       </c>
       <c r="E17" s="59"/>
-      <c r="F17" s="109" t="s">
+      <c r="F17" s="76" t="s">
         <v>8</v>
       </c>
       <c r="G17" s="62"/>
@@ -3544,7 +4150,7 @@
         <v>45</v>
       </c>
       <c r="E18" s="59"/>
-      <c r="F18" s="109" t="s">
+      <c r="F18" s="76" t="s">
         <v>10</v>
       </c>
       <c r="G18" s="62"/>
@@ -3564,7 +4170,7 @@
       </c>
       <c r="E19" s="59"/>
       <c r="F19" s="59"/>
-      <c r="G19" s="98"/>
+      <c r="G19" s="68"/>
     </row>
     <row r="20" spans="1:7" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="61" t="s">
@@ -3580,11 +4186,14 @@
         <v>50</v>
       </c>
       <c r="E20" s="63"/>
-      <c r="F20" s="100"/>
-      <c r="G20" s="101"/>
+      <c r="F20" s="70"/>
+      <c r="G20" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="F3:G3"/>
     <mergeCell ref="I8:N8"/>
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="F9:G10"/>
@@ -3593,10 +4202,1729 @@
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="F8:G8"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="F3:G3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1602ACBA-3598-49C3-B1EA-05E1FB6B8EBD}">
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="16384" width="8.88671875" style="65"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="130" t="s">
+        <v>125</v>
+      </c>
+      <c r="B1" s="126" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="126" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="126" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1" s="126" t="s">
+        <v>128</v>
+      </c>
+      <c r="F1" s="126" t="s">
+        <v>19</v>
+      </c>
+      <c r="G1" s="131"/>
+      <c r="I1" s="126" t="s">
+        <v>129</v>
+      </c>
+      <c r="J1" s="126" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="132">
+        <v>45662</v>
+      </c>
+      <c r="B2" s="65" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="65" t="s">
+        <v>131</v>
+      </c>
+      <c r="D2" s="65">
+        <v>850</v>
+      </c>
+      <c r="E2" s="65" t="s">
+        <v>132</v>
+      </c>
+      <c r="F2" s="65" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="65" t="s">
+        <v>133</v>
+      </c>
+      <c r="J2" s="65" t="s">
+        <v>134</v>
+      </c>
+      <c r="K2" s="65">
+        <f>SUMIF(C2:C11,"Travel",D2:D11)</f>
+        <v>1800</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" s="132">
+        <v>45665</v>
+      </c>
+      <c r="B3" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="65" t="s">
+        <v>135</v>
+      </c>
+      <c r="D3" s="65">
+        <v>1200</v>
+      </c>
+      <c r="E3" s="65" t="s">
+        <v>136</v>
+      </c>
+      <c r="F3" s="65" t="s">
+        <v>29</v>
+      </c>
+      <c r="I3" s="65" t="s">
+        <v>137</v>
+      </c>
+      <c r="J3" s="65" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A4" s="132">
+        <v>45672</v>
+      </c>
+      <c r="B4" s="65" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="65" t="s">
+        <v>139</v>
+      </c>
+      <c r="D4" s="65">
+        <v>5000</v>
+      </c>
+      <c r="E4" s="65" t="s">
+        <v>136</v>
+      </c>
+      <c r="F4" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="I4" s="65" t="s">
+        <v>140</v>
+      </c>
+      <c r="J4" s="65" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A5" s="132">
+        <v>45677</v>
+      </c>
+      <c r="B5" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="65" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="65">
+        <v>300</v>
+      </c>
+      <c r="E5" s="65" t="s">
+        <v>132</v>
+      </c>
+      <c r="F5" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="I5" s="65" t="s">
+        <v>142</v>
+      </c>
+      <c r="J5" s="65" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="132">
+        <v>45685</v>
+      </c>
+      <c r="B6" s="65" t="s">
+        <v>144</v>
+      </c>
+      <c r="C6" s="65" t="s">
+        <v>145</v>
+      </c>
+      <c r="D6" s="65">
+        <v>700</v>
+      </c>
+      <c r="E6" s="65" t="s">
+        <v>146</v>
+      </c>
+      <c r="F6" s="65" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="65" t="s">
+        <v>147</v>
+      </c>
+      <c r="J6" s="65" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A7" s="132">
+        <v>45692</v>
+      </c>
+      <c r="B7" s="65" t="s">
+        <v>2</v>
+      </c>
+      <c r="C7" s="65" t="s">
+        <v>139</v>
+      </c>
+      <c r="D7" s="65">
+        <v>4800</v>
+      </c>
+      <c r="E7" s="65" t="s">
+        <v>136</v>
+      </c>
+      <c r="F7" s="65" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" s="65" t="s">
+        <v>149</v>
+      </c>
+      <c r="J7" s="65" t="s">
+        <v>150</v>
+      </c>
+      <c r="K7" s="65">
+        <f>SUMIFS(D2:D11,C2:C11,"Software",A2:A11,"&gt;=1/1/2025",A2:A11,"&lt;=12/31/2025")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A8" s="132">
+        <v>45698</v>
+      </c>
+      <c r="B8" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" s="65" t="s">
+        <v>131</v>
+      </c>
+      <c r="D8" s="65">
+        <v>950</v>
+      </c>
+      <c r="E8" s="65" t="s">
+        <v>132</v>
+      </c>
+      <c r="F8" s="65" t="s">
+        <v>29</v>
+      </c>
+      <c r="I8" s="65" t="s">
+        <v>151</v>
+      </c>
+      <c r="J8" s="65" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A9" s="132">
+        <v>45706</v>
+      </c>
+      <c r="B9" s="65" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="65" t="s">
+        <v>27</v>
+      </c>
+      <c r="D9" s="65">
+        <v>400</v>
+      </c>
+      <c r="E9" s="65" t="s">
+        <v>132</v>
+      </c>
+      <c r="F9" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="I9" s="65" t="s">
+        <v>153</v>
+      </c>
+      <c r="J9" s="65" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A10" s="132">
+        <v>45711</v>
+      </c>
+      <c r="B10" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="65" t="s">
+        <v>135</v>
+      </c>
+      <c r="D10" s="65">
+        <v>2500</v>
+      </c>
+      <c r="E10" s="65" t="s">
+        <v>136</v>
+      </c>
+      <c r="F10" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="I10" s="65" t="s">
+        <v>155</v>
+      </c>
+      <c r="J10" s="65" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="132">
+        <v>45715</v>
+      </c>
+      <c r="B11" s="65" t="s">
+        <v>144</v>
+      </c>
+      <c r="C11" s="65" t="s">
+        <v>145</v>
+      </c>
+      <c r="D11" s="65">
+        <v>750</v>
+      </c>
+      <c r="E11" s="65" t="s">
+        <v>136</v>
+      </c>
+      <c r="F11" s="65" t="s">
+        <v>26</v>
+      </c>
+      <c r="I11" s="65" t="s">
+        <v>157</v>
+      </c>
+      <c r="J11" s="65" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A12" s="132"/>
+      <c r="I12" s="65" t="s">
+        <v>159</v>
+      </c>
+      <c r="J12" s="65" t="s">
+        <v>160</v>
+      </c>
+      <c r="K12" s="65">
+        <f>SUMIFS(D2:D11,F2:F11,"East",A2:A11,"&gt;=1/1/2025",A2:A11,"&lt;=12/31/2025")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A13" s="132"/>
+      <c r="I13" s="65" t="s">
+        <v>161</v>
+      </c>
+      <c r="J13" s="65" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A14" s="132"/>
+      <c r="I14" s="65" t="s">
+        <v>163</v>
+      </c>
+      <c r="J14" s="65" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A15" s="132"/>
+      <c r="I15" s="65" t="s">
+        <v>165</v>
+      </c>
+      <c r="J15" s="65" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A16" s="132"/>
+      <c r="I16" s="65" t="s">
+        <v>167</v>
+      </c>
+      <c r="J16" s="65" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="132"/>
+      <c r="I17" s="65" t="s">
+        <v>169</v>
+      </c>
+      <c r="J17" s="65" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="132"/>
+      <c r="I18" s="65" t="s">
+        <v>171</v>
+      </c>
+      <c r="J18" s="65" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" s="132"/>
+      <c r="I19" s="65" t="s">
+        <v>173</v>
+      </c>
+      <c r="J19" s="65" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="132"/>
+      <c r="I20" s="65" t="s">
+        <v>175</v>
+      </c>
+      <c r="J20" s="65" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="132"/>
+      <c r="I21" s="65" t="s">
+        <v>177</v>
+      </c>
+      <c r="J21" s="65" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="133" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" s="132"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" s="132"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" s="132"/>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A22" r:id="rId1" xr:uid="{2357E178-5FEB-448D-8918-3927F291C1AE}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E468253-D8BB-4FA6-816D-27ABA8930A6D}">
+  <dimension ref="A1:J24"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="9.109375" style="65" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.77734375" style="65" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="7.88671875" style="65" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" style="65" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="8.88671875" style="65"/>
+    <col min="9" max="9" width="63.109375" style="65" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.88671875" style="65" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="65"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="129" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="129" t="s">
+        <v>223</v>
+      </c>
+      <c r="B1" s="129" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="129" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="129" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1" s="129" t="s">
+        <v>222</v>
+      </c>
+      <c r="I1" s="129" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="65" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="65" t="s">
+        <v>193</v>
+      </c>
+      <c r="D2" s="65">
+        <v>500</v>
+      </c>
+      <c r="E2" s="65" t="s">
+        <v>220</v>
+      </c>
+      <c r="I2" s="129" t="s">
+        <v>219</v>
+      </c>
+      <c r="J2" s="129" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="65" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="65" t="s">
+        <v>197</v>
+      </c>
+      <c r="D3" s="65">
+        <v>700</v>
+      </c>
+      <c r="E3" s="65" t="s">
+        <v>217</v>
+      </c>
+      <c r="I3" s="65" t="s">
+        <v>216</v>
+      </c>
+      <c r="J3" s="65">
+        <f>COUNTIF(C2:C11,"Overdue")</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="65" t="s">
+        <v>215</v>
+      </c>
+      <c r="B4" s="65" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="65" t="s">
+        <v>193</v>
+      </c>
+      <c r="D4" s="65">
+        <v>300</v>
+      </c>
+      <c r="E4" s="65" t="s">
+        <v>214</v>
+      </c>
+      <c r="I4" s="65" t="s">
+        <v>213</v>
+      </c>
+      <c r="J4" s="65">
+        <f>COUNTIF(C2:C11,"Paid")</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="65" t="s">
+        <v>212</v>
+      </c>
+      <c r="B5" s="65" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="65" t="s">
+        <v>197</v>
+      </c>
+      <c r="D5" s="65">
+        <v>400</v>
+      </c>
+      <c r="E5" s="65" t="s">
+        <v>211</v>
+      </c>
+      <c r="I5" s="65" t="s">
+        <v>210</v>
+      </c>
+      <c r="J5" s="65">
+        <f>COUNTIF(B2:B11,"North")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="65" t="s">
+        <v>209</v>
+      </c>
+      <c r="B6" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="65" t="s">
+        <v>193</v>
+      </c>
+      <c r="D6" s="65">
+        <v>600</v>
+      </c>
+      <c r="E6" s="65" t="s">
+        <v>208</v>
+      </c>
+      <c r="I6" s="65" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="65" t="s">
+        <v>206</v>
+      </c>
+      <c r="B7" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="65" t="s">
+        <v>197</v>
+      </c>
+      <c r="D7" s="65">
+        <v>450</v>
+      </c>
+      <c r="E7" s="65" t="s">
+        <v>205</v>
+      </c>
+      <c r="I7" s="65" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="65" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="65" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="65" t="s">
+        <v>197</v>
+      </c>
+      <c r="D8" s="65">
+        <v>550</v>
+      </c>
+      <c r="E8" s="65" t="s">
+        <v>203</v>
+      </c>
+      <c r="I8" s="65" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="65" t="s">
+        <v>201</v>
+      </c>
+      <c r="B9" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="65" t="s">
+        <v>193</v>
+      </c>
+      <c r="D9" s="65">
+        <v>200</v>
+      </c>
+      <c r="E9" s="65" t="s">
+        <v>200</v>
+      </c>
+      <c r="I9" s="65" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="65" t="s">
+        <v>198</v>
+      </c>
+      <c r="B10" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="65" t="s">
+        <v>197</v>
+      </c>
+      <c r="D10" s="65">
+        <v>350</v>
+      </c>
+      <c r="E10" s="65" t="s">
+        <v>196</v>
+      </c>
+      <c r="I10" s="65" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="65" t="s">
+        <v>194</v>
+      </c>
+      <c r="B11" s="65" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="65" t="s">
+        <v>193</v>
+      </c>
+      <c r="D11" s="65">
+        <v>800</v>
+      </c>
+      <c r="E11" s="65" t="s">
+        <v>192</v>
+      </c>
+      <c r="I11" s="65" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I12" s="65" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I13" s="65" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I14" s="65" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I15" s="65" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I16" s="65" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I17" s="65" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I18" s="65" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I19" s="65" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I20" s="65" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I21" s="65" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I22" s="65" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="127" t="s">
+        <v>224</v>
+      </c>
+      <c r="B24" s="128"/>
+      <c r="C24" s="128"/>
+      <c r="D24" s="128"/>
+      <c r="E24" s="128"/>
+      <c r="F24" s="128"/>
+      <c r="G24" s="128"/>
+      <c r="H24" s="128"/>
+      <c r="I24" s="128"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A24:I24"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A24" r:id="rId1" xr:uid="{90728C1F-923A-461E-9979-2A463338B88E}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{116B6492-7E8B-47E0-8222-5EB871C51B32}">
+  <dimension ref="A1:J25"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="6.109375" style="65" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" style="65" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" style="65" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" style="65" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.109375" style="65" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7.44140625" style="65" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="8.77734375" style="65"/>
+    <col min="9" max="9" width="61.33203125" style="65" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.33203125" style="65" customWidth="1"/>
+    <col min="11" max="16384" width="8.77734375" style="65"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="126" t="s">
+        <v>225</v>
+      </c>
+      <c r="B1" s="126" t="s">
+        <v>226</v>
+      </c>
+      <c r="C1" s="126" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="126" t="s">
+        <v>227</v>
+      </c>
+      <c r="E1" s="126" t="s">
+        <v>228</v>
+      </c>
+      <c r="F1" s="126" t="s">
+        <v>229</v>
+      </c>
+      <c r="I1" s="126" t="s">
+        <v>219</v>
+      </c>
+      <c r="J1" s="126" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="65">
+        <v>101</v>
+      </c>
+      <c r="B2" s="65" t="s">
+        <v>231</v>
+      </c>
+      <c r="C2" s="65" t="s">
+        <v>232</v>
+      </c>
+      <c r="D2" s="65" t="s">
+        <v>233</v>
+      </c>
+      <c r="E2" s="65">
+        <v>65000</v>
+      </c>
+      <c r="F2" s="65">
+        <v>0.1</v>
+      </c>
+      <c r="I2" s="65" t="s">
+        <v>234</v>
+      </c>
+      <c r="J2" s="65" t="str">
+        <f>VLOOKUP(104,A1:F11,2)</f>
+        <v>David Chen</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="65">
+        <v>102</v>
+      </c>
+      <c r="B3" s="65" t="s">
+        <v>235</v>
+      </c>
+      <c r="C3" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="D3" s="65" t="s">
+        <v>236</v>
+      </c>
+      <c r="E3" s="65">
+        <v>72000</v>
+      </c>
+      <c r="F3" s="65">
+        <v>0.12</v>
+      </c>
+      <c r="I3" s="65" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" s="65">
+        <v>103</v>
+      </c>
+      <c r="B4" s="65" t="s">
+        <v>238</v>
+      </c>
+      <c r="C4" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="65" t="s">
+        <v>239</v>
+      </c>
+      <c r="E4" s="65">
+        <v>80000</v>
+      </c>
+      <c r="F4" s="65">
+        <v>0.08</v>
+      </c>
+      <c r="I4" s="65" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" s="65">
+        <v>104</v>
+      </c>
+      <c r="B5" s="65" t="s">
+        <v>241</v>
+      </c>
+      <c r="C5" s="65" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="65" t="s">
+        <v>233</v>
+      </c>
+      <c r="E5" s="65">
+        <v>58000</v>
+      </c>
+      <c r="F5" s="65">
+        <v>0.09</v>
+      </c>
+      <c r="I5" s="65" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" s="65">
+        <v>105</v>
+      </c>
+      <c r="B6" s="65" t="s">
+        <v>243</v>
+      </c>
+      <c r="C6" s="65" t="s">
+        <v>232</v>
+      </c>
+      <c r="D6" s="65" t="s">
+        <v>236</v>
+      </c>
+      <c r="E6" s="65">
+        <v>62000</v>
+      </c>
+      <c r="F6" s="65">
+        <v>0.11</v>
+      </c>
+      <c r="I6" s="65" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" s="65">
+        <v>106</v>
+      </c>
+      <c r="B7" s="65" t="s">
+        <v>245</v>
+      </c>
+      <c r="C7" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="65" t="s">
+        <v>246</v>
+      </c>
+      <c r="E7" s="65">
+        <v>76000</v>
+      </c>
+      <c r="F7" s="65">
+        <v>0.1</v>
+      </c>
+      <c r="I7" s="65" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" s="65">
+        <v>107</v>
+      </c>
+      <c r="B8" s="65" t="s">
+        <v>248</v>
+      </c>
+      <c r="C8" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" s="65" t="s">
+        <v>239</v>
+      </c>
+      <c r="E8" s="65">
+        <v>82000</v>
+      </c>
+      <c r="F8" s="65">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I8" s="65" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" s="65">
+        <v>108</v>
+      </c>
+      <c r="B9" s="65" t="s">
+        <v>250</v>
+      </c>
+      <c r="C9" s="65" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="65" t="s">
+        <v>236</v>
+      </c>
+      <c r="E9" s="65">
+        <v>55000</v>
+      </c>
+      <c r="F9" s="65">
+        <v>0.09</v>
+      </c>
+      <c r="I9" s="65" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="65">
+        <v>109</v>
+      </c>
+      <c r="B10" s="65" t="s">
+        <v>252</v>
+      </c>
+      <c r="C10" s="65" t="s">
+        <v>232</v>
+      </c>
+      <c r="D10" s="65" t="s">
+        <v>246</v>
+      </c>
+      <c r="E10" s="65">
+        <v>68000</v>
+      </c>
+      <c r="F10" s="65">
+        <v>0.1</v>
+      </c>
+      <c r="I10" s="65" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" s="65">
+        <v>110</v>
+      </c>
+      <c r="B11" s="65" t="s">
+        <v>254</v>
+      </c>
+      <c r="C11" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="65" t="s">
+        <v>233</v>
+      </c>
+      <c r="E11" s="65">
+        <v>85000</v>
+      </c>
+      <c r="F11" s="65">
+        <v>0.12</v>
+      </c>
+      <c r="I11" s="65" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I12" s="65" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I13" s="65" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I14" s="65" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I15" s="65" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="I16" s="65" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I17" s="65" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I18" s="65" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I19" s="65" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I20" s="65" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="I21" s="65" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="127" t="s">
+        <v>266</v>
+      </c>
+      <c r="B25" s="128"/>
+      <c r="C25" s="128"/>
+      <c r="D25" s="128"/>
+      <c r="E25" s="128"/>
+      <c r="F25" s="128"/>
+      <c r="G25" s="128"/>
+      <c r="H25" s="128"/>
+      <c r="I25" s="128"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A25:I25"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A25" r:id="rId1" xr:uid="{DA744765-1E4A-472E-93B9-8433C0065260}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F9F5792-D527-4DAE-8F40-0C8A70D97254}">
+  <dimension ref="A1:N24"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19.88671875" style="65" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.6640625" style="65" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9" style="65" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="9.6640625" style="65" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.77734375" style="65" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="65" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.88671875" style="65" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.44140625" style="65" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.33203125" style="65" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.21875" style="65" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="2" style="65" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="56.21875" style="65" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="37.109375" style="65" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.88671875" style="65"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="126" t="s">
+        <v>267</v>
+      </c>
+      <c r="B1" s="126" t="s">
+        <v>268</v>
+      </c>
+      <c r="C1" s="126" t="s">
+        <v>269</v>
+      </c>
+      <c r="D1" s="126" t="s">
+        <v>270</v>
+      </c>
+      <c r="E1" s="126" t="s">
+        <v>271</v>
+      </c>
+      <c r="F1" s="126" t="s">
+        <v>272</v>
+      </c>
+      <c r="G1" s="126" t="s">
+        <v>273</v>
+      </c>
+      <c r="H1" s="126" t="s">
+        <v>274</v>
+      </c>
+      <c r="I1" s="126" t="s">
+        <v>275</v>
+      </c>
+      <c r="J1" s="126" t="s">
+        <v>276</v>
+      </c>
+      <c r="K1" s="126" t="s">
+        <v>277</v>
+      </c>
+      <c r="L1" s="126">
+        <v>0</v>
+      </c>
+      <c r="M1" s="126" t="s">
+        <v>219</v>
+      </c>
+      <c r="N1" s="126" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="65" t="s">
+        <v>225</v>
+      </c>
+      <c r="B2" s="65">
+        <v>101</v>
+      </c>
+      <c r="C2" s="65">
+        <v>102</v>
+      </c>
+      <c r="D2" s="65">
+        <v>103</v>
+      </c>
+      <c r="E2" s="65">
+        <v>104</v>
+      </c>
+      <c r="F2" s="65">
+        <v>105</v>
+      </c>
+      <c r="G2" s="65">
+        <v>106</v>
+      </c>
+      <c r="H2" s="65">
+        <v>107</v>
+      </c>
+      <c r="I2" s="65">
+        <v>108</v>
+      </c>
+      <c r="J2" s="65">
+        <v>109</v>
+      </c>
+      <c r="K2" s="65">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="65" t="s">
+        <v>226</v>
+      </c>
+      <c r="B3" s="65" t="s">
+        <v>231</v>
+      </c>
+      <c r="C3" s="65" t="s">
+        <v>235</v>
+      </c>
+      <c r="D3" s="65" t="s">
+        <v>238</v>
+      </c>
+      <c r="E3" s="65" t="s">
+        <v>241</v>
+      </c>
+      <c r="F3" s="65" t="s">
+        <v>243</v>
+      </c>
+      <c r="G3" s="65" t="s">
+        <v>245</v>
+      </c>
+      <c r="H3" s="65" t="s">
+        <v>248</v>
+      </c>
+      <c r="I3" s="65" t="s">
+        <v>250</v>
+      </c>
+      <c r="J3" s="65" t="s">
+        <v>252</v>
+      </c>
+      <c r="K3" s="65" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="65" t="s">
+        <v>42</v>
+      </c>
+      <c r="B4" s="65" t="s">
+        <v>232</v>
+      </c>
+      <c r="C4" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="E4" s="65" t="s">
+        <v>45</v>
+      </c>
+      <c r="F4" s="65" t="s">
+        <v>232</v>
+      </c>
+      <c r="G4" s="65" t="s">
+        <v>44</v>
+      </c>
+      <c r="H4" s="65" t="s">
+        <v>46</v>
+      </c>
+      <c r="I4" s="65" t="s">
+        <v>45</v>
+      </c>
+      <c r="J4" s="65" t="s">
+        <v>232</v>
+      </c>
+      <c r="K4" s="65" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" s="65" t="s">
+        <v>227</v>
+      </c>
+      <c r="B5" s="65" t="s">
+        <v>233</v>
+      </c>
+      <c r="C5" s="65" t="s">
+        <v>236</v>
+      </c>
+      <c r="D5" s="65" t="s">
+        <v>239</v>
+      </c>
+      <c r="E5" s="65" t="s">
+        <v>233</v>
+      </c>
+      <c r="F5" s="65" t="s">
+        <v>236</v>
+      </c>
+      <c r="G5" s="65" t="s">
+        <v>246</v>
+      </c>
+      <c r="H5" s="65" t="s">
+        <v>239</v>
+      </c>
+      <c r="I5" s="65" t="s">
+        <v>236</v>
+      </c>
+      <c r="J5" s="65" t="s">
+        <v>246</v>
+      </c>
+      <c r="K5" s="65" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="65" t="s">
+        <v>228</v>
+      </c>
+      <c r="B6" s="65">
+        <v>65000</v>
+      </c>
+      <c r="C6" s="65">
+        <v>72000</v>
+      </c>
+      <c r="D6" s="65">
+        <v>80000</v>
+      </c>
+      <c r="E6" s="65">
+        <v>58000</v>
+      </c>
+      <c r="F6" s="65">
+        <v>62000</v>
+      </c>
+      <c r="G6" s="65">
+        <v>76000</v>
+      </c>
+      <c r="H6" s="65">
+        <v>82000</v>
+      </c>
+      <c r="I6" s="65">
+        <v>55000</v>
+      </c>
+      <c r="J6" s="65">
+        <v>68000</v>
+      </c>
+      <c r="K6" s="65">
+        <v>85000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A7" s="65" t="s">
+        <v>229</v>
+      </c>
+      <c r="B7" s="65">
+        <v>0.1</v>
+      </c>
+      <c r="C7" s="65">
+        <v>0.12</v>
+      </c>
+      <c r="D7" s="65">
+        <v>0.08</v>
+      </c>
+      <c r="E7" s="65">
+        <v>0.09</v>
+      </c>
+      <c r="F7" s="65">
+        <v>0.11</v>
+      </c>
+      <c r="G7" s="65">
+        <v>0.1</v>
+      </c>
+      <c r="H7" s="65">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I7" s="65">
+        <v>0.09</v>
+      </c>
+      <c r="J7" s="65">
+        <v>0.1</v>
+      </c>
+      <c r="K7" s="65">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M9" s="65" t="s">
+        <v>278</v>
+      </c>
+      <c r="N9" s="65" t="str">
+        <f>HLOOKUP(104, B2:K6, 2, FALSE)</f>
+        <v>David Chen</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M10" s="65" t="s">
+        <v>279</v>
+      </c>
+      <c r="N10" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M11" s="65" t="s">
+        <v>280</v>
+      </c>
+      <c r="N11" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M12" s="65" t="s">
+        <v>281</v>
+      </c>
+      <c r="N12" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M13" s="65" t="s">
+        <v>282</v>
+      </c>
+      <c r="N13" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M14" s="65" t="s">
+        <v>283</v>
+      </c>
+      <c r="N14" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M15" s="65" t="s">
+        <v>284</v>
+      </c>
+      <c r="N15" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M16" s="65" t="s">
+        <v>285</v>
+      </c>
+      <c r="N16" s="65" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M17" s="65" t="s">
+        <v>287</v>
+      </c>
+      <c r="N17" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M18" s="65" t="s">
+        <v>288</v>
+      </c>
+      <c r="N18" s="65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A24" s="127" t="s">
+        <v>289</v>
+      </c>
+      <c r="B24" s="128"/>
+      <c r="C24" s="128"/>
+      <c r="D24" s="128"/>
+      <c r="E24" s="128"/>
+      <c r="F24" s="128"/>
+      <c r="G24" s="128"/>
+      <c r="H24" s="128"/>
+      <c r="I24" s="128"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A24:I24"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A24" r:id="rId1" xr:uid="{9C1324F4-AF41-44EA-9993-7DB6909778ED}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B5A70E6-D93D-44C4-88D6-4B03C3177468}">
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="39.21875" style="65" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" style="65" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.77734375" style="65" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.44140625" style="65" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5" style="65" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="65"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="129" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="129" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1" s="129" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1" s="129" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="129" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="129" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="65">
+        <v>101</v>
+      </c>
+      <c r="B2" s="65" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="65" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="65">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="65">
+        <v>102</v>
+      </c>
+      <c r="B3" s="65" t="s">
+        <v>290</v>
+      </c>
+      <c r="C3" s="65" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="65">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="65">
+        <v>103</v>
+      </c>
+      <c r="B4" s="65" t="s">
+        <v>291</v>
+      </c>
+      <c r="C4" s="65" t="s">
+        <v>292</v>
+      </c>
+      <c r="D4" s="65" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="65">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="65">
+        <v>104</v>
+      </c>
+      <c r="B5" s="65" t="s">
+        <v>293</v>
+      </c>
+      <c r="C5" s="65" t="s">
+        <v>292</v>
+      </c>
+      <c r="D5" s="65" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="65">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="65">
+        <v>105</v>
+      </c>
+      <c r="B6" s="65" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6" s="65" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="65">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="129" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="129" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" s="129" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="129" t="s">
+        <v>219</v>
+      </c>
+      <c r="B9" s="129" t="s">
+        <v>218</v>
+      </c>
+      <c r="C9" s="129" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="65" t="s">
+        <v>295</v>
+      </c>
+      <c r="B10" s="65">
+        <f>INDEX(E2:E6, MATCH("Phone", B2:B6, 0))</f>
+        <v>3000</v>
+      </c>
+      <c r="C10" s="65">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="65" t="s">
+        <v>296</v>
+      </c>
+      <c r="B11" s="65" t="str">
+        <f>INDEX(D2:D6, MATCH(104, A2:A6, 0))</f>
+        <v>West</v>
+      </c>
+      <c r="C11" s="65" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="65" t="s">
+        <v>297</v>
+      </c>
+      <c r="C12" s="65" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="65" t="s">
+        <v>298</v>
+      </c>
+      <c r="C13" s="65">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="65" t="s">
+        <v>299</v>
+      </c>
+      <c r="C14" s="65" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="65" t="s">
+        <v>300</v>
+      </c>
+      <c r="C15" s="65" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="65" t="s">
+        <v>301</v>
+      </c>
+      <c r="C16" s="65">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="65" t="s">
+        <v>302</v>
+      </c>
+      <c r="C17" s="65" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="65" t="s">
+        <v>303</v>
+      </c>
+      <c r="C18" s="65" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="65" t="s">
+        <v>304</v>
+      </c>
+      <c r="C19" s="65" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="127" t="s">
+        <v>305</v>
+      </c>
+      <c r="B23" s="128"/>
+      <c r="C23" s="128"/>
+      <c r="D23" s="128"/>
+      <c r="E23" s="128"/>
+      <c r="F23" s="128"/>
+      <c r="G23" s="128"/>
+      <c r="H23" s="128"/>
+      <c r="I23" s="128"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A23:I23"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A23" r:id="rId1" xr:uid="{84AAEC77-B9FF-440B-B977-DC74327C06C7}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Practice_file.xlsx
+++ b/Practice_file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d58d4d655bee1e81/Desktop/Github/Practice_Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="204" documentId="11_F25DC773A252ABDACC1048BD89DC52D45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F3C7770-62F2-4343-B1FB-37879EF43E67}"/>
+  <xr:revisionPtr revIDLastSave="210" documentId="11_F25DC773A252ABDACC1048BD89DC52D45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4300A19-707D-4C0E-B913-3F4EA55A2F48}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SUMIF,AVGIF" sheetId="1" r:id="rId1"/>
@@ -1644,128 +1644,8 @@
     <xf numFmtId="0" fontId="9" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1776,6 +1656,126 @@
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2072,14 +2072,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="11" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="88" t="s">
+      <c r="A1" s="94" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="88"/>
-      <c r="E1" s="88"/>
-      <c r="F1" s="88"/>
+      <c r="B1" s="94"/>
+      <c r="C1" s="94"/>
+      <c r="D1" s="94"/>
+      <c r="E1" s="94"/>
+      <c r="F1" s="94"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
@@ -2241,17 +2241,17 @@
       <c r="F12" s="18"/>
     </row>
     <row r="15" spans="1:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="88" t="s">
+      <c r="A15" s="94" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="88"/>
-      <c r="C15" s="88"/>
-      <c r="D15" s="88"/>
-      <c r="E15" s="88"/>
-      <c r="F15" s="88"/>
-      <c r="G15" s="88"/>
-      <c r="H15" s="88"/>
-      <c r="I15" s="88"/>
+      <c r="B15" s="94"/>
+      <c r="C15" s="94"/>
+      <c r="D15" s="94"/>
+      <c r="E15" s="94"/>
+      <c r="F15" s="94"/>
+      <c r="G15" s="94"/>
+      <c r="H15" s="94"/>
+      <c r="I15" s="94"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
@@ -2524,15 +2524,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="90" t="s">
+      <c r="A1" s="106" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
-      <c r="G1" s="92"/>
+      <c r="B1" s="107"/>
+      <c r="C1" s="107"/>
+      <c r="D1" s="107"/>
+      <c r="E1" s="107"/>
+      <c r="F1" s="107"/>
+      <c r="G1" s="108"/>
       <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2773,15 +2773,15 @@
     </row>
     <row r="15" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="16" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="90" t="s">
+      <c r="A16" s="106" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="91"/>
-      <c r="C16" s="91"/>
-      <c r="D16" s="91"/>
-      <c r="E16" s="91"/>
-      <c r="F16" s="102"/>
-      <c r="G16" s="102"/>
+      <c r="B16" s="107"/>
+      <c r="C16" s="107"/>
+      <c r="D16" s="107"/>
+      <c r="E16" s="107"/>
+      <c r="F16" s="118"/>
+      <c r="G16" s="118"/>
     </row>
     <row r="17" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="24" t="s">
@@ -2829,10 +2829,10 @@
         <f>COUNTIF(B18:B27,"&gt;30")</f>
         <v>6</v>
       </c>
-      <c r="H18" s="103" t="s">
+      <c r="H18" s="100" t="s">
         <v>70</v>
       </c>
-      <c r="I18" s="104"/>
+      <c r="I18" s="101"/>
     </row>
     <row r="19" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="29" t="s">
@@ -2857,10 +2857,10 @@
         <f>COUNTIF(E18:E27,"Male")</f>
         <v>5</v>
       </c>
-      <c r="H19" s="103" t="s">
+      <c r="H19" s="100" t="s">
         <v>71</v>
       </c>
-      <c r="I19" s="104"/>
+      <c r="I19" s="101"/>
     </row>
     <row r="20" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="29" t="s">
@@ -3016,16 +3016,16 @@
     </row>
     <row r="30" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="31" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="93" t="s">
+      <c r="A31" s="109" t="s">
         <v>60</v>
       </c>
-      <c r="B31" s="94"/>
-      <c r="C31" s="94"/>
-      <c r="D31" s="94"/>
-      <c r="E31" s="94"/>
-      <c r="F31" s="94"/>
-      <c r="G31" s="94"/>
-      <c r="H31" s="95"/>
+      <c r="B31" s="110"/>
+      <c r="C31" s="110"/>
+      <c r="D31" s="110"/>
+      <c r="E31" s="110"/>
+      <c r="F31" s="110"/>
+      <c r="G31" s="110"/>
+      <c r="H31" s="111"/>
     </row>
     <row r="32" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="39" t="s">
@@ -3041,9 +3041,9 @@
         <v>62</v>
       </c>
       <c r="E32" s="40"/>
-      <c r="F32" s="105"/>
-      <c r="G32" s="106"/>
-      <c r="H32" s="107"/>
+      <c r="F32" s="102"/>
+      <c r="G32" s="103"/>
+      <c r="H32" s="104"/>
     </row>
     <row r="33" spans="1:10" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="29" t="s">
@@ -3062,15 +3062,15 @@
         <f>COUNTIF(D33:D51,"Pending")</f>
         <v>7</v>
       </c>
-      <c r="F33" s="96" t="s">
+      <c r="F33" s="112" t="s">
         <v>69</v>
       </c>
-      <c r="G33" s="97"/>
-      <c r="H33" s="98"/>
-      <c r="I33" s="108" t="s">
+      <c r="G33" s="113"/>
+      <c r="H33" s="114"/>
+      <c r="I33" s="105" t="s">
         <v>72</v>
       </c>
-      <c r="J33" s="104"/>
+      <c r="J33" s="101"/>
     </row>
     <row r="34" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="29" t="s">
@@ -3089,15 +3089,15 @@
         <f>COUNTIFS(B33:B51,"West",D33:D51,"Delivered")</f>
         <v>3</v>
       </c>
-      <c r="F34" s="99" t="s">
+      <c r="F34" s="115" t="s">
         <v>73</v>
       </c>
-      <c r="G34" s="100"/>
-      <c r="H34" s="101"/>
-      <c r="I34" s="111" t="s">
+      <c r="G34" s="116"/>
+      <c r="H34" s="117"/>
+      <c r="I34" s="97" t="s">
         <v>74</v>
       </c>
-      <c r="J34" s="111"/>
+      <c r="J34" s="97"/>
     </row>
     <row r="35" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="29" t="s">
@@ -3113,11 +3113,11 @@
         <v>64</v>
       </c>
       <c r="E35" s="25"/>
-      <c r="F35" s="89"/>
-      <c r="G35" s="89"/>
-      <c r="H35" s="89"/>
-      <c r="I35" s="112"/>
-      <c r="J35" s="111"/>
+      <c r="F35" s="99"/>
+      <c r="G35" s="99"/>
+      <c r="H35" s="99"/>
+      <c r="I35" s="98"/>
+      <c r="J35" s="97"/>
     </row>
     <row r="36" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="29" t="s">
@@ -3133,11 +3133,11 @@
         <v>64</v>
       </c>
       <c r="E36" s="25"/>
-      <c r="F36" s="89"/>
-      <c r="G36" s="89"/>
-      <c r="H36" s="89"/>
-      <c r="I36" s="109"/>
-      <c r="J36" s="110"/>
+      <c r="F36" s="99"/>
+      <c r="G36" s="99"/>
+      <c r="H36" s="99"/>
+      <c r="I36" s="95"/>
+      <c r="J36" s="96"/>
     </row>
     <row r="37" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="29" t="s">
@@ -3153,11 +3153,11 @@
         <v>66</v>
       </c>
       <c r="E37" s="25"/>
-      <c r="F37" s="89"/>
-      <c r="G37" s="89"/>
-      <c r="H37" s="89"/>
-      <c r="I37" s="109"/>
-      <c r="J37" s="110"/>
+      <c r="F37" s="99"/>
+      <c r="G37" s="99"/>
+      <c r="H37" s="99"/>
+      <c r="I37" s="95"/>
+      <c r="J37" s="96"/>
     </row>
     <row r="38" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="29" t="s">
@@ -3173,11 +3173,11 @@
         <v>64</v>
       </c>
       <c r="E38" s="25"/>
-      <c r="F38" s="89"/>
-      <c r="G38" s="89"/>
-      <c r="H38" s="89"/>
-      <c r="I38" s="109"/>
-      <c r="J38" s="110"/>
+      <c r="F38" s="99"/>
+      <c r="G38" s="99"/>
+      <c r="H38" s="99"/>
+      <c r="I38" s="95"/>
+      <c r="J38" s="96"/>
     </row>
     <row r="39" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="29" t="s">
@@ -3193,11 +3193,11 @@
         <v>64</v>
       </c>
       <c r="E39" s="25"/>
-      <c r="F39" s="89"/>
-      <c r="G39" s="89"/>
-      <c r="H39" s="89"/>
-      <c r="I39" s="109"/>
-      <c r="J39" s="110"/>
+      <c r="F39" s="99"/>
+      <c r="G39" s="99"/>
+      <c r="H39" s="99"/>
+      <c r="I39" s="95"/>
+      <c r="J39" s="96"/>
     </row>
     <row r="40" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="29" t="s">
@@ -3213,11 +3213,11 @@
         <v>66</v>
       </c>
       <c r="E40" s="25"/>
-      <c r="F40" s="89"/>
-      <c r="G40" s="89"/>
-      <c r="H40" s="89"/>
-      <c r="I40" s="109"/>
-      <c r="J40" s="110"/>
+      <c r="F40" s="99"/>
+      <c r="G40" s="99"/>
+      <c r="H40" s="99"/>
+      <c r="I40" s="95"/>
+      <c r="J40" s="96"/>
     </row>
     <row r="41" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="29" t="s">
@@ -3233,11 +3233,11 @@
         <v>64</v>
       </c>
       <c r="E41" s="25"/>
-      <c r="F41" s="89"/>
-      <c r="G41" s="89"/>
-      <c r="H41" s="89"/>
-      <c r="I41" s="109"/>
-      <c r="J41" s="110"/>
+      <c r="F41" s="99"/>
+      <c r="G41" s="99"/>
+      <c r="H41" s="99"/>
+      <c r="I41" s="95"/>
+      <c r="J41" s="96"/>
     </row>
     <row r="42" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="29" t="s">
@@ -3253,11 +3253,11 @@
         <v>66</v>
       </c>
       <c r="E42" s="25"/>
-      <c r="F42" s="89"/>
-      <c r="G42" s="89"/>
-      <c r="H42" s="89"/>
-      <c r="I42" s="109"/>
-      <c r="J42" s="110"/>
+      <c r="F42" s="99"/>
+      <c r="G42" s="99"/>
+      <c r="H42" s="99"/>
+      <c r="I42" s="95"/>
+      <c r="J42" s="96"/>
     </row>
     <row r="43" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="29" t="s">
@@ -3273,11 +3273,11 @@
         <v>64</v>
       </c>
       <c r="E43" s="25"/>
-      <c r="F43" s="89"/>
-      <c r="G43" s="89"/>
-      <c r="H43" s="89"/>
-      <c r="I43" s="109"/>
-      <c r="J43" s="110"/>
+      <c r="F43" s="99"/>
+      <c r="G43" s="99"/>
+      <c r="H43" s="99"/>
+      <c r="I43" s="95"/>
+      <c r="J43" s="96"/>
     </row>
     <row r="44" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="29" t="s">
@@ -3293,11 +3293,11 @@
         <v>64</v>
       </c>
       <c r="E44" s="25"/>
-      <c r="F44" s="89"/>
-      <c r="G44" s="89"/>
-      <c r="H44" s="89"/>
-      <c r="I44" s="109"/>
-      <c r="J44" s="110"/>
+      <c r="F44" s="99"/>
+      <c r="G44" s="99"/>
+      <c r="H44" s="99"/>
+      <c r="I44" s="95"/>
+      <c r="J44" s="96"/>
     </row>
     <row r="45" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="29" t="s">
@@ -3313,9 +3313,9 @@
         <v>66</v>
       </c>
       <c r="E45" s="25"/>
-      <c r="F45" s="89"/>
-      <c r="G45" s="89"/>
-      <c r="H45" s="89"/>
+      <c r="F45" s="99"/>
+      <c r="G45" s="99"/>
+      <c r="H45" s="99"/>
     </row>
     <row r="46" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="29" t="s">
@@ -3331,9 +3331,9 @@
         <v>64</v>
       </c>
       <c r="E46" s="25"/>
-      <c r="F46" s="89"/>
-      <c r="G46" s="89"/>
-      <c r="H46" s="89"/>
+      <c r="F46" s="99"/>
+      <c r="G46" s="99"/>
+      <c r="H46" s="99"/>
     </row>
     <row r="47" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="29" t="s">
@@ -3349,9 +3349,9 @@
         <v>66</v>
       </c>
       <c r="E47" s="25"/>
-      <c r="F47" s="89"/>
-      <c r="G47" s="89"/>
-      <c r="H47" s="89"/>
+      <c r="F47" s="99"/>
+      <c r="G47" s="99"/>
+      <c r="H47" s="99"/>
     </row>
     <row r="48" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="29" t="s">
@@ -3367,9 +3367,9 @@
         <v>64</v>
       </c>
       <c r="E48" s="25"/>
-      <c r="F48" s="89"/>
-      <c r="G48" s="89"/>
-      <c r="H48" s="89"/>
+      <c r="F48" s="99"/>
+      <c r="G48" s="99"/>
+      <c r="H48" s="99"/>
     </row>
     <row r="49" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="29" t="s">
@@ -3385,9 +3385,9 @@
         <v>64</v>
       </c>
       <c r="E49" s="25"/>
-      <c r="F49" s="89"/>
-      <c r="G49" s="89"/>
-      <c r="H49" s="89"/>
+      <c r="F49" s="99"/>
+      <c r="G49" s="99"/>
+      <c r="H49" s="99"/>
     </row>
     <row r="50" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="29" t="s">
@@ -3403,9 +3403,9 @@
         <v>66</v>
       </c>
       <c r="E50" s="25"/>
-      <c r="F50" s="89"/>
-      <c r="G50" s="89"/>
-      <c r="H50" s="89"/>
+      <c r="F50" s="99"/>
+      <c r="G50" s="99"/>
+      <c r="H50" s="99"/>
     </row>
     <row r="51" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="29" t="s">
@@ -3421,22 +3421,22 @@
         <v>64</v>
       </c>
       <c r="E51" s="25"/>
-      <c r="F51" s="89"/>
-      <c r="G51" s="89"/>
-      <c r="H51" s="89"/>
+      <c r="F51" s="99"/>
+      <c r="G51" s="99"/>
+      <c r="H51" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="I34:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="A16:G16"/>
     <mergeCell ref="F48:H48"/>
     <mergeCell ref="F49:H49"/>
     <mergeCell ref="F50:H50"/>
@@ -3453,16 +3453,16 @@
     <mergeCell ref="F47:H47"/>
     <mergeCell ref="F36:H36"/>
     <mergeCell ref="F37:H37"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="I34:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3484,14 +3484,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="113" t="s">
+      <c r="A1" s="119" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="114"/>
-      <c r="C1" s="114"/>
-      <c r="D1" s="114"/>
-      <c r="E1" s="114"/>
-      <c r="F1" s="115"/>
+      <c r="B1" s="120"/>
+      <c r="C1" s="120"/>
+      <c r="D1" s="120"/>
+      <c r="E1" s="120"/>
+      <c r="F1" s="121"/>
     </row>
     <row r="2" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="58" t="s">
@@ -3548,20 +3548,20 @@
       <c r="G4" s="65" t="s">
         <v>84</v>
       </c>
-      <c r="H4" s="116" t="s">
+      <c r="H4" s="122" t="s">
         <v>89</v>
       </c>
-      <c r="I4" s="116"/>
-      <c r="J4" s="116"/>
-      <c r="K4" s="116"/>
-      <c r="L4" s="116"/>
-      <c r="M4" s="116"/>
-      <c r="N4" s="116"/>
-      <c r="O4" s="116"/>
-      <c r="P4" s="116"/>
-      <c r="Q4" s="116"/>
-      <c r="R4" s="116"/>
-      <c r="S4" s="116"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="122"/>
+      <c r="K4" s="122"/>
+      <c r="L4" s="122"/>
+      <c r="M4" s="122"/>
+      <c r="N4" s="122"/>
+      <c r="O4" s="122"/>
+      <c r="P4" s="122"/>
+      <c r="Q4" s="122"/>
+      <c r="R4" s="122"/>
+      <c r="S4" s="122"/>
     </row>
     <row r="5" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="61" t="s">
@@ -3641,20 +3641,20 @@
       <c r="H10" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="I10" s="116" t="s">
+      <c r="I10" s="122" t="s">
         <v>88</v>
       </c>
-      <c r="J10" s="116"/>
-      <c r="K10" s="116"/>
-      <c r="L10" s="116"/>
-      <c r="M10" s="116"/>
-      <c r="N10" s="116"/>
-      <c r="O10" s="116"/>
-      <c r="P10" s="116"/>
-      <c r="Q10" s="116"/>
-      <c r="R10" s="116"/>
-      <c r="S10" s="116"/>
-      <c r="T10" s="116"/>
+      <c r="J10" s="122"/>
+      <c r="K10" s="122"/>
+      <c r="L10" s="122"/>
+      <c r="M10" s="122"/>
+      <c r="N10" s="122"/>
+      <c r="O10" s="122"/>
+      <c r="P10" s="122"/>
+      <c r="Q10" s="122"/>
+      <c r="R10" s="122"/>
+      <c r="S10" s="122"/>
+      <c r="T10" s="122"/>
     </row>
     <row r="11" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="54" t="s">
@@ -3680,19 +3680,19 @@
         <f>HLOOKUP("Laptop",A10:F13,2,0)</f>
         <v>1000</v>
       </c>
-      <c r="I11" s="117" t="s">
+      <c r="I11" s="123" t="s">
         <v>85</v>
       </c>
-      <c r="J11" s="116"/>
-      <c r="K11" s="116"/>
-      <c r="L11" s="116"/>
-      <c r="M11" s="116"/>
-      <c r="N11" s="116"/>
-      <c r="O11" s="116"/>
-      <c r="P11" s="116"/>
-      <c r="Q11" s="116"/>
-      <c r="R11" s="116"/>
-      <c r="S11" s="116"/>
+      <c r="J11" s="122"/>
+      <c r="K11" s="122"/>
+      <c r="L11" s="122"/>
+      <c r="M11" s="122"/>
+      <c r="N11" s="122"/>
+      <c r="O11" s="122"/>
+      <c r="P11" s="122"/>
+      <c r="Q11" s="122"/>
+      <c r="R11" s="122"/>
+      <c r="S11" s="122"/>
     </row>
     <row r="12" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="54" t="s">
@@ -3718,19 +3718,19 @@
         <f>HLOOKUP("Tablet",A10:F13,3,0)</f>
         <v>Electronics</v>
       </c>
-      <c r="I12" s="117" t="s">
+      <c r="I12" s="123" t="s">
         <v>86</v>
       </c>
-      <c r="J12" s="116"/>
-      <c r="K12" s="116"/>
-      <c r="L12" s="116"/>
-      <c r="M12" s="116"/>
-      <c r="N12" s="116"/>
-      <c r="O12" s="116"/>
-      <c r="P12" s="116"/>
-      <c r="Q12" s="116"/>
-      <c r="R12" s="116"/>
-      <c r="S12" s="116"/>
+      <c r="J12" s="122"/>
+      <c r="K12" s="122"/>
+      <c r="L12" s="122"/>
+      <c r="M12" s="122"/>
+      <c r="N12" s="122"/>
+      <c r="O12" s="122"/>
+      <c r="P12" s="122"/>
+      <c r="Q12" s="122"/>
+      <c r="R12" s="122"/>
+      <c r="S12" s="122"/>
     </row>
     <row r="13" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="54" t="s">
@@ -3756,19 +3756,19 @@
         <f>HLOOKUP("Keyboard",A10:F13,4,0)</f>
         <v>50</v>
       </c>
-      <c r="I13" s="117" t="s">
+      <c r="I13" s="123" t="s">
         <v>87</v>
       </c>
-      <c r="J13" s="116"/>
-      <c r="K13" s="116"/>
-      <c r="L13" s="116"/>
-      <c r="M13" s="116"/>
-      <c r="N13" s="116"/>
-      <c r="O13" s="116"/>
-      <c r="P13" s="116"/>
-      <c r="Q13" s="116"/>
-      <c r="R13" s="116"/>
-      <c r="S13" s="116"/>
+      <c r="J13" s="122"/>
+      <c r="K13" s="122"/>
+      <c r="L13" s="122"/>
+      <c r="M13" s="122"/>
+      <c r="N13" s="122"/>
+      <c r="O13" s="122"/>
+      <c r="P13" s="122"/>
+      <c r="Q13" s="122"/>
+      <c r="R13" s="122"/>
+      <c r="S13" s="122"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -3794,15 +3794,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="124" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="119"/>
-      <c r="D1" s="119"/>
-      <c r="E1" s="119"/>
-      <c r="F1" s="119"/>
-      <c r="G1" s="120"/>
+      <c r="B1" s="125"/>
+      <c r="C1" s="125"/>
+      <c r="D1" s="125"/>
+      <c r="E1" s="125"/>
+      <c r="F1" s="125"/>
+      <c r="G1" s="126"/>
     </row>
     <row r="2" spans="1:14" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="77" t="s">
@@ -3840,10 +3840,10 @@
         <f>_xlfn.XLOOKUP("P102",A3:A12,D3:D12)</f>
         <v>1500</v>
       </c>
-      <c r="F3" s="124" t="s">
+      <c r="F3" s="130" t="s">
         <v>109</v>
       </c>
-      <c r="G3" s="125"/>
+      <c r="G3" s="131"/>
       <c r="H3" s="65" t="s">
         <v>118</v>
       </c>
@@ -3865,10 +3865,10 @@
         <f>_xlfn.XLOOKUP("P999",A3:A12,C3:C12,"Not Found")</f>
         <v>Not Found</v>
       </c>
-      <c r="F4" s="124" t="s">
+      <c r="F4" s="130" t="s">
         <v>110</v>
       </c>
-      <c r="G4" s="125"/>
+      <c r="G4" s="131"/>
       <c r="H4" s="65" t="s">
         <v>117</v>
       </c>
@@ -3890,10 +3890,10 @@
         <f>INDEX(A3:D12,3,2)</f>
         <v>Keyboard</v>
       </c>
-      <c r="F5" s="124" t="s">
+      <c r="F5" s="130" t="s">
         <v>112</v>
       </c>
-      <c r="G5" s="125"/>
+      <c r="G5" s="131"/>
       <c r="H5" s="65" t="s">
         <v>111</v>
       </c>
@@ -3915,10 +3915,10 @@
         <f>MATCH("Laptop",B3:B12,0)</f>
         <v>1</v>
       </c>
-      <c r="F6" s="124" t="s">
+      <c r="F6" s="130" t="s">
         <v>114</v>
       </c>
-      <c r="G6" s="125"/>
+      <c r="G6" s="131"/>
       <c r="H6" s="65" t="s">
         <v>116</v>
       </c>
@@ -3940,10 +3940,10 @@
         <f>INDEX(D3:D12,MATCH("Monitor",B3:B12,0))</f>
         <v>10000</v>
       </c>
-      <c r="F7" s="124" t="s">
+      <c r="F7" s="130" t="s">
         <v>115</v>
       </c>
-      <c r="G7" s="125"/>
+      <c r="G7" s="131"/>
       <c r="H7" s="65" t="s">
         <v>119</v>
       </c>
@@ -3962,16 +3962,16 @@
         <v>4000</v>
       </c>
       <c r="E8" s="84"/>
-      <c r="F8" s="124"/>
-      <c r="G8" s="125"/>
-      <c r="I8" s="116" t="s">
+      <c r="F8" s="130"/>
+      <c r="G8" s="131"/>
+      <c r="I8" s="122" t="s">
         <v>113</v>
       </c>
-      <c r="J8" s="116"/>
-      <c r="K8" s="116"/>
-      <c r="L8" s="116"/>
-      <c r="M8" s="116"/>
-      <c r="N8" s="116"/>
+      <c r="J8" s="122"/>
+      <c r="K8" s="122"/>
+      <c r="L8" s="122"/>
+      <c r="M8" s="122"/>
+      <c r="N8" s="122"/>
     </row>
     <row r="9" spans="1:14" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="69" t="s">
@@ -3990,10 +3990,10 @@
         <f ca="1">OFFSET(A2,5,1)</f>
         <v>Speaker</v>
       </c>
-      <c r="F9" s="124" t="s">
+      <c r="F9" s="130" t="s">
         <v>120</v>
       </c>
-      <c r="G9" s="125"/>
+      <c r="G9" s="131"/>
       <c r="H9" s="65" t="s">
         <v>121</v>
       </c>
@@ -4012,8 +4012,8 @@
         <v>30000</v>
       </c>
       <c r="E10" s="84"/>
-      <c r="F10" s="124"/>
-      <c r="G10" s="125"/>
+      <c r="F10" s="130"/>
+      <c r="G10" s="131"/>
     </row>
     <row r="11" spans="1:14" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="69" t="s">
@@ -4032,10 +4032,10 @@
         <f t="array" aca="1" ref="E11" ca="1">INDIRECT(F2)</f>
         <v>200</v>
       </c>
-      <c r="F11" s="124" t="s">
+      <c r="F11" s="130" t="s">
         <v>123</v>
       </c>
-      <c r="G11" s="125"/>
+      <c r="G11" s="131"/>
       <c r="H11" s="65" t="s">
         <v>124</v>
       </c>
@@ -4067,15 +4067,15 @@
       <c r="G13" s="59"/>
     </row>
     <row r="14" spans="1:14" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="121" t="s">
+      <c r="A14" s="127" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="122"/>
-      <c r="C14" s="122"/>
-      <c r="D14" s="122"/>
-      <c r="E14" s="122"/>
-      <c r="F14" s="122"/>
-      <c r="G14" s="123"/>
+      <c r="B14" s="128"/>
+      <c r="C14" s="128"/>
+      <c r="D14" s="128"/>
+      <c r="E14" s="128"/>
+      <c r="F14" s="128"/>
+      <c r="G14" s="129"/>
     </row>
     <row r="15" spans="1:14" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="58" t="s">
@@ -4212,38 +4212,48 @@
   <dimension ref="A1:K25"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="8.88671875" style="65"/>
+    <col min="1" max="1" width="10.6640625" style="65" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" style="65" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.88671875" style="65" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.33203125" style="65" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.88671875" style="65" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.44140625" style="65" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="8.88671875" style="65"/>
+    <col min="9" max="9" width="9" style="65" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="58.77734375" style="65" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.44140625" style="65" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="65"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="130" t="s">
+      <c r="A1" s="90" t="s">
         <v>125</v>
       </c>
-      <c r="B1" s="126" t="s">
+      <c r="B1" s="88" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="126" t="s">
+      <c r="C1" s="88" t="s">
         <v>126</v>
       </c>
-      <c r="D1" s="126" t="s">
+      <c r="D1" s="88" t="s">
         <v>127</v>
       </c>
-      <c r="E1" s="126" t="s">
+      <c r="E1" s="88" t="s">
         <v>128</v>
       </c>
-      <c r="F1" s="126" t="s">
+      <c r="F1" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="G1" s="131"/>
-      <c r="I1" s="126" t="s">
+      <c r="G1" s="91"/>
+      <c r="I1" s="88" t="s">
         <v>129</v>
       </c>
-      <c r="J1" s="126" t="s">
+      <c r="J1" s="88" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="132">
+      <c r="A2" s="92">
         <v>45662</v>
       </c>
       <c r="B2" s="65" t="s">
@@ -4273,7 +4283,7 @@
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="132">
+      <c r="A3" s="92">
         <v>45665</v>
       </c>
       <c r="B3" s="65" t="s">
@@ -4297,9 +4307,13 @@
       <c r="J3" s="65" t="s">
         <v>138</v>
       </c>
+      <c r="K3" s="65">
+        <f>SUMIF(B2:B11,"Sales",D2:D11)</f>
+        <v>5650</v>
+      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="132">
+      <c r="A4" s="92">
         <v>45672</v>
       </c>
       <c r="B4" s="65" t="s">
@@ -4323,9 +4337,13 @@
       <c r="J4" s="65" t="s">
         <v>141</v>
       </c>
+      <c r="K4" s="65">
+        <f>SUMIFS(D2:D11,C2:C11,"Utilities",F2:F11,"East")</f>
+        <v>1450</v>
+      </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A5" s="132">
+      <c r="A5" s="92">
         <v>45677</v>
       </c>
       <c r="B5" s="65" t="s">
@@ -4351,7 +4369,7 @@
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="132">
+      <c r="A6" s="92">
         <v>45685</v>
       </c>
       <c r="B6" s="65" t="s">
@@ -4377,7 +4395,7 @@
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="132">
+      <c r="A7" s="92">
         <v>45692</v>
       </c>
       <c r="B7" s="65" t="s">
@@ -4407,7 +4425,7 @@
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="132">
+      <c r="A8" s="92">
         <v>45698</v>
       </c>
       <c r="B8" s="65" t="s">
@@ -4433,7 +4451,7 @@
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="132">
+      <c r="A9" s="92">
         <v>45706</v>
       </c>
       <c r="B9" s="65" t="s">
@@ -4459,7 +4477,7 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="132">
+      <c r="A10" s="92">
         <v>45711</v>
       </c>
       <c r="B10" s="65" t="s">
@@ -4485,7 +4503,7 @@
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="132">
+      <c r="A11" s="92">
         <v>45715</v>
       </c>
       <c r="B11" s="65" t="s">
@@ -4511,7 +4529,7 @@
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="132"/>
+      <c r="A12" s="92"/>
       <c r="I12" s="65" t="s">
         <v>159</v>
       </c>
@@ -4524,7 +4542,7 @@
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="132"/>
+      <c r="A13" s="92"/>
       <c r="I13" s="65" t="s">
         <v>161</v>
       </c>
@@ -4533,7 +4551,7 @@
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="132"/>
+      <c r="A14" s="92"/>
       <c r="I14" s="65" t="s">
         <v>163</v>
       </c>
@@ -4542,7 +4560,7 @@
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="132"/>
+      <c r="A15" s="92"/>
       <c r="I15" s="65" t="s">
         <v>165</v>
       </c>
@@ -4551,7 +4569,7 @@
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="132"/>
+      <c r="A16" s="92"/>
       <c r="I16" s="65" t="s">
         <v>167</v>
       </c>
@@ -4560,7 +4578,7 @@
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="132"/>
+      <c r="A17" s="92"/>
       <c r="I17" s="65" t="s">
         <v>169</v>
       </c>
@@ -4569,7 +4587,7 @@
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="132"/>
+      <c r="A18" s="92"/>
       <c r="I18" s="65" t="s">
         <v>171</v>
       </c>
@@ -4578,7 +4596,7 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="132"/>
+      <c r="A19" s="92"/>
       <c r="I19" s="65" t="s">
         <v>173</v>
       </c>
@@ -4587,7 +4605,7 @@
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="132"/>
+      <c r="A20" s="92"/>
       <c r="I20" s="65" t="s">
         <v>175</v>
       </c>
@@ -4596,7 +4614,7 @@
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="132"/>
+      <c r="A21" s="92"/>
       <c r="I21" s="65" t="s">
         <v>177</v>
       </c>
@@ -4605,18 +4623,18 @@
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="133" t="s">
+      <c r="A22" s="93" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="132"/>
+      <c r="A23" s="92"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="132"/>
+      <c r="A24" s="92"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="132"/>
+      <c r="A25" s="92"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -4641,23 +4659,23 @@
     <col min="11" max="16384" width="8.88671875" style="65"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="129" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="129" t="s">
+    <row r="1" spans="1:10" s="89" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="89" t="s">
         <v>223</v>
       </c>
-      <c r="B1" s="129" t="s">
+      <c r="B1" s="89" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="129" t="s">
+      <c r="C1" s="89" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="129" t="s">
+      <c r="D1" s="89" t="s">
         <v>127</v>
       </c>
-      <c r="E1" s="129" t="s">
+      <c r="E1" s="89" t="s">
         <v>222</v>
       </c>
-      <c r="I1" s="129" t="s">
+      <c r="I1" s="89" t="s">
         <v>221</v>
       </c>
     </row>
@@ -4677,10 +4695,10 @@
       <c r="E2" s="65" t="s">
         <v>220</v>
       </c>
-      <c r="I2" s="129" t="s">
+      <c r="I2" s="89" t="s">
         <v>219</v>
       </c>
-      <c r="J2" s="129" t="s">
+      <c r="J2" s="89" t="s">
         <v>218</v>
       </c>
     </row>
@@ -4932,17 +4950,17 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="127" t="s">
+      <c r="A24" s="132" t="s">
         <v>224</v>
       </c>
-      <c r="B24" s="128"/>
-      <c r="C24" s="128"/>
-      <c r="D24" s="128"/>
-      <c r="E24" s="128"/>
-      <c r="F24" s="128"/>
-      <c r="G24" s="128"/>
-      <c r="H24" s="128"/>
-      <c r="I24" s="128"/>
+      <c r="B24" s="133"/>
+      <c r="C24" s="133"/>
+      <c r="D24" s="133"/>
+      <c r="E24" s="133"/>
+      <c r="F24" s="133"/>
+      <c r="G24" s="133"/>
+      <c r="H24" s="133"/>
+      <c r="I24" s="133"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4973,28 +4991,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="126" t="s">
+      <c r="A1" s="88" t="s">
         <v>225</v>
       </c>
-      <c r="B1" s="126" t="s">
+      <c r="B1" s="88" t="s">
         <v>226</v>
       </c>
-      <c r="C1" s="126" t="s">
+      <c r="C1" s="88" t="s">
         <v>42</v>
       </c>
-      <c r="D1" s="126" t="s">
+      <c r="D1" s="88" t="s">
         <v>227</v>
       </c>
-      <c r="E1" s="126" t="s">
+      <c r="E1" s="88" t="s">
         <v>228</v>
       </c>
-      <c r="F1" s="126" t="s">
+      <c r="F1" s="88" t="s">
         <v>229</v>
       </c>
-      <c r="I1" s="126" t="s">
+      <c r="I1" s="88" t="s">
         <v>219</v>
       </c>
-      <c r="J1" s="126" t="s">
+      <c r="J1" s="88" t="s">
         <v>230</v>
       </c>
     </row>
@@ -5283,17 +5301,17 @@
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="127" t="s">
+      <c r="A25" s="132" t="s">
         <v>266</v>
       </c>
-      <c r="B25" s="128"/>
-      <c r="C25" s="128"/>
-      <c r="D25" s="128"/>
-      <c r="E25" s="128"/>
-      <c r="F25" s="128"/>
-      <c r="G25" s="128"/>
-      <c r="H25" s="128"/>
-      <c r="I25" s="128"/>
+      <c r="B25" s="133"/>
+      <c r="C25" s="133"/>
+      <c r="D25" s="133"/>
+      <c r="E25" s="133"/>
+      <c r="F25" s="133"/>
+      <c r="G25" s="133"/>
+      <c r="H25" s="133"/>
+      <c r="I25" s="133"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5328,46 +5346,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A1" s="126" t="s">
+      <c r="A1" s="88" t="s">
         <v>267</v>
       </c>
-      <c r="B1" s="126" t="s">
+      <c r="B1" s="88" t="s">
         <v>268</v>
       </c>
-      <c r="C1" s="126" t="s">
+      <c r="C1" s="88" t="s">
         <v>269</v>
       </c>
-      <c r="D1" s="126" t="s">
+      <c r="D1" s="88" t="s">
         <v>270</v>
       </c>
-      <c r="E1" s="126" t="s">
+      <c r="E1" s="88" t="s">
         <v>271</v>
       </c>
-      <c r="F1" s="126" t="s">
+      <c r="F1" s="88" t="s">
         <v>272</v>
       </c>
-      <c r="G1" s="126" t="s">
+      <c r="G1" s="88" t="s">
         <v>273</v>
       </c>
-      <c r="H1" s="126" t="s">
+      <c r="H1" s="88" t="s">
         <v>274</v>
       </c>
-      <c r="I1" s="126" t="s">
+      <c r="I1" s="88" t="s">
         <v>275</v>
       </c>
-      <c r="J1" s="126" t="s">
+      <c r="J1" s="88" t="s">
         <v>276</v>
       </c>
-      <c r="K1" s="126" t="s">
+      <c r="K1" s="88" t="s">
         <v>277</v>
       </c>
-      <c r="L1" s="126">
+      <c r="L1" s="88">
         <v>0</v>
       </c>
-      <c r="M1" s="126" t="s">
+      <c r="M1" s="88" t="s">
         <v>219</v>
       </c>
-      <c r="N1" s="126" t="s">
+      <c r="N1" s="88" t="s">
         <v>230</v>
       </c>
     </row>
@@ -5663,17 +5681,17 @@
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="127" t="s">
+      <c r="A24" s="132" t="s">
         <v>289</v>
       </c>
-      <c r="B24" s="128"/>
-      <c r="C24" s="128"/>
-      <c r="D24" s="128"/>
-      <c r="E24" s="128"/>
-      <c r="F24" s="128"/>
-      <c r="G24" s="128"/>
-      <c r="H24" s="128"/>
-      <c r="I24" s="128"/>
+      <c r="B24" s="133"/>
+      <c r="C24" s="133"/>
+      <c r="D24" s="133"/>
+      <c r="E24" s="133"/>
+      <c r="F24" s="133"/>
+      <c r="G24" s="133"/>
+      <c r="H24" s="133"/>
+      <c r="I24" s="133"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5699,20 +5717,20 @@
     <col min="6" max="16384" width="8.88671875" style="65"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="129" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="129" t="s">
+    <row r="1" spans="1:5" s="89" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="89" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="129" t="s">
+      <c r="B1" s="89" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="129" t="s">
+      <c r="C1" s="89" t="s">
         <v>77</v>
       </c>
-      <c r="D1" s="129" t="s">
+      <c r="D1" s="89" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="129" t="s">
+      <c r="E1" s="89" t="s">
         <v>2</v>
       </c>
     </row>
@@ -5801,19 +5819,19 @@
         <v>4000</v>
       </c>
     </row>
-    <row r="8" spans="1:5" s="129" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="129" t="s">
+    <row r="8" spans="1:5" s="89" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="89" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="9" spans="1:5" s="129" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="129" t="s">
+    <row r="9" spans="1:5" s="89" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="89" t="s">
         <v>219</v>
       </c>
-      <c r="B9" s="129" t="s">
+      <c r="B9" s="89" t="s">
         <v>218</v>
       </c>
-      <c r="C9" s="129" t="s">
+      <c r="C9" s="89" t="s">
         <v>43</v>
       </c>
     </row>
@@ -5906,17 +5924,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="127" t="s">
+      <c r="A23" s="132" t="s">
         <v>305</v>
       </c>
-      <c r="B23" s="128"/>
-      <c r="C23" s="128"/>
-      <c r="D23" s="128"/>
-      <c r="E23" s="128"/>
-      <c r="F23" s="128"/>
-      <c r="G23" s="128"/>
-      <c r="H23" s="128"/>
-      <c r="I23" s="128"/>
+      <c r="B23" s="133"/>
+      <c r="C23" s="133"/>
+      <c r="D23" s="133"/>
+      <c r="E23" s="133"/>
+      <c r="F23" s="133"/>
+      <c r="G23" s="133"/>
+      <c r="H23" s="133"/>
+      <c r="I23" s="133"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Practice_file.xlsx
+++ b/Practice_file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d58d4d655bee1e81/Desktop/Github/Practice_Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="210" documentId="11_F25DC773A252ABDACC1048BD89DC52D45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4300A19-707D-4C0E-B913-3F4EA55A2F48}"/>
+  <xr:revisionPtr revIDLastSave="211" documentId="11_F25DC773A252ABDACC1048BD89DC52D45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60CAE58C-11E2-479F-A8DE-EAE9A8CC2A96}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1659,6 +1659,66 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1670,66 +1730,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2524,15 +2524,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="96" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="107"/>
-      <c r="C1" s="107"/>
-      <c r="D1" s="107"/>
-      <c r="E1" s="107"/>
-      <c r="F1" s="107"/>
-      <c r="G1" s="108"/>
+      <c r="B1" s="97"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="97"/>
+      <c r="E1" s="97"/>
+      <c r="F1" s="97"/>
+      <c r="G1" s="98"/>
       <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2773,15 +2773,15 @@
     </row>
     <row r="15" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="16" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="106" t="s">
+      <c r="A16" s="96" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="107"/>
-      <c r="C16" s="107"/>
-      <c r="D16" s="107"/>
-      <c r="E16" s="107"/>
-      <c r="F16" s="118"/>
-      <c r="G16" s="118"/>
+      <c r="B16" s="97"/>
+      <c r="C16" s="97"/>
+      <c r="D16" s="97"/>
+      <c r="E16" s="97"/>
+      <c r="F16" s="108"/>
+      <c r="G16" s="108"/>
     </row>
     <row r="17" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="24" t="s">
@@ -2829,10 +2829,10 @@
         <f>COUNTIF(B18:B27,"&gt;30")</f>
         <v>6</v>
       </c>
-      <c r="H18" s="100" t="s">
+      <c r="H18" s="109" t="s">
         <v>70</v>
       </c>
-      <c r="I18" s="101"/>
+      <c r="I18" s="110"/>
     </row>
     <row r="19" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="29" t="s">
@@ -2857,10 +2857,10 @@
         <f>COUNTIF(E18:E27,"Male")</f>
         <v>5</v>
       </c>
-      <c r="H19" s="100" t="s">
+      <c r="H19" s="109" t="s">
         <v>71</v>
       </c>
-      <c r="I19" s="101"/>
+      <c r="I19" s="110"/>
     </row>
     <row r="20" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="29" t="s">
@@ -3016,16 +3016,16 @@
     </row>
     <row r="30" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="31" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="109" t="s">
+      <c r="A31" s="99" t="s">
         <v>60</v>
       </c>
-      <c r="B31" s="110"/>
-      <c r="C31" s="110"/>
-      <c r="D31" s="110"/>
-      <c r="E31" s="110"/>
-      <c r="F31" s="110"/>
-      <c r="G31" s="110"/>
-      <c r="H31" s="111"/>
+      <c r="B31" s="100"/>
+      <c r="C31" s="100"/>
+      <c r="D31" s="100"/>
+      <c r="E31" s="100"/>
+      <c r="F31" s="100"/>
+      <c r="G31" s="100"/>
+      <c r="H31" s="101"/>
     </row>
     <row r="32" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="39" t="s">
@@ -3041,9 +3041,9 @@
         <v>62</v>
       </c>
       <c r="E32" s="40"/>
-      <c r="F32" s="102"/>
-      <c r="G32" s="103"/>
-      <c r="H32" s="104"/>
+      <c r="F32" s="111"/>
+      <c r="G32" s="112"/>
+      <c r="H32" s="113"/>
     </row>
     <row r="33" spans="1:10" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="29" t="s">
@@ -3062,15 +3062,15 @@
         <f>COUNTIF(D33:D51,"Pending")</f>
         <v>7</v>
       </c>
-      <c r="F33" s="112" t="s">
+      <c r="F33" s="102" t="s">
         <v>69</v>
       </c>
-      <c r="G33" s="113"/>
-      <c r="H33" s="114"/>
-      <c r="I33" s="105" t="s">
+      <c r="G33" s="103"/>
+      <c r="H33" s="104"/>
+      <c r="I33" s="114" t="s">
         <v>72</v>
       </c>
-      <c r="J33" s="101"/>
+      <c r="J33" s="110"/>
     </row>
     <row r="34" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="29" t="s">
@@ -3089,15 +3089,15 @@
         <f>COUNTIFS(B33:B51,"West",D33:D51,"Delivered")</f>
         <v>3</v>
       </c>
-      <c r="F34" s="115" t="s">
+      <c r="F34" s="105" t="s">
         <v>73</v>
       </c>
-      <c r="G34" s="116"/>
-      <c r="H34" s="117"/>
-      <c r="I34" s="97" t="s">
+      <c r="G34" s="106"/>
+      <c r="H34" s="107"/>
+      <c r="I34" s="117" t="s">
         <v>74</v>
       </c>
-      <c r="J34" s="97"/>
+      <c r="J34" s="117"/>
     </row>
     <row r="35" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="29" t="s">
@@ -3113,11 +3113,11 @@
         <v>64</v>
       </c>
       <c r="E35" s="25"/>
-      <c r="F35" s="99"/>
-      <c r="G35" s="99"/>
-      <c r="H35" s="99"/>
-      <c r="I35" s="98"/>
-      <c r="J35" s="97"/>
+      <c r="F35" s="95"/>
+      <c r="G35" s="95"/>
+      <c r="H35" s="95"/>
+      <c r="I35" s="118"/>
+      <c r="J35" s="117"/>
     </row>
     <row r="36" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="29" t="s">
@@ -3133,11 +3133,11 @@
         <v>64</v>
       </c>
       <c r="E36" s="25"/>
-      <c r="F36" s="99"/>
-      <c r="G36" s="99"/>
-      <c r="H36" s="99"/>
-      <c r="I36" s="95"/>
-      <c r="J36" s="96"/>
+      <c r="F36" s="95"/>
+      <c r="G36" s="95"/>
+      <c r="H36" s="95"/>
+      <c r="I36" s="115"/>
+      <c r="J36" s="116"/>
     </row>
     <row r="37" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="29" t="s">
@@ -3153,11 +3153,11 @@
         <v>66</v>
       </c>
       <c r="E37" s="25"/>
-      <c r="F37" s="99"/>
-      <c r="G37" s="99"/>
-      <c r="H37" s="99"/>
-      <c r="I37" s="95"/>
-      <c r="J37" s="96"/>
+      <c r="F37" s="95"/>
+      <c r="G37" s="95"/>
+      <c r="H37" s="95"/>
+      <c r="I37" s="115"/>
+      <c r="J37" s="116"/>
     </row>
     <row r="38" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="29" t="s">
@@ -3173,11 +3173,11 @@
         <v>64</v>
       </c>
       <c r="E38" s="25"/>
-      <c r="F38" s="99"/>
-      <c r="G38" s="99"/>
-      <c r="H38" s="99"/>
-      <c r="I38" s="95"/>
-      <c r="J38" s="96"/>
+      <c r="F38" s="95"/>
+      <c r="G38" s="95"/>
+      <c r="H38" s="95"/>
+      <c r="I38" s="115"/>
+      <c r="J38" s="116"/>
     </row>
     <row r="39" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="29" t="s">
@@ -3193,11 +3193,11 @@
         <v>64</v>
       </c>
       <c r="E39" s="25"/>
-      <c r="F39" s="99"/>
-      <c r="G39" s="99"/>
-      <c r="H39" s="99"/>
-      <c r="I39" s="95"/>
-      <c r="J39" s="96"/>
+      <c r="F39" s="95"/>
+      <c r="G39" s="95"/>
+      <c r="H39" s="95"/>
+      <c r="I39" s="115"/>
+      <c r="J39" s="116"/>
     </row>
     <row r="40" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="29" t="s">
@@ -3213,11 +3213,11 @@
         <v>66</v>
       </c>
       <c r="E40" s="25"/>
-      <c r="F40" s="99"/>
-      <c r="G40" s="99"/>
-      <c r="H40" s="99"/>
-      <c r="I40" s="95"/>
-      <c r="J40" s="96"/>
+      <c r="F40" s="95"/>
+      <c r="G40" s="95"/>
+      <c r="H40" s="95"/>
+      <c r="I40" s="115"/>
+      <c r="J40" s="116"/>
     </row>
     <row r="41" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="29" t="s">
@@ -3233,11 +3233,11 @@
         <v>64</v>
       </c>
       <c r="E41" s="25"/>
-      <c r="F41" s="99"/>
-      <c r="G41" s="99"/>
-      <c r="H41" s="99"/>
-      <c r="I41" s="95"/>
-      <c r="J41" s="96"/>
+      <c r="F41" s="95"/>
+      <c r="G41" s="95"/>
+      <c r="H41" s="95"/>
+      <c r="I41" s="115"/>
+      <c r="J41" s="116"/>
     </row>
     <row r="42" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="29" t="s">
@@ -3253,11 +3253,11 @@
         <v>66</v>
       </c>
       <c r="E42" s="25"/>
-      <c r="F42" s="99"/>
-      <c r="G42" s="99"/>
-      <c r="H42" s="99"/>
-      <c r="I42" s="95"/>
-      <c r="J42" s="96"/>
+      <c r="F42" s="95"/>
+      <c r="G42" s="95"/>
+      <c r="H42" s="95"/>
+      <c r="I42" s="115"/>
+      <c r="J42" s="116"/>
     </row>
     <row r="43" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="29" t="s">
@@ -3273,11 +3273,11 @@
         <v>64</v>
       </c>
       <c r="E43" s="25"/>
-      <c r="F43" s="99"/>
-      <c r="G43" s="99"/>
-      <c r="H43" s="99"/>
-      <c r="I43" s="95"/>
-      <c r="J43" s="96"/>
+      <c r="F43" s="95"/>
+      <c r="G43" s="95"/>
+      <c r="H43" s="95"/>
+      <c r="I43" s="115"/>
+      <c r="J43" s="116"/>
     </row>
     <row r="44" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="29" t="s">
@@ -3293,11 +3293,11 @@
         <v>64</v>
       </c>
       <c r="E44" s="25"/>
-      <c r="F44" s="99"/>
-      <c r="G44" s="99"/>
-      <c r="H44" s="99"/>
-      <c r="I44" s="95"/>
-      <c r="J44" s="96"/>
+      <c r="F44" s="95"/>
+      <c r="G44" s="95"/>
+      <c r="H44" s="95"/>
+      <c r="I44" s="115"/>
+      <c r="J44" s="116"/>
     </row>
     <row r="45" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="29" t="s">
@@ -3313,9 +3313,9 @@
         <v>66</v>
       </c>
       <c r="E45" s="25"/>
-      <c r="F45" s="99"/>
-      <c r="G45" s="99"/>
-      <c r="H45" s="99"/>
+      <c r="F45" s="95"/>
+      <c r="G45" s="95"/>
+      <c r="H45" s="95"/>
     </row>
     <row r="46" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="29" t="s">
@@ -3331,9 +3331,9 @@
         <v>64</v>
       </c>
       <c r="E46" s="25"/>
-      <c r="F46" s="99"/>
-      <c r="G46" s="99"/>
-      <c r="H46" s="99"/>
+      <c r="F46" s="95"/>
+      <c r="G46" s="95"/>
+      <c r="H46" s="95"/>
     </row>
     <row r="47" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="29" t="s">
@@ -3349,9 +3349,9 @@
         <v>66</v>
       </c>
       <c r="E47" s="25"/>
-      <c r="F47" s="99"/>
-      <c r="G47" s="99"/>
-      <c r="H47" s="99"/>
+      <c r="F47" s="95"/>
+      <c r="G47" s="95"/>
+      <c r="H47" s="95"/>
     </row>
     <row r="48" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="29" t="s">
@@ -3367,9 +3367,9 @@
         <v>64</v>
       </c>
       <c r="E48" s="25"/>
-      <c r="F48" s="99"/>
-      <c r="G48" s="99"/>
-      <c r="H48" s="99"/>
+      <c r="F48" s="95"/>
+      <c r="G48" s="95"/>
+      <c r="H48" s="95"/>
     </row>
     <row r="49" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="29" t="s">
@@ -3385,9 +3385,9 @@
         <v>64</v>
       </c>
       <c r="E49" s="25"/>
-      <c r="F49" s="99"/>
-      <c r="G49" s="99"/>
-      <c r="H49" s="99"/>
+      <c r="F49" s="95"/>
+      <c r="G49" s="95"/>
+      <c r="H49" s="95"/>
     </row>
     <row r="50" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="29" t="s">
@@ -3403,9 +3403,9 @@
         <v>66</v>
       </c>
       <c r="E50" s="25"/>
-      <c r="F50" s="99"/>
-      <c r="G50" s="99"/>
-      <c r="H50" s="99"/>
+      <c r="F50" s="95"/>
+      <c r="G50" s="95"/>
+      <c r="H50" s="95"/>
     </row>
     <row r="51" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="29" t="s">
@@ -3421,22 +3421,22 @@
         <v>64</v>
       </c>
       <c r="E51" s="25"/>
-      <c r="F51" s="99"/>
-      <c r="G51" s="99"/>
-      <c r="H51" s="99"/>
+      <c r="F51" s="95"/>
+      <c r="G51" s="95"/>
+      <c r="H51" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="I34:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
     <mergeCell ref="F48:H48"/>
     <mergeCell ref="F49:H49"/>
     <mergeCell ref="F50:H50"/>
@@ -3453,16 +3453,16 @@
     <mergeCell ref="F47:H47"/>
     <mergeCell ref="F36:H36"/>
     <mergeCell ref="F37:H37"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="I34:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="A16:G16"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4367,6 +4367,10 @@
       <c r="J5" s="65" t="s">
         <v>143</v>
       </c>
+      <c r="K5" s="65">
+        <f>SUMIF(E2:E11,"Credit Card",D2:D11)</f>
+        <v>2500</v>
+      </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="92">
@@ -4393,6 +4397,10 @@
       <c r="J6" s="65" t="s">
         <v>148</v>
       </c>
+      <c r="K6" s="65">
+        <f>SUMIF(B2:B11,"HR",D2:D11)</f>
+        <v>5400</v>
+      </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="92">
@@ -4420,8 +4428,8 @@
         <v>150</v>
       </c>
       <c r="K7" s="65">
-        <f>SUMIFS(D2:D11,C2:C11,"Software",A2:A11,"&gt;=1/1/2025",A2:A11,"&lt;=12/31/2025")</f>
-        <v>0</v>
+        <f>SUMIFS(D:D,C:C,"Software",A:A,"&gt;=01-Jan-2025",A:A,"&lt;=31-Jan-2025")</f>
+        <v>1200</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
@@ -4449,6 +4457,10 @@
       <c r="J8" s="65" t="s">
         <v>152</v>
       </c>
+      <c r="K8" s="65">
+        <f>SUMIFS(D2:D11,C2:C11,"Travel",F2:F11,"West",E2:E11,"Credit Card")</f>
+        <v>950</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="92">
@@ -4475,6 +4487,10 @@
       <c r="J9" s="65" t="s">
         <v>154</v>
       </c>
+      <c r="K9" s="65">
+        <f>SUMIFS(D2:D11,B2:B11,"IT",A2:A11,"&gt;=01-Feb-2025",A2:A11,"&lt;=28-Feb-2025")</f>
+        <v>2500</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="92">
@@ -4501,6 +4517,10 @@
       <c r="J10" s="65" t="s">
         <v>156</v>
       </c>
+      <c r="K10" s="65">
+        <f>SUMIFS(D2:D11,C2:C11,"Office Supplies",F2:F11,"North")</f>
+        <v>400</v>
+      </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="92">
@@ -4526,6 +4546,10 @@
       </c>
       <c r="J11" s="65" t="s">
         <v>158</v>
+      </c>
+      <c r="K11" s="65">
+        <f>SUMIFS(D2:D11,C2:C11,"Utilities",E2:E11,"Bank Transfer")</f>
+        <v>750</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
@@ -4537,8 +4561,8 @@
         <v>160</v>
       </c>
       <c r="K12" s="65">
-        <f>SUMIFS(D2:D11,F2:F11,"East",A2:A11,"&gt;=1/1/2025",A2:A11,"&lt;=12/31/2025")</f>
-        <v>0</v>
+        <f>SUMIFS(D2:D11,F2:F11,"East",A2:A11,"&gt;=1-Jan-2025",A2:A11,"&lt;=31-Jan-2025")</f>
+        <v>1550</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -4548,6 +4572,10 @@
       </c>
       <c r="J13" s="65" t="s">
         <v>162</v>
+      </c>
+      <c r="K13" s="65">
+        <f>SUMIFS(D2:D11,F2:F11,"East",C2:C11,"Salaries",A2:A11,"&gt;= 1-Feb-2025",A2:A11,"&lt;=29-Feb-2025")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">

--- a/Practice_file.xlsx
+++ b/Practice_file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d58d4d655bee1e81/Desktop/Github/Practice_Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="211" documentId="11_F25DC773A252ABDACC1048BD89DC52D45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{60CAE58C-11E2-479F-A8DE-EAE9A8CC2A96}"/>
+  <xr:revisionPtr revIDLastSave="218" documentId="11_F25DC773A252ABDACC1048BD89DC52D45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17E397EE-A414-44B4-8CC0-AC5EA7F4F73A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -996,7 +996,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yy;@"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1098,6 +1098,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF2D3134"/>
+      <name val="Courier New"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1483,7 +1489,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="134">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1776,6 +1782,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -4209,7 +4216,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1602ACBA-3598-49C3-B1EA-05E1FB6B8EBD}">
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.6640625" style="65" customWidth="1"/>
@@ -4225,7 +4232,7 @@
     <col min="12" max="16384" width="8.88671875" style="65"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="90" t="s">
         <v>125</v>
       </c>
@@ -4252,7 +4259,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="92">
         <v>45662</v>
       </c>
@@ -4282,7 +4289,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="92">
         <v>45665</v>
       </c>
@@ -4312,7 +4319,7 @@
         <v>5650</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="92">
         <v>45672</v>
       </c>
@@ -4342,7 +4349,7 @@
         <v>1450</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="92">
         <v>45677</v>
       </c>
@@ -4372,7 +4379,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="92">
         <v>45685</v>
       </c>
@@ -4402,7 +4409,7 @@
         <v>5400</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="92">
         <v>45692</v>
       </c>
@@ -4432,7 +4439,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="92">
         <v>45698</v>
       </c>
@@ -4462,7 +4469,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="92">
         <v>45706</v>
       </c>
@@ -4492,7 +4499,7 @@
         <v>2500</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="92">
         <v>45711</v>
       </c>
@@ -4522,7 +4529,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="92">
         <v>45715</v>
       </c>
@@ -4552,7 +4559,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="92"/>
       <c r="I12" s="65" t="s">
         <v>159</v>
@@ -4565,7 +4572,7 @@
         <v>1550</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="92"/>
       <c r="I13" s="65" t="s">
         <v>161</v>
@@ -4574,11 +4581,12 @@
         <v>162</v>
       </c>
       <c r="K13" s="65">
-        <f>SUMIFS(D2:D11,F2:F11,"East",C2:C11,"Salaries",A2:A11,"&gt;= 1-Feb-2025",A2:A11,"&lt;=29-Feb-2025")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+        <f>SUMIFS(D2:D11,C2:C11,"Salaries",F2:F11,"East",A2:A11,"&gt;=01-Feb-2025",A2:A11,"&lt;=28-Feb-2025")</f>
+        <v>4800</v>
+      </c>
+      <c r="L13" s="134"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="92"/>
       <c r="I14" s="65" t="s">
         <v>163</v>
@@ -4587,7 +4595,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="92"/>
       <c r="I15" s="65" t="s">
         <v>165</v>
@@ -4596,7 +4604,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="92"/>
       <c r="I16" s="65" t="s">
         <v>167</v>

--- a/Practice_file.xlsx
+++ b/Practice_file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d58d4d655bee1e81/Desktop/Github/Practice_Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="218" documentId="11_F25DC773A252ABDACC1048BD89DC52D45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17E397EE-A414-44B4-8CC0-AC5EA7F4F73A}"/>
+  <xr:revisionPtr revIDLastSave="230" documentId="11_F25DC773A252ABDACC1048BD89DC52D45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96C385BB-B0EE-41F3-B4BE-24138FD23D9D}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SUMIF,AVGIF" sheetId="1" r:id="rId1"/>
@@ -69,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="306">
   <si>
     <t>Data for Practice</t>
   </si>
@@ -1489,7 +1489,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="135">
+  <cellXfs count="136">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1662,12 +1662,43 @@
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1707,36 +1738,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1782,7 +1783,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2079,14 +2082,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="11" customFormat="1" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="94" t="s">
+      <c r="A1" s="95" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="94"/>
-      <c r="C1" s="94"/>
-      <c r="D1" s="94"/>
-      <c r="E1" s="94"/>
-      <c r="F1" s="94"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
@@ -2248,17 +2251,17 @@
       <c r="F12" s="18"/>
     </row>
     <row r="15" spans="1:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="94" t="s">
+      <c r="A15" s="95" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="94"/>
-      <c r="C15" s="94"/>
-      <c r="D15" s="94"/>
-      <c r="E15" s="94"/>
-      <c r="F15" s="94"/>
-      <c r="G15" s="94"/>
-      <c r="H15" s="94"/>
-      <c r="I15" s="94"/>
+      <c r="B15" s="95"/>
+      <c r="C15" s="95"/>
+      <c r="D15" s="95"/>
+      <c r="E15" s="95"/>
+      <c r="F15" s="95"/>
+      <c r="G15" s="95"/>
+      <c r="H15" s="95"/>
+      <c r="I15" s="95"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
@@ -2531,15 +2534,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="107" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="97"/>
-      <c r="E1" s="97"/>
-      <c r="F1" s="97"/>
-      <c r="G1" s="98"/>
+      <c r="B1" s="108"/>
+      <c r="C1" s="108"/>
+      <c r="D1" s="108"/>
+      <c r="E1" s="108"/>
+      <c r="F1" s="108"/>
+      <c r="G1" s="109"/>
       <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2780,15 +2783,15 @@
     </row>
     <row r="15" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="16" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="96" t="s">
+      <c r="A16" s="107" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="97"/>
-      <c r="C16" s="97"/>
-      <c r="D16" s="97"/>
-      <c r="E16" s="97"/>
-      <c r="F16" s="108"/>
-      <c r="G16" s="108"/>
+      <c r="B16" s="108"/>
+      <c r="C16" s="108"/>
+      <c r="D16" s="108"/>
+      <c r="E16" s="108"/>
+      <c r="F16" s="119"/>
+      <c r="G16" s="119"/>
     </row>
     <row r="17" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="24" t="s">
@@ -2836,10 +2839,10 @@
         <f>COUNTIF(B18:B27,"&gt;30")</f>
         <v>6</v>
       </c>
-      <c r="H18" s="109" t="s">
+      <c r="H18" s="101" t="s">
         <v>70</v>
       </c>
-      <c r="I18" s="110"/>
+      <c r="I18" s="102"/>
     </row>
     <row r="19" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="29" t="s">
@@ -2864,10 +2867,10 @@
         <f>COUNTIF(E18:E27,"Male")</f>
         <v>5</v>
       </c>
-      <c r="H19" s="109" t="s">
+      <c r="H19" s="101" t="s">
         <v>71</v>
       </c>
-      <c r="I19" s="110"/>
+      <c r="I19" s="102"/>
     </row>
     <row r="20" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="29" t="s">
@@ -3023,16 +3026,16 @@
     </row>
     <row r="30" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="31" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="99" t="s">
+      <c r="A31" s="110" t="s">
         <v>60</v>
       </c>
-      <c r="B31" s="100"/>
-      <c r="C31" s="100"/>
-      <c r="D31" s="100"/>
-      <c r="E31" s="100"/>
-      <c r="F31" s="100"/>
-      <c r="G31" s="100"/>
-      <c r="H31" s="101"/>
+      <c r="B31" s="111"/>
+      <c r="C31" s="111"/>
+      <c r="D31" s="111"/>
+      <c r="E31" s="111"/>
+      <c r="F31" s="111"/>
+      <c r="G31" s="111"/>
+      <c r="H31" s="112"/>
     </row>
     <row r="32" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="39" t="s">
@@ -3048,9 +3051,9 @@
         <v>62</v>
       </c>
       <c r="E32" s="40"/>
-      <c r="F32" s="111"/>
-      <c r="G32" s="112"/>
-      <c r="H32" s="113"/>
+      <c r="F32" s="103"/>
+      <c r="G32" s="104"/>
+      <c r="H32" s="105"/>
     </row>
     <row r="33" spans="1:10" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="29" t="s">
@@ -3069,15 +3072,15 @@
         <f>COUNTIF(D33:D51,"Pending")</f>
         <v>7</v>
       </c>
-      <c r="F33" s="102" t="s">
+      <c r="F33" s="113" t="s">
         <v>69</v>
       </c>
-      <c r="G33" s="103"/>
-      <c r="H33" s="104"/>
-      <c r="I33" s="114" t="s">
+      <c r="G33" s="114"/>
+      <c r="H33" s="115"/>
+      <c r="I33" s="106" t="s">
         <v>72</v>
       </c>
-      <c r="J33" s="110"/>
+      <c r="J33" s="102"/>
     </row>
     <row r="34" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="29" t="s">
@@ -3096,15 +3099,15 @@
         <f>COUNTIFS(B33:B51,"West",D33:D51,"Delivered")</f>
         <v>3</v>
       </c>
-      <c r="F34" s="105" t="s">
+      <c r="F34" s="116" t="s">
         <v>73</v>
       </c>
-      <c r="G34" s="106"/>
-      <c r="H34" s="107"/>
-      <c r="I34" s="117" t="s">
+      <c r="G34" s="117"/>
+      <c r="H34" s="118"/>
+      <c r="I34" s="98" t="s">
         <v>74</v>
       </c>
-      <c r="J34" s="117"/>
+      <c r="J34" s="98"/>
     </row>
     <row r="35" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="29" t="s">
@@ -3120,11 +3123,11 @@
         <v>64</v>
       </c>
       <c r="E35" s="25"/>
-      <c r="F35" s="95"/>
-      <c r="G35" s="95"/>
-      <c r="H35" s="95"/>
-      <c r="I35" s="118"/>
-      <c r="J35" s="117"/>
+      <c r="F35" s="100"/>
+      <c r="G35" s="100"/>
+      <c r="H35" s="100"/>
+      <c r="I35" s="99"/>
+      <c r="J35" s="98"/>
     </row>
     <row r="36" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="29" t="s">
@@ -3140,11 +3143,11 @@
         <v>64</v>
       </c>
       <c r="E36" s="25"/>
-      <c r="F36" s="95"/>
-      <c r="G36" s="95"/>
-      <c r="H36" s="95"/>
-      <c r="I36" s="115"/>
-      <c r="J36" s="116"/>
+      <c r="F36" s="100"/>
+      <c r="G36" s="100"/>
+      <c r="H36" s="100"/>
+      <c r="I36" s="96"/>
+      <c r="J36" s="97"/>
     </row>
     <row r="37" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="29" t="s">
@@ -3160,11 +3163,11 @@
         <v>66</v>
       </c>
       <c r="E37" s="25"/>
-      <c r="F37" s="95"/>
-      <c r="G37" s="95"/>
-      <c r="H37" s="95"/>
-      <c r="I37" s="115"/>
-      <c r="J37" s="116"/>
+      <c r="F37" s="100"/>
+      <c r="G37" s="100"/>
+      <c r="H37" s="100"/>
+      <c r="I37" s="96"/>
+      <c r="J37" s="97"/>
     </row>
     <row r="38" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="29" t="s">
@@ -3180,11 +3183,11 @@
         <v>64</v>
       </c>
       <c r="E38" s="25"/>
-      <c r="F38" s="95"/>
-      <c r="G38" s="95"/>
-      <c r="H38" s="95"/>
-      <c r="I38" s="115"/>
-      <c r="J38" s="116"/>
+      <c r="F38" s="100"/>
+      <c r="G38" s="100"/>
+      <c r="H38" s="100"/>
+      <c r="I38" s="96"/>
+      <c r="J38" s="97"/>
     </row>
     <row r="39" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="29" t="s">
@@ -3200,11 +3203,11 @@
         <v>64</v>
       </c>
       <c r="E39" s="25"/>
-      <c r="F39" s="95"/>
-      <c r="G39" s="95"/>
-      <c r="H39" s="95"/>
-      <c r="I39" s="115"/>
-      <c r="J39" s="116"/>
+      <c r="F39" s="100"/>
+      <c r="G39" s="100"/>
+      <c r="H39" s="100"/>
+      <c r="I39" s="96"/>
+      <c r="J39" s="97"/>
     </row>
     <row r="40" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="29" t="s">
@@ -3220,11 +3223,11 @@
         <v>66</v>
       </c>
       <c r="E40" s="25"/>
-      <c r="F40" s="95"/>
-      <c r="G40" s="95"/>
-      <c r="H40" s="95"/>
-      <c r="I40" s="115"/>
-      <c r="J40" s="116"/>
+      <c r="F40" s="100"/>
+      <c r="G40" s="100"/>
+      <c r="H40" s="100"/>
+      <c r="I40" s="96"/>
+      <c r="J40" s="97"/>
     </row>
     <row r="41" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="29" t="s">
@@ -3240,11 +3243,11 @@
         <v>64</v>
       </c>
       <c r="E41" s="25"/>
-      <c r="F41" s="95"/>
-      <c r="G41" s="95"/>
-      <c r="H41" s="95"/>
-      <c r="I41" s="115"/>
-      <c r="J41" s="116"/>
+      <c r="F41" s="100"/>
+      <c r="G41" s="100"/>
+      <c r="H41" s="100"/>
+      <c r="I41" s="96"/>
+      <c r="J41" s="97"/>
     </row>
     <row r="42" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="29" t="s">
@@ -3260,11 +3263,11 @@
         <v>66</v>
       </c>
       <c r="E42" s="25"/>
-      <c r="F42" s="95"/>
-      <c r="G42" s="95"/>
-      <c r="H42" s="95"/>
-      <c r="I42" s="115"/>
-      <c r="J42" s="116"/>
+      <c r="F42" s="100"/>
+      <c r="G42" s="100"/>
+      <c r="H42" s="100"/>
+      <c r="I42" s="96"/>
+      <c r="J42" s="97"/>
     </row>
     <row r="43" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="29" t="s">
@@ -3280,11 +3283,11 @@
         <v>64</v>
       </c>
       <c r="E43" s="25"/>
-      <c r="F43" s="95"/>
-      <c r="G43" s="95"/>
-      <c r="H43" s="95"/>
-      <c r="I43" s="115"/>
-      <c r="J43" s="116"/>
+      <c r="F43" s="100"/>
+      <c r="G43" s="100"/>
+      <c r="H43" s="100"/>
+      <c r="I43" s="96"/>
+      <c r="J43" s="97"/>
     </row>
     <row r="44" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="29" t="s">
@@ -3300,11 +3303,11 @@
         <v>64</v>
       </c>
       <c r="E44" s="25"/>
-      <c r="F44" s="95"/>
-      <c r="G44" s="95"/>
-      <c r="H44" s="95"/>
-      <c r="I44" s="115"/>
-      <c r="J44" s="116"/>
+      <c r="F44" s="100"/>
+      <c r="G44" s="100"/>
+      <c r="H44" s="100"/>
+      <c r="I44" s="96"/>
+      <c r="J44" s="97"/>
     </row>
     <row r="45" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="29" t="s">
@@ -3320,9 +3323,9 @@
         <v>66</v>
       </c>
       <c r="E45" s="25"/>
-      <c r="F45" s="95"/>
-      <c r="G45" s="95"/>
-      <c r="H45" s="95"/>
+      <c r="F45" s="100"/>
+      <c r="G45" s="100"/>
+      <c r="H45" s="100"/>
     </row>
     <row r="46" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="29" t="s">
@@ -3338,9 +3341,9 @@
         <v>64</v>
       </c>
       <c r="E46" s="25"/>
-      <c r="F46" s="95"/>
-      <c r="G46" s="95"/>
-      <c r="H46" s="95"/>
+      <c r="F46" s="100"/>
+      <c r="G46" s="100"/>
+      <c r="H46" s="100"/>
     </row>
     <row r="47" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="29" t="s">
@@ -3356,9 +3359,9 @@
         <v>66</v>
       </c>
       <c r="E47" s="25"/>
-      <c r="F47" s="95"/>
-      <c r="G47" s="95"/>
-      <c r="H47" s="95"/>
+      <c r="F47" s="100"/>
+      <c r="G47" s="100"/>
+      <c r="H47" s="100"/>
     </row>
     <row r="48" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="29" t="s">
@@ -3374,9 +3377,9 @@
         <v>64</v>
       </c>
       <c r="E48" s="25"/>
-      <c r="F48" s="95"/>
-      <c r="G48" s="95"/>
-      <c r="H48" s="95"/>
+      <c r="F48" s="100"/>
+      <c r="G48" s="100"/>
+      <c r="H48" s="100"/>
     </row>
     <row r="49" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="29" t="s">
@@ -3392,9 +3395,9 @@
         <v>64</v>
       </c>
       <c r="E49" s="25"/>
-      <c r="F49" s="95"/>
-      <c r="G49" s="95"/>
-      <c r="H49" s="95"/>
+      <c r="F49" s="100"/>
+      <c r="G49" s="100"/>
+      <c r="H49" s="100"/>
     </row>
     <row r="50" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="29" t="s">
@@ -3410,9 +3413,9 @@
         <v>66</v>
       </c>
       <c r="E50" s="25"/>
-      <c r="F50" s="95"/>
-      <c r="G50" s="95"/>
-      <c r="H50" s="95"/>
+      <c r="F50" s="100"/>
+      <c r="G50" s="100"/>
+      <c r="H50" s="100"/>
     </row>
     <row r="51" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="29" t="s">
@@ -3428,22 +3431,22 @@
         <v>64</v>
       </c>
       <c r="E51" s="25"/>
-      <c r="F51" s="95"/>
-      <c r="G51" s="95"/>
-      <c r="H51" s="95"/>
+      <c r="F51" s="100"/>
+      <c r="G51" s="100"/>
+      <c r="H51" s="100"/>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="I34:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="A16:G16"/>
     <mergeCell ref="F48:H48"/>
     <mergeCell ref="F49:H49"/>
     <mergeCell ref="F50:H50"/>
@@ -3460,16 +3463,16 @@
     <mergeCell ref="F47:H47"/>
     <mergeCell ref="F36:H36"/>
     <mergeCell ref="F37:H37"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="I34:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3491,14 +3494,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="119" t="s">
+      <c r="A1" s="120" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="120"/>
-      <c r="C1" s="120"/>
-      <c r="D1" s="120"/>
-      <c r="E1" s="120"/>
-      <c r="F1" s="121"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="122"/>
     </row>
     <row r="2" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="58" t="s">
@@ -3555,20 +3558,20 @@
       <c r="G4" s="65" t="s">
         <v>84</v>
       </c>
-      <c r="H4" s="122" t="s">
+      <c r="H4" s="123" t="s">
         <v>89</v>
       </c>
-      <c r="I4" s="122"/>
-      <c r="J4" s="122"/>
-      <c r="K4" s="122"/>
-      <c r="L4" s="122"/>
-      <c r="M4" s="122"/>
-      <c r="N4" s="122"/>
-      <c r="O4" s="122"/>
-      <c r="P4" s="122"/>
-      <c r="Q4" s="122"/>
-      <c r="R4" s="122"/>
-      <c r="S4" s="122"/>
+      <c r="I4" s="123"/>
+      <c r="J4" s="123"/>
+      <c r="K4" s="123"/>
+      <c r="L4" s="123"/>
+      <c r="M4" s="123"/>
+      <c r="N4" s="123"/>
+      <c r="O4" s="123"/>
+      <c r="P4" s="123"/>
+      <c r="Q4" s="123"/>
+      <c r="R4" s="123"/>
+      <c r="S4" s="123"/>
     </row>
     <row r="5" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="61" t="s">
@@ -3648,20 +3651,20 @@
       <c r="H10" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="I10" s="122" t="s">
+      <c r="I10" s="123" t="s">
         <v>88</v>
       </c>
-      <c r="J10" s="122"/>
-      <c r="K10" s="122"/>
-      <c r="L10" s="122"/>
-      <c r="M10" s="122"/>
-      <c r="N10" s="122"/>
-      <c r="O10" s="122"/>
-      <c r="P10" s="122"/>
-      <c r="Q10" s="122"/>
-      <c r="R10" s="122"/>
-      <c r="S10" s="122"/>
-      <c r="T10" s="122"/>
+      <c r="J10" s="123"/>
+      <c r="K10" s="123"/>
+      <c r="L10" s="123"/>
+      <c r="M10" s="123"/>
+      <c r="N10" s="123"/>
+      <c r="O10" s="123"/>
+      <c r="P10" s="123"/>
+      <c r="Q10" s="123"/>
+      <c r="R10" s="123"/>
+      <c r="S10" s="123"/>
+      <c r="T10" s="123"/>
     </row>
     <row r="11" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="54" t="s">
@@ -3687,19 +3690,19 @@
         <f>HLOOKUP("Laptop",A10:F13,2,0)</f>
         <v>1000</v>
       </c>
-      <c r="I11" s="123" t="s">
+      <c r="I11" s="124" t="s">
         <v>85</v>
       </c>
-      <c r="J11" s="122"/>
-      <c r="K11" s="122"/>
-      <c r="L11" s="122"/>
-      <c r="M11" s="122"/>
-      <c r="N11" s="122"/>
-      <c r="O11" s="122"/>
-      <c r="P11" s="122"/>
-      <c r="Q11" s="122"/>
-      <c r="R11" s="122"/>
-      <c r="S11" s="122"/>
+      <c r="J11" s="123"/>
+      <c r="K11" s="123"/>
+      <c r="L11" s="123"/>
+      <c r="M11" s="123"/>
+      <c r="N11" s="123"/>
+      <c r="O11" s="123"/>
+      <c r="P11" s="123"/>
+      <c r="Q11" s="123"/>
+      <c r="R11" s="123"/>
+      <c r="S11" s="123"/>
     </row>
     <row r="12" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="54" t="s">
@@ -3725,19 +3728,19 @@
         <f>HLOOKUP("Tablet",A10:F13,3,0)</f>
         <v>Electronics</v>
       </c>
-      <c r="I12" s="123" t="s">
+      <c r="I12" s="124" t="s">
         <v>86</v>
       </c>
-      <c r="J12" s="122"/>
-      <c r="K12" s="122"/>
-      <c r="L12" s="122"/>
-      <c r="M12" s="122"/>
-      <c r="N12" s="122"/>
-      <c r="O12" s="122"/>
-      <c r="P12" s="122"/>
-      <c r="Q12" s="122"/>
-      <c r="R12" s="122"/>
-      <c r="S12" s="122"/>
+      <c r="J12" s="123"/>
+      <c r="K12" s="123"/>
+      <c r="L12" s="123"/>
+      <c r="M12" s="123"/>
+      <c r="N12" s="123"/>
+      <c r="O12" s="123"/>
+      <c r="P12" s="123"/>
+      <c r="Q12" s="123"/>
+      <c r="R12" s="123"/>
+      <c r="S12" s="123"/>
     </row>
     <row r="13" spans="1:20" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="54" t="s">
@@ -3763,19 +3766,19 @@
         <f>HLOOKUP("Keyboard",A10:F13,4,0)</f>
         <v>50</v>
       </c>
-      <c r="I13" s="123" t="s">
+      <c r="I13" s="124" t="s">
         <v>87</v>
       </c>
-      <c r="J13" s="122"/>
-      <c r="K13" s="122"/>
-      <c r="L13" s="122"/>
-      <c r="M13" s="122"/>
-      <c r="N13" s="122"/>
-      <c r="O13" s="122"/>
-      <c r="P13" s="122"/>
-      <c r="Q13" s="122"/>
-      <c r="R13" s="122"/>
-      <c r="S13" s="122"/>
+      <c r="J13" s="123"/>
+      <c r="K13" s="123"/>
+      <c r="L13" s="123"/>
+      <c r="M13" s="123"/>
+      <c r="N13" s="123"/>
+      <c r="O13" s="123"/>
+      <c r="P13" s="123"/>
+      <c r="Q13" s="123"/>
+      <c r="R13" s="123"/>
+      <c r="S13" s="123"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -3801,15 +3804,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="124" t="s">
+      <c r="A1" s="125" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="125"/>
-      <c r="C1" s="125"/>
-      <c r="D1" s="125"/>
-      <c r="E1" s="125"/>
-      <c r="F1" s="125"/>
-      <c r="G1" s="126"/>
+      <c r="B1" s="126"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="126"/>
+      <c r="E1" s="126"/>
+      <c r="F1" s="126"/>
+      <c r="G1" s="127"/>
     </row>
     <row r="2" spans="1:14" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="77" t="s">
@@ -3847,10 +3850,10 @@
         <f>_xlfn.XLOOKUP("P102",A3:A12,D3:D12)</f>
         <v>1500</v>
       </c>
-      <c r="F3" s="130" t="s">
+      <c r="F3" s="131" t="s">
         <v>109</v>
       </c>
-      <c r="G3" s="131"/>
+      <c r="G3" s="132"/>
       <c r="H3" s="65" t="s">
         <v>118</v>
       </c>
@@ -3872,10 +3875,10 @@
         <f>_xlfn.XLOOKUP("P999",A3:A12,C3:C12,"Not Found")</f>
         <v>Not Found</v>
       </c>
-      <c r="F4" s="130" t="s">
+      <c r="F4" s="131" t="s">
         <v>110</v>
       </c>
-      <c r="G4" s="131"/>
+      <c r="G4" s="132"/>
       <c r="H4" s="65" t="s">
         <v>117</v>
       </c>
@@ -3897,10 +3900,10 @@
         <f>INDEX(A3:D12,3,2)</f>
         <v>Keyboard</v>
       </c>
-      <c r="F5" s="130" t="s">
+      <c r="F5" s="131" t="s">
         <v>112</v>
       </c>
-      <c r="G5" s="131"/>
+      <c r="G5" s="132"/>
       <c r="H5" s="65" t="s">
         <v>111</v>
       </c>
@@ -3922,10 +3925,10 @@
         <f>MATCH("Laptop",B3:B12,0)</f>
         <v>1</v>
       </c>
-      <c r="F6" s="130" t="s">
+      <c r="F6" s="131" t="s">
         <v>114</v>
       </c>
-      <c r="G6" s="131"/>
+      <c r="G6" s="132"/>
       <c r="H6" s="65" t="s">
         <v>116</v>
       </c>
@@ -3947,10 +3950,10 @@
         <f>INDEX(D3:D12,MATCH("Monitor",B3:B12,0))</f>
         <v>10000</v>
       </c>
-      <c r="F7" s="130" t="s">
+      <c r="F7" s="131" t="s">
         <v>115</v>
       </c>
-      <c r="G7" s="131"/>
+      <c r="G7" s="132"/>
       <c r="H7" s="65" t="s">
         <v>119</v>
       </c>
@@ -3969,16 +3972,16 @@
         <v>4000</v>
       </c>
       <c r="E8" s="84"/>
-      <c r="F8" s="130"/>
-      <c r="G8" s="131"/>
-      <c r="I8" s="122" t="s">
+      <c r="F8" s="131"/>
+      <c r="G8" s="132"/>
+      <c r="I8" s="123" t="s">
         <v>113</v>
       </c>
-      <c r="J8" s="122"/>
-      <c r="K8" s="122"/>
-      <c r="L8" s="122"/>
-      <c r="M8" s="122"/>
-      <c r="N8" s="122"/>
+      <c r="J8" s="123"/>
+      <c r="K8" s="123"/>
+      <c r="L8" s="123"/>
+      <c r="M8" s="123"/>
+      <c r="N8" s="123"/>
     </row>
     <row r="9" spans="1:14" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="69" t="s">
@@ -3997,10 +4000,10 @@
         <f ca="1">OFFSET(A2,5,1)</f>
         <v>Speaker</v>
       </c>
-      <c r="F9" s="130" t="s">
+      <c r="F9" s="131" t="s">
         <v>120</v>
       </c>
-      <c r="G9" s="131"/>
+      <c r="G9" s="132"/>
       <c r="H9" s="65" t="s">
         <v>121</v>
       </c>
@@ -4019,8 +4022,8 @@
         <v>30000</v>
       </c>
       <c r="E10" s="84"/>
-      <c r="F10" s="130"/>
-      <c r="G10" s="131"/>
+      <c r="F10" s="131"/>
+      <c r="G10" s="132"/>
     </row>
     <row r="11" spans="1:14" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="69" t="s">
@@ -4039,10 +4042,10 @@
         <f t="array" aca="1" ref="E11" ca="1">INDIRECT(F2)</f>
         <v>200</v>
       </c>
-      <c r="F11" s="130" t="s">
+      <c r="F11" s="131" t="s">
         <v>123</v>
       </c>
-      <c r="G11" s="131"/>
+      <c r="G11" s="132"/>
       <c r="H11" s="65" t="s">
         <v>124</v>
       </c>
@@ -4074,15 +4077,15 @@
       <c r="G13" s="59"/>
     </row>
     <row r="14" spans="1:14" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="127" t="s">
+      <c r="A14" s="128" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="128"/>
-      <c r="C14" s="128"/>
-      <c r="D14" s="128"/>
-      <c r="E14" s="128"/>
-      <c r="F14" s="128"/>
-      <c r="G14" s="129"/>
+      <c r="B14" s="129"/>
+      <c r="C14" s="129"/>
+      <c r="D14" s="129"/>
+      <c r="E14" s="129"/>
+      <c r="F14" s="129"/>
+      <c r="G14" s="130"/>
     </row>
     <row r="15" spans="1:14" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="58" t="s">
@@ -4584,7 +4587,7 @@
         <f>SUMIFS(D2:D11,C2:C11,"Salaries",F2:F11,"East",A2:A11,"&gt;=01-Feb-2025",A2:A11,"&lt;=28-Feb-2025")</f>
         <v>4800</v>
       </c>
-      <c r="L13" s="134"/>
+      <c r="L13" s="94"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="92"/>
@@ -4829,6 +4832,10 @@
       <c r="I6" s="65" t="s">
         <v>207</v>
       </c>
+      <c r="J6" s="65">
+        <f>COUNTIF(D2:D11,"&gt;500")</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="65" t="s">
@@ -4849,6 +4856,10 @@
       <c r="I7" s="65" t="s">
         <v>204</v>
       </c>
+      <c r="J7" s="65">
+        <f>COUNTIF(D2:D11,"&lt;400")</f>
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="65" t="s">
@@ -4986,17 +4997,17 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A24" s="132" t="s">
+      <c r="A24" s="133" t="s">
         <v>224</v>
       </c>
-      <c r="B24" s="133"/>
-      <c r="C24" s="133"/>
-      <c r="D24" s="133"/>
-      <c r="E24" s="133"/>
-      <c r="F24" s="133"/>
-      <c r="G24" s="133"/>
-      <c r="H24" s="133"/>
-      <c r="I24" s="133"/>
+      <c r="B24" s="134"/>
+      <c r="C24" s="134"/>
+      <c r="D24" s="134"/>
+      <c r="E24" s="134"/>
+      <c r="F24" s="134"/>
+      <c r="G24" s="134"/>
+      <c r="H24" s="134"/>
+      <c r="I24" s="134"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5011,7 +5022,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{116B6492-7E8B-47E0-8222-5EB871C51B32}">
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.109375" style="65" bestFit="1" customWidth="1"/>
@@ -5026,7 +5037,7 @@
     <col min="11" max="16384" width="8.77734375" style="65"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="88" t="s">
         <v>225</v>
       </c>
@@ -5052,7 +5063,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="65">
         <v>101</v>
       </c>
@@ -5079,7 +5090,7 @@
         <v>David Chen</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="65">
         <v>102</v>
       </c>
@@ -5101,8 +5112,16 @@
       <c r="I3" s="65" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J3" s="65" t="str">
+        <f>VLOOKUP(A7,A2:F11,3,0)</f>
+        <v>Marketing</v>
+      </c>
+      <c r="K3" s="65" t="str">
+        <f>VLOOKUP(106,A2:F11,3,0)</f>
+        <v>Marketing</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="65">
         <v>103</v>
       </c>
@@ -5124,8 +5143,12 @@
       <c r="I4" s="65" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J4" s="65">
+        <f>VLOOKUP(102,A2:F11,5,0)</f>
+        <v>72000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="65">
         <v>104</v>
       </c>
@@ -5147,8 +5170,12 @@
       <c r="I5" s="65" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J5" s="65">
+        <f>VLOOKUP(109,A2:F11,6,0)</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="65">
         <v>105</v>
       </c>
@@ -5170,8 +5197,12 @@
       <c r="I6" s="65" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J6" s="65" t="str">
+        <f>VLOOKUP(101,A2:F11,4,0)</f>
+        <v>New York</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="65">
         <v>106</v>
       </c>
@@ -5194,7 +5225,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="65">
         <v>107</v>
       </c>
@@ -5217,7 +5248,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="65">
         <v>108</v>
       </c>
@@ -5240,7 +5271,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="65">
         <v>109</v>
       </c>
@@ -5263,7 +5294,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="65">
         <v>110</v>
       </c>
@@ -5286,27 +5317,27 @@
         <v>255</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="I12" s="65" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="I13" s="65" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="I14" s="65" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="I15" s="65" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="I16" s="65" t="s">
         <v>260</v>
       </c>
@@ -5337,17 +5368,17 @@
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A25" s="132" t="s">
+      <c r="A25" s="133" t="s">
         <v>266</v>
       </c>
-      <c r="B25" s="133"/>
-      <c r="C25" s="133"/>
-      <c r="D25" s="133"/>
-      <c r="E25" s="133"/>
-      <c r="F25" s="133"/>
-      <c r="G25" s="133"/>
-      <c r="H25" s="133"/>
-      <c r="I25" s="133"/>
+      <c r="B25" s="134"/>
+      <c r="C25" s="134"/>
+      <c r="D25" s="134"/>
+      <c r="E25" s="134"/>
+      <c r="F25" s="134"/>
+      <c r="G25" s="134"/>
+      <c r="H25" s="134"/>
+      <c r="I25" s="134"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5362,8 +5393,8 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F9F5792-D527-4DAE-8F40-0C8A70D97254}">
-  <dimension ref="A1:N24"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K24"/>
+  <sheetFormatPr defaultColWidth="11.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.88671875" style="65" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.6640625" style="65" bestFit="1" customWidth="1"/>
@@ -5372,16 +5403,13 @@
     <col min="6" max="6" width="9.77734375" style="65" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" style="65" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="8.88671875" style="65" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.44140625" style="65" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="37.109375" style="65" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.33203125" style="65" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.21875" style="65" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="2" style="65" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="56.21875" style="65" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="37.109375" style="65" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.88671875" style="65"/>
+    <col min="12" max="16384" width="11.6640625" style="65"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="88" t="s">
         <v>267</v>
       </c>
@@ -5415,17 +5443,8 @@
       <c r="K1" s="88" t="s">
         <v>277</v>
       </c>
-      <c r="L1" s="88">
-        <v>0</v>
-      </c>
-      <c r="M1" s="88" t="s">
-        <v>219</v>
-      </c>
-      <c r="N1" s="88" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="65" t="s">
         <v>225</v>
       </c>
@@ -5460,7 +5479,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3" s="65" t="s">
         <v>226</v>
       </c>
@@ -5495,7 +5514,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4" s="65" t="s">
         <v>42</v>
       </c>
@@ -5530,7 +5549,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" s="65" t="s">
         <v>227</v>
       </c>
@@ -5565,7 +5584,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
         <v>228</v>
       </c>
@@ -5600,7 +5619,7 @@
         <v>85000</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="65" t="s">
         <v>229</v>
       </c>
@@ -5635,103 +5654,155 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M9" s="65" t="s">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D12" s="135" t="s">
         <v>278</v>
       </c>
-      <c r="N9" s="65" t="str">
+      <c r="E12" s="135"/>
+      <c r="F12" s="135"/>
+      <c r="G12" s="135"/>
+      <c r="H12" s="135"/>
+      <c r="I12" s="65" t="str">
         <f>HLOOKUP(104, B2:K6, 2, FALSE)</f>
         <v>David Chen</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M10" s="65" t="s">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D13" s="135" t="s">
         <v>279</v>
       </c>
-      <c r="N10" s="65">
+      <c r="E13" s="135"/>
+      <c r="F13" s="135"/>
+      <c r="G13" s="135"/>
+      <c r="H13" s="135"/>
+      <c r="I13" s="65" t="str">
+        <f>HLOOKUP(106,B2:K7,3,0)</f>
+        <v>Marketing</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D14" s="135" t="s">
+        <v>280</v>
+      </c>
+      <c r="E14" s="135"/>
+      <c r="F14" s="135"/>
+      <c r="G14" s="135"/>
+      <c r="H14" s="135"/>
+      <c r="I14" s="65">
+        <f>HLOOKUP(102,B2:K7,5,0)</f>
+        <v>72000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D15" s="135" t="s">
+        <v>281</v>
+      </c>
+      <c r="E15" s="135"/>
+      <c r="F15" s="135"/>
+      <c r="G15" s="135"/>
+      <c r="H15" s="135"/>
+      <c r="I15" s="65">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M11" s="65" t="s">
-        <v>280</v>
-      </c>
-      <c r="N11" s="65">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D16" s="135" t="s">
+        <v>282</v>
+      </c>
+      <c r="E16" s="135"/>
+      <c r="F16" s="135"/>
+      <c r="G16" s="135"/>
+      <c r="H16" s="135"/>
+      <c r="I16" s="65">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M12" s="65" t="s">
-        <v>281</v>
-      </c>
-      <c r="N12" s="65">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D17" s="135" t="s">
+        <v>283</v>
+      </c>
+      <c r="E17" s="135"/>
+      <c r="F17" s="135"/>
+      <c r="G17" s="135"/>
+      <c r="H17" s="135"/>
+      <c r="I17" s="65">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M13" s="65" t="s">
-        <v>282</v>
-      </c>
-      <c r="N13" s="65">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D18" s="135" t="s">
+        <v>284</v>
+      </c>
+      <c r="E18" s="135"/>
+      <c r="F18" s="135"/>
+      <c r="G18" s="135"/>
+      <c r="H18" s="135"/>
+      <c r="I18" s="65">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M14" s="65" t="s">
-        <v>283</v>
-      </c>
-      <c r="N14" s="65">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D19" s="135" t="s">
+        <v>285</v>
+      </c>
+      <c r="E19" s="135"/>
+      <c r="F19" s="135"/>
+      <c r="G19" s="135"/>
+      <c r="H19" s="135"/>
+      <c r="I19" s="65" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D20" s="135" t="s">
+        <v>287</v>
+      </c>
+      <c r="E20" s="135"/>
+      <c r="F20" s="135"/>
+      <c r="G20" s="135"/>
+      <c r="H20" s="135"/>
+      <c r="I20" s="65">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M15" s="65" t="s">
-        <v>284</v>
-      </c>
-      <c r="N15" s="65">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D21" s="135" t="s">
+        <v>288</v>
+      </c>
+      <c r="E21" s="135"/>
+      <c r="F21" s="135"/>
+      <c r="G21" s="135"/>
+      <c r="H21" s="135"/>
+      <c r="I21" s="65">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M16" s="65" t="s">
-        <v>285</v>
-      </c>
-      <c r="N16" s="65" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M17" s="65" t="s">
-        <v>287</v>
-      </c>
-      <c r="N17" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M18" s="65" t="s">
-        <v>288</v>
-      </c>
-      <c r="N18" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A24" s="132" t="s">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="133" t="s">
         <v>289</v>
       </c>
-      <c r="B24" s="133"/>
-      <c r="C24" s="133"/>
-      <c r="D24" s="133"/>
-      <c r="E24" s="133"/>
-      <c r="F24" s="133"/>
-      <c r="G24" s="133"/>
-      <c r="H24" s="133"/>
-      <c r="I24" s="133"/>
+      <c r="B24" s="134"/>
+      <c r="C24" s="134"/>
+      <c r="D24" s="134"/>
+      <c r="E24" s="134"/>
+      <c r="F24" s="134"/>
+      <c r="G24" s="134"/>
+      <c r="H24" s="134"/>
+      <c r="I24" s="134"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="11">
     <mergeCell ref="A24:I24"/>
+    <mergeCell ref="D12:H12"/>
+    <mergeCell ref="D13:H13"/>
+    <mergeCell ref="D14:H14"/>
+    <mergeCell ref="D15:H15"/>
+    <mergeCell ref="D16:H16"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D18:H18"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="D20:H20"/>
+    <mergeCell ref="D21:H21"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A24" r:id="rId1" xr:uid="{9C1324F4-AF41-44EA-9993-7DB6909778ED}"/>
@@ -5745,9 +5816,9 @@
   <dimension ref="A1:I23"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="39.21875" style="65" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.6640625" style="65" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.77734375" style="65" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.109375" style="65" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.21875" style="65" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" style="65" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.44140625" style="65" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="5" style="65" bestFit="1" customWidth="1"/>
     <col min="6" max="16384" width="8.88671875" style="65"/>
@@ -5899,6 +5970,10 @@
       <c r="A12" s="65" t="s">
         <v>297</v>
       </c>
+      <c r="B12" s="65" t="str">
+        <f>INDEX(C2:C6,MATCH("Monitor",B2:B6,))</f>
+        <v>Electronics</v>
+      </c>
       <c r="C12" s="65" t="s">
         <v>23</v>
       </c>
@@ -5960,17 +6035,17 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="132" t="s">
+      <c r="A23" s="133" t="s">
         <v>305</v>
       </c>
-      <c r="B23" s="133"/>
-      <c r="C23" s="133"/>
-      <c r="D23" s="133"/>
-      <c r="E23" s="133"/>
-      <c r="F23" s="133"/>
-      <c r="G23" s="133"/>
-      <c r="H23" s="133"/>
-      <c r="I23" s="133"/>
+      <c r="B23" s="134"/>
+      <c r="C23" s="134"/>
+      <c r="D23" s="134"/>
+      <c r="E23" s="134"/>
+      <c r="F23" s="134"/>
+      <c r="G23" s="134"/>
+      <c r="H23" s="134"/>
+      <c r="I23" s="134"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Practice_file.xlsx
+++ b/Practice_file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d58d4d655bee1e81/Desktop/Github/Practice_Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="230" documentId="11_F25DC773A252ABDACC1048BD89DC52D45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96C385BB-B0EE-41F3-B4BE-24138FD23D9D}"/>
+  <xr:revisionPtr revIDLastSave="245" documentId="11_F25DC773A252ABDACC1048BD89DC52D45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CEEE60B1-52D3-4450-8E75-19481F5BF597}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SUMIF,AVGIF" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -1666,6 +1666,66 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1677,66 +1737,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2534,15 +2534,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="107" t="s">
+      <c r="A1" s="97" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="108"/>
-      <c r="C1" s="108"/>
-      <c r="D1" s="108"/>
-      <c r="E1" s="108"/>
-      <c r="F1" s="108"/>
-      <c r="G1" s="109"/>
+      <c r="B1" s="98"/>
+      <c r="C1" s="98"/>
+      <c r="D1" s="98"/>
+      <c r="E1" s="98"/>
+      <c r="F1" s="98"/>
+      <c r="G1" s="99"/>
       <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -2783,15 +2783,15 @@
     </row>
     <row r="15" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="16" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="107" t="s">
+      <c r="A16" s="97" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="108"/>
-      <c r="C16" s="108"/>
-      <c r="D16" s="108"/>
-      <c r="E16" s="108"/>
-      <c r="F16" s="119"/>
-      <c r="G16" s="119"/>
+      <c r="B16" s="98"/>
+      <c r="C16" s="98"/>
+      <c r="D16" s="98"/>
+      <c r="E16" s="98"/>
+      <c r="F16" s="109"/>
+      <c r="G16" s="109"/>
     </row>
     <row r="17" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="24" t="s">
@@ -2839,10 +2839,10 @@
         <f>COUNTIF(B18:B27,"&gt;30")</f>
         <v>6</v>
       </c>
-      <c r="H18" s="101" t="s">
+      <c r="H18" s="110" t="s">
         <v>70</v>
       </c>
-      <c r="I18" s="102"/>
+      <c r="I18" s="111"/>
     </row>
     <row r="19" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A19" s="29" t="s">
@@ -2867,10 +2867,10 @@
         <f>COUNTIF(E18:E27,"Male")</f>
         <v>5</v>
       </c>
-      <c r="H19" s="101" t="s">
+      <c r="H19" s="110" t="s">
         <v>71</v>
       </c>
-      <c r="I19" s="102"/>
+      <c r="I19" s="111"/>
     </row>
     <row r="20" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A20" s="29" t="s">
@@ -3026,16 +3026,16 @@
     </row>
     <row r="30" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="31" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A31" s="110" t="s">
+      <c r="A31" s="100" t="s">
         <v>60</v>
       </c>
-      <c r="B31" s="111"/>
-      <c r="C31" s="111"/>
-      <c r="D31" s="111"/>
-      <c r="E31" s="111"/>
-      <c r="F31" s="111"/>
-      <c r="G31" s="111"/>
-      <c r="H31" s="112"/>
+      <c r="B31" s="101"/>
+      <c r="C31" s="101"/>
+      <c r="D31" s="101"/>
+      <c r="E31" s="101"/>
+      <c r="F31" s="101"/>
+      <c r="G31" s="101"/>
+      <c r="H31" s="102"/>
     </row>
     <row r="32" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="39" t="s">
@@ -3051,9 +3051,9 @@
         <v>62</v>
       </c>
       <c r="E32" s="40"/>
-      <c r="F32" s="103"/>
-      <c r="G32" s="104"/>
-      <c r="H32" s="105"/>
+      <c r="F32" s="112"/>
+      <c r="G32" s="113"/>
+      <c r="H32" s="114"/>
     </row>
     <row r="33" spans="1:10" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="29" t="s">
@@ -3072,15 +3072,15 @@
         <f>COUNTIF(D33:D51,"Pending")</f>
         <v>7</v>
       </c>
-      <c r="F33" s="113" t="s">
+      <c r="F33" s="103" t="s">
         <v>69</v>
       </c>
-      <c r="G33" s="114"/>
-      <c r="H33" s="115"/>
-      <c r="I33" s="106" t="s">
+      <c r="G33" s="104"/>
+      <c r="H33" s="105"/>
+      <c r="I33" s="115" t="s">
         <v>72</v>
       </c>
-      <c r="J33" s="102"/>
+      <c r="J33" s="111"/>
     </row>
     <row r="34" spans="1:10" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="29" t="s">
@@ -3099,15 +3099,15 @@
         <f>COUNTIFS(B33:B51,"West",D33:D51,"Delivered")</f>
         <v>3</v>
       </c>
-      <c r="F34" s="116" t="s">
+      <c r="F34" s="106" t="s">
         <v>73</v>
       </c>
-      <c r="G34" s="117"/>
-      <c r="H34" s="118"/>
-      <c r="I34" s="98" t="s">
+      <c r="G34" s="107"/>
+      <c r="H34" s="108"/>
+      <c r="I34" s="118" t="s">
         <v>74</v>
       </c>
-      <c r="J34" s="98"/>
+      <c r="J34" s="118"/>
     </row>
     <row r="35" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="29" t="s">
@@ -3123,11 +3123,11 @@
         <v>64</v>
       </c>
       <c r="E35" s="25"/>
-      <c r="F35" s="100"/>
-      <c r="G35" s="100"/>
-      <c r="H35" s="100"/>
-      <c r="I35" s="99"/>
-      <c r="J35" s="98"/>
+      <c r="F35" s="96"/>
+      <c r="G35" s="96"/>
+      <c r="H35" s="96"/>
+      <c r="I35" s="119"/>
+      <c r="J35" s="118"/>
     </row>
     <row r="36" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A36" s="29" t="s">
@@ -3143,11 +3143,11 @@
         <v>64</v>
       </c>
       <c r="E36" s="25"/>
-      <c r="F36" s="100"/>
-      <c r="G36" s="100"/>
-      <c r="H36" s="100"/>
-      <c r="I36" s="96"/>
-      <c r="J36" s="97"/>
+      <c r="F36" s="96"/>
+      <c r="G36" s="96"/>
+      <c r="H36" s="96"/>
+      <c r="I36" s="116"/>
+      <c r="J36" s="117"/>
     </row>
     <row r="37" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="29" t="s">
@@ -3163,11 +3163,11 @@
         <v>66</v>
       </c>
       <c r="E37" s="25"/>
-      <c r="F37" s="100"/>
-      <c r="G37" s="100"/>
-      <c r="H37" s="100"/>
-      <c r="I37" s="96"/>
-      <c r="J37" s="97"/>
+      <c r="F37" s="96"/>
+      <c r="G37" s="96"/>
+      <c r="H37" s="96"/>
+      <c r="I37" s="116"/>
+      <c r="J37" s="117"/>
     </row>
     <row r="38" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A38" s="29" t="s">
@@ -3183,11 +3183,11 @@
         <v>64</v>
       </c>
       <c r="E38" s="25"/>
-      <c r="F38" s="100"/>
-      <c r="G38" s="100"/>
-      <c r="H38" s="100"/>
-      <c r="I38" s="96"/>
-      <c r="J38" s="97"/>
+      <c r="F38" s="96"/>
+      <c r="G38" s="96"/>
+      <c r="H38" s="96"/>
+      <c r="I38" s="116"/>
+      <c r="J38" s="117"/>
     </row>
     <row r="39" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="29" t="s">
@@ -3203,11 +3203,11 @@
         <v>64</v>
       </c>
       <c r="E39" s="25"/>
-      <c r="F39" s="100"/>
-      <c r="G39" s="100"/>
-      <c r="H39" s="100"/>
-      <c r="I39" s="96"/>
-      <c r="J39" s="97"/>
+      <c r="F39" s="96"/>
+      <c r="G39" s="96"/>
+      <c r="H39" s="96"/>
+      <c r="I39" s="116"/>
+      <c r="J39" s="117"/>
     </row>
     <row r="40" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A40" s="29" t="s">
@@ -3223,11 +3223,11 @@
         <v>66</v>
       </c>
       <c r="E40" s="25"/>
-      <c r="F40" s="100"/>
-      <c r="G40" s="100"/>
-      <c r="H40" s="100"/>
-      <c r="I40" s="96"/>
-      <c r="J40" s="97"/>
+      <c r="F40" s="96"/>
+      <c r="G40" s="96"/>
+      <c r="H40" s="96"/>
+      <c r="I40" s="116"/>
+      <c r="J40" s="117"/>
     </row>
     <row r="41" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A41" s="29" t="s">
@@ -3243,11 +3243,11 @@
         <v>64</v>
       </c>
       <c r="E41" s="25"/>
-      <c r="F41" s="100"/>
-      <c r="G41" s="100"/>
-      <c r="H41" s="100"/>
-      <c r="I41" s="96"/>
-      <c r="J41" s="97"/>
+      <c r="F41" s="96"/>
+      <c r="G41" s="96"/>
+      <c r="H41" s="96"/>
+      <c r="I41" s="116"/>
+      <c r="J41" s="117"/>
     </row>
     <row r="42" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A42" s="29" t="s">
@@ -3263,11 +3263,11 @@
         <v>66</v>
       </c>
       <c r="E42" s="25"/>
-      <c r="F42" s="100"/>
-      <c r="G42" s="100"/>
-      <c r="H42" s="100"/>
-      <c r="I42" s="96"/>
-      <c r="J42" s="97"/>
+      <c r="F42" s="96"/>
+      <c r="G42" s="96"/>
+      <c r="H42" s="96"/>
+      <c r="I42" s="116"/>
+      <c r="J42" s="117"/>
     </row>
     <row r="43" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="29" t="s">
@@ -3283,11 +3283,11 @@
         <v>64</v>
       </c>
       <c r="E43" s="25"/>
-      <c r="F43" s="100"/>
-      <c r="G43" s="100"/>
-      <c r="H43" s="100"/>
-      <c r="I43" s="96"/>
-      <c r="J43" s="97"/>
+      <c r="F43" s="96"/>
+      <c r="G43" s="96"/>
+      <c r="H43" s="96"/>
+      <c r="I43" s="116"/>
+      <c r="J43" s="117"/>
     </row>
     <row r="44" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A44" s="29" t="s">
@@ -3303,11 +3303,11 @@
         <v>64</v>
       </c>
       <c r="E44" s="25"/>
-      <c r="F44" s="100"/>
-      <c r="G44" s="100"/>
-      <c r="H44" s="100"/>
-      <c r="I44" s="96"/>
-      <c r="J44" s="97"/>
+      <c r="F44" s="96"/>
+      <c r="G44" s="96"/>
+      <c r="H44" s="96"/>
+      <c r="I44" s="116"/>
+      <c r="J44" s="117"/>
     </row>
     <row r="45" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A45" s="29" t="s">
@@ -3323,9 +3323,9 @@
         <v>66</v>
       </c>
       <c r="E45" s="25"/>
-      <c r="F45" s="100"/>
-      <c r="G45" s="100"/>
-      <c r="H45" s="100"/>
+      <c r="F45" s="96"/>
+      <c r="G45" s="96"/>
+      <c r="H45" s="96"/>
     </row>
     <row r="46" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A46" s="29" t="s">
@@ -3341,9 +3341,9 @@
         <v>64</v>
       </c>
       <c r="E46" s="25"/>
-      <c r="F46" s="100"/>
-      <c r="G46" s="100"/>
-      <c r="H46" s="100"/>
+      <c r="F46" s="96"/>
+      <c r="G46" s="96"/>
+      <c r="H46" s="96"/>
     </row>
     <row r="47" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A47" s="29" t="s">
@@ -3359,9 +3359,9 @@
         <v>66</v>
       </c>
       <c r="E47" s="25"/>
-      <c r="F47" s="100"/>
-      <c r="G47" s="100"/>
-      <c r="H47" s="100"/>
+      <c r="F47" s="96"/>
+      <c r="G47" s="96"/>
+      <c r="H47" s="96"/>
     </row>
     <row r="48" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="29" t="s">
@@ -3377,9 +3377,9 @@
         <v>64</v>
       </c>
       <c r="E48" s="25"/>
-      <c r="F48" s="100"/>
-      <c r="G48" s="100"/>
-      <c r="H48" s="100"/>
+      <c r="F48" s="96"/>
+      <c r="G48" s="96"/>
+      <c r="H48" s="96"/>
     </row>
     <row r="49" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="29" t="s">
@@ -3395,9 +3395,9 @@
         <v>64</v>
       </c>
       <c r="E49" s="25"/>
-      <c r="F49" s="100"/>
-      <c r="G49" s="100"/>
-      <c r="H49" s="100"/>
+      <c r="F49" s="96"/>
+      <c r="G49" s="96"/>
+      <c r="H49" s="96"/>
     </row>
     <row r="50" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A50" s="29" t="s">
@@ -3413,9 +3413,9 @@
         <v>66</v>
       </c>
       <c r="E50" s="25"/>
-      <c r="F50" s="100"/>
-      <c r="G50" s="100"/>
-      <c r="H50" s="100"/>
+      <c r="F50" s="96"/>
+      <c r="G50" s="96"/>
+      <c r="H50" s="96"/>
     </row>
     <row r="51" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="29" t="s">
@@ -3431,22 +3431,22 @@
         <v>64</v>
       </c>
       <c r="E51" s="25"/>
-      <c r="F51" s="100"/>
-      <c r="G51" s="100"/>
-      <c r="H51" s="100"/>
+      <c r="F51" s="96"/>
+      <c r="G51" s="96"/>
+      <c r="H51" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="I34:J35"/>
+    <mergeCell ref="I36:J36"/>
+    <mergeCell ref="I37:J37"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="I41:J41"/>
     <mergeCell ref="F48:H48"/>
     <mergeCell ref="F49:H49"/>
     <mergeCell ref="F50:H50"/>
@@ -3463,16 +3463,16 @@
     <mergeCell ref="F47:H47"/>
     <mergeCell ref="F36:H36"/>
     <mergeCell ref="F37:H37"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="I34:J35"/>
-    <mergeCell ref="I36:J36"/>
-    <mergeCell ref="I37:J37"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="A16:G16"/>
   </mergeCells>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5393,23 +5393,15 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F9F5792-D527-4DAE-8F40-0C8A70D97254}">
-  <dimension ref="A1:K24"/>
-  <sheetFormatPr defaultColWidth="11.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:Q24"/>
+  <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.88671875" style="65" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.6640625" style="65" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9" style="65" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="9.6640625" style="65" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.77734375" style="65" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9" style="65" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.88671875" style="65" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="37.109375" style="65" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.33203125" style="65" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.21875" style="65" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="11.6640625" style="65"/>
+    <col min="1" max="1" width="12.21875" style="65" customWidth="1"/>
+    <col min="2" max="11" width="11" style="65" customWidth="1"/>
+    <col min="12" max="16384" width="10.33203125" style="65"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="88" t="s">
         <v>267</v>
       </c>
@@ -5444,7 +5436,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="65" t="s">
         <v>225</v>
       </c>
@@ -5479,7 +5471,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" s="65" t="s">
         <v>226</v>
       </c>
@@ -5514,7 +5506,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="65" t="s">
         <v>42</v>
       </c>
@@ -5549,7 +5541,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="65" t="s">
         <v>227</v>
       </c>
@@ -5584,7 +5576,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="65" t="s">
         <v>228</v>
       </c>
@@ -5619,7 +5611,7 @@
         <v>85000</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="65" t="s">
         <v>229</v>
       </c>
@@ -5654,130 +5646,119 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D12" s="135" t="s">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="L15" s="135" t="s">
         <v>278</v>
       </c>
-      <c r="E12" s="135"/>
-      <c r="F12" s="135"/>
-      <c r="G12" s="135"/>
-      <c r="H12" s="135"/>
-      <c r="I12" s="65" t="str">
+      <c r="M15" s="135"/>
+      <c r="N15" s="135"/>
+      <c r="O15" s="135"/>
+      <c r="P15" s="135"/>
+      <c r="Q15" s="65" t="str">
         <f>HLOOKUP(104, B2:K6, 2, FALSE)</f>
         <v>David Chen</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D13" s="135" t="s">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="L16" s="135" t="s">
         <v>279</v>
       </c>
-      <c r="E13" s="135"/>
-      <c r="F13" s="135"/>
-      <c r="G13" s="135"/>
-      <c r="H13" s="135"/>
-      <c r="I13" s="65" t="str">
+      <c r="M16" s="135"/>
+      <c r="N16" s="135"/>
+      <c r="O16" s="135"/>
+      <c r="P16" s="135"/>
+      <c r="Q16" s="65" t="str">
         <f>HLOOKUP(106,B2:K7,3,0)</f>
         <v>Marketing</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D14" s="135" t="s">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="L17" s="135" t="s">
         <v>280</v>
       </c>
-      <c r="E14" s="135"/>
-      <c r="F14" s="135"/>
-      <c r="G14" s="135"/>
-      <c r="H14" s="135"/>
-      <c r="I14" s="65">
+      <c r="M17" s="135"/>
+      <c r="N17" s="135"/>
+      <c r="O17" s="135"/>
+      <c r="P17" s="135"/>
+      <c r="Q17" s="65">
         <f>HLOOKUP(102,B2:K7,5,0)</f>
         <v>72000</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D15" s="135" t="s">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="L18" s="135" t="s">
         <v>281</v>
       </c>
-      <c r="E15" s="135"/>
-      <c r="F15" s="135"/>
-      <c r="G15" s="135"/>
-      <c r="H15" s="135"/>
-      <c r="I15" s="65">
+      <c r="M18" s="135"/>
+      <c r="N18" s="135"/>
+      <c r="O18" s="135"/>
+      <c r="P18" s="135"/>
+      <c r="Q18" s="65">
+        <f>HLOOKUP(109,B2:K7,6,0)</f>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="L19" s="135" t="s">
+        <v>282</v>
+      </c>
+      <c r="M19" s="135"/>
+      <c r="N19" s="135"/>
+      <c r="O19" s="135"/>
+      <c r="P19" s="135"/>
+      <c r="Q19" s="65">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="D16" s="135" t="s">
-        <v>282</v>
-      </c>
-      <c r="E16" s="135"/>
-      <c r="F16" s="135"/>
-      <c r="G16" s="135"/>
-      <c r="H16" s="135"/>
-      <c r="I16" s="65">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="L20" s="135" t="s">
+        <v>283</v>
+      </c>
+      <c r="M20" s="135"/>
+      <c r="N20" s="135"/>
+      <c r="O20" s="135"/>
+      <c r="P20" s="135"/>
+      <c r="Q20" s="65">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D17" s="135" t="s">
-        <v>283</v>
-      </c>
-      <c r="E17" s="135"/>
-      <c r="F17" s="135"/>
-      <c r="G17" s="135"/>
-      <c r="H17" s="135"/>
-      <c r="I17" s="65">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="L21" s="135" t="s">
+        <v>284</v>
+      </c>
+      <c r="M21" s="135"/>
+      <c r="N21" s="135"/>
+      <c r="O21" s="135"/>
+      <c r="P21" s="135"/>
+      <c r="Q21" s="65">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D18" s="135" t="s">
-        <v>284</v>
-      </c>
-      <c r="E18" s="135"/>
-      <c r="F18" s="135"/>
-      <c r="G18" s="135"/>
-      <c r="H18" s="135"/>
-      <c r="I18" s="65">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="L22" s="135" t="s">
+        <v>285</v>
+      </c>
+      <c r="M22" s="135"/>
+      <c r="N22" s="135"/>
+      <c r="O22" s="135"/>
+      <c r="P22" s="135"/>
+      <c r="Q22" s="65" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="L23" s="135" t="s">
+        <v>287</v>
+      </c>
+      <c r="M23" s="135"/>
+      <c r="N23" s="135"/>
+      <c r="O23" s="135"/>
+      <c r="P23" s="135"/>
+      <c r="Q23" s="65">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D19" s="135" t="s">
-        <v>285</v>
-      </c>
-      <c r="E19" s="135"/>
-      <c r="F19" s="135"/>
-      <c r="G19" s="135"/>
-      <c r="H19" s="135"/>
-      <c r="I19" s="65" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D20" s="135" t="s">
-        <v>287</v>
-      </c>
-      <c r="E20" s="135"/>
-      <c r="F20" s="135"/>
-      <c r="G20" s="135"/>
-      <c r="H20" s="135"/>
-      <c r="I20" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D21" s="135" t="s">
-        <v>288</v>
-      </c>
-      <c r="E21" s="135"/>
-      <c r="F21" s="135"/>
-      <c r="G21" s="135"/>
-      <c r="H21" s="135"/>
-      <c r="I21" s="65">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A24" s="133" t="s">
         <v>289</v>
       </c>
@@ -5789,20 +5770,30 @@
       <c r="G24" s="134"/>
       <c r="H24" s="134"/>
       <c r="I24" s="134"/>
+      <c r="L24" s="135" t="s">
+        <v>288</v>
+      </c>
+      <c r="M24" s="135"/>
+      <c r="N24" s="135"/>
+      <c r="O24" s="135"/>
+      <c r="P24" s="135"/>
+      <c r="Q24" s="65">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="A24:I24"/>
-    <mergeCell ref="D12:H12"/>
-    <mergeCell ref="D13:H13"/>
-    <mergeCell ref="D14:H14"/>
-    <mergeCell ref="D15:H15"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D18:H18"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D20:H20"/>
-    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="L15:P15"/>
+    <mergeCell ref="L16:P16"/>
+    <mergeCell ref="L17:P17"/>
+    <mergeCell ref="L18:P18"/>
+    <mergeCell ref="L19:P19"/>
+    <mergeCell ref="L20:P20"/>
+    <mergeCell ref="L21:P21"/>
+    <mergeCell ref="L22:P22"/>
+    <mergeCell ref="L23:P23"/>
+    <mergeCell ref="L24:P24"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A24" r:id="rId1" xr:uid="{9C1324F4-AF41-44EA-9993-7DB6909778ED}"/>
@@ -5971,7 +5962,7 @@
         <v>297</v>
       </c>
       <c r="B12" s="65" t="str">
-        <f>INDEX(C2:C6,MATCH("Monitor",B2:B6,))</f>
+        <f>INDEX(C2:C6,MATCH("Monitor",B2:B6,0))</f>
         <v>Electronics</v>
       </c>
       <c r="C12" s="65" t="s">
@@ -5982,6 +5973,10 @@
       <c r="A13" s="65" t="s">
         <v>298</v>
       </c>
+      <c r="B13" s="65">
+        <f>INDEX(E2:E6,MATCH(101,A2:A6,0))</f>
+        <v>5000</v>
+      </c>
       <c r="C13" s="65">
         <v>5000</v>
       </c>
@@ -5990,6 +5985,10 @@
       <c r="A14" s="65" t="s">
         <v>299</v>
       </c>
+      <c r="B14" s="65" t="str">
+        <f>INDEX(B2:B6,MATCH("East",D2:D6,0))</f>
+        <v>Chair</v>
+      </c>
       <c r="C14" s="65" t="s">
         <v>291</v>
       </c>
@@ -5998,6 +5997,10 @@
       <c r="A15" s="65" t="s">
         <v>300</v>
       </c>
+      <c r="B15" s="65" t="str">
+        <f>INDEX(D2:D6,MATCH("Chair",B2:B6,0))</f>
+        <v>East</v>
+      </c>
       <c r="C15" s="65" t="s">
         <v>26</v>
       </c>
@@ -6005,6 +6008,10 @@
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="65" t="s">
         <v>301</v>
+      </c>
+      <c r="B16" s="65">
+        <f>INDEX(E2:E6,MATCH(105,A2:A6,0))</f>
+        <v>4000</v>
       </c>
       <c r="C16" s="65">
         <v>4000</v>

--- a/Practice_file.xlsx
+++ b/Practice_file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d58d4d655bee1e81/Desktop/Github/Practice_Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="245" documentId="11_F25DC773A252ABDACC1048BD89DC52D45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CEEE60B1-52D3-4450-8E75-19481F5BF597}"/>
+  <xr:revisionPtr revIDLastSave="253" documentId="11_F25DC773A252ABDACC1048BD89DC52D45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91048442-4521-4952-A089-A7E54E868F67}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SUMIF,AVGIF" sheetId="1" r:id="rId1"/>
@@ -5224,6 +5224,10 @@
       <c r="I7" s="65" t="s">
         <v>247</v>
       </c>
+      <c r="J7" s="65">
+        <f>VLOOKUP(110,A2:F11,5,0)</f>
+        <v>85000</v>
+      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="65">
@@ -5247,6 +5251,10 @@
       <c r="I8" s="65" t="s">
         <v>249</v>
       </c>
+      <c r="J8" s="65" t="str">
+        <f>VLOOKUP(103,A2:F11,3,0)</f>
+        <v>IT</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="65">
@@ -5270,6 +5278,10 @@
       <c r="I9" s="65" t="s">
         <v>251</v>
       </c>
+      <c r="J9" s="65" t="str">
+        <f>INDEX(B2:B11,MATCH(62000,E2:E11,0))</f>
+        <v>Emily Davis</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10" s="65">
@@ -5293,6 +5305,10 @@
       <c r="I10" s="65" t="s">
         <v>253</v>
       </c>
+      <c r="J10" s="65">
+        <f>VLOOKUP(105,A2:F11,5,0)*(1+VLOOKUP(105,A2:F11,6,0))</f>
+        <v>68820</v>
+      </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11" s="65">
@@ -5316,58 +5332,102 @@
       <c r="I11" s="65" t="s">
         <v>255</v>
       </c>
+      <c r="J11" s="65" t="str">
+        <f>VLOOKUP(107,A2:F11,4,0)</f>
+        <v>San Diego</v>
+      </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="I12" s="65" t="s">
         <v>256</v>
       </c>
+      <c r="J12" s="65">
+        <f>VLOOKUP(102,A2:F11,5,0)*VLOOKUP(102,A2:F11,6,0)</f>
+        <v>8640</v>
+      </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="I13" s="65" t="s">
         <v>257</v>
       </c>
+      <c r="J13" s="65" t="str">
+        <f>VLOOKUP(108,A2:F11,3,0)</f>
+        <v>HR</v>
+      </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="I14" s="65" t="s">
         <v>258</v>
       </c>
+      <c r="J14" s="65" t="str">
+        <f>VLOOKUP(109,A2:F11,2,0)</f>
+        <v>Irene Scott</v>
+      </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="I15" s="65" t="s">
         <v>259</v>
       </c>
+      <c r="J15" s="65" cm="1">
+        <f t="array" ref="J15">INDEX(E2:E11,MATCH(1,(C2:C11="Finance")*(D2:D11="Boston"),0))</f>
+        <v>68000</v>
+      </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="I16" s="65" t="s">
         <v>260</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J16" s="65" t="str">
+        <f>VLOOKUP(101,A2:F11,3,0)</f>
+        <v>Finance</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="I17" s="65" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J17" s="65">
+        <f>VLOOKUP(110,A2:F11,6,0)</f>
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="I18" s="65" t="s">
         <v>262</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J18" s="65">
+        <f>VLOOKUP(103,A2:F11,5,0)*1.05</f>
+        <v>84000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="I19" s="65" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J19" s="65" t="str">
+        <f>VLOOKUP(105,A2:F11,4,0)</f>
+        <v>Chicago</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="I20" s="65" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J20" s="65" t="str">
+        <f>VLOOKUP(106,A2:F11,2,0)</f>
+        <v>Frank Lee</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="I21" s="65" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="J21" s="65">
+        <f>VLOOKUP(107,A2:F11,5)*(1+(VLOOKUP(107,A2:F11,6,0)))</f>
+        <v>87740</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="133" t="s">
         <v>266</v>
       </c>
@@ -5706,8 +5766,9 @@
       <c r="N19" s="135"/>
       <c r="O19" s="135"/>
       <c r="P19" s="135"/>
-      <c r="Q19" s="65">
-        <v>0</v>
+      <c r="Q19" s="65" t="str">
+        <f>HLOOKUP(101,B2:K7,4,0)</f>
+        <v>New York</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
@@ -5719,7 +5780,8 @@
       <c r="O20" s="135"/>
       <c r="P20" s="135"/>
       <c r="Q20" s="65">
-        <v>0</v>
+        <f>HLOOKUP(110,A2:K7,5,0)</f>
+        <v>85000</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
@@ -5730,8 +5792,9 @@
       <c r="N21" s="135"/>
       <c r="O21" s="135"/>
       <c r="P21" s="135"/>
-      <c r="Q21" s="65">
-        <v>0</v>
+      <c r="Q21" s="65" t="str">
+        <f>HLOOKUP(103,B2:K7,3,0)</f>
+        <v>IT</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">

--- a/Practice_file.xlsx
+++ b/Practice_file.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d58d4d655bee1e81/Desktop/Github/Practice_Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="253" documentId="11_F25DC773A252ABDACC1048BD89DC52D45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{91048442-4521-4952-A089-A7E54E868F67}"/>
+  <xr:revisionPtr revIDLastSave="275" documentId="11_F25DC773A252ABDACC1048BD89DC52D45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A04277C-047F-45F8-991E-0578B4C89E0E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,10 +18,11 @@
     <sheet name="V,HLOOKUP" sheetId="3" r:id="rId3"/>
     <sheet name="X,INDEX,MATCH" sheetId="4" r:id="rId4"/>
     <sheet name="Practice SUMIF" sheetId="5" r:id="rId5"/>
-    <sheet name="COUNTIF" sheetId="6" r:id="rId6"/>
-    <sheet name="VLOOKUP" sheetId="7" r:id="rId7"/>
-    <sheet name="HLOOKUP" sheetId="8" r:id="rId8"/>
-    <sheet name="INDEXMATCH" sheetId="9" r:id="rId9"/>
+    <sheet name="AVGIF" sheetId="12" r:id="rId6"/>
+    <sheet name="COUNTIF" sheetId="6" r:id="rId7"/>
+    <sheet name="VLOOKUP" sheetId="7" r:id="rId8"/>
+    <sheet name="HLOOKUP" sheetId="8" r:id="rId9"/>
+    <sheet name="INDEXMATCH" sheetId="9" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -69,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="308">
   <si>
     <t>Data for Practice</t>
   </si>
@@ -987,6 +988,12 @@
   </si>
   <si>
     <t>https://pivotxl.com/index-match-practice-exercises-xls-download/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Region </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sales </t>
   </si>
 </sst>
 </file>
@@ -1106,7 +1113,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1158,6 +1165,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1489,7 +1502,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="136">
+  <cellXfs count="139">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1785,6 +1798,15 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2521,6 +2543,269 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B5A70E6-D93D-44C4-88D6-4B03C3177468}">
+  <dimension ref="A1:I23"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="37.109375" style="65" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.21875" style="65" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.33203125" style="65" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.44140625" style="65" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5" style="65" bestFit="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.88671875" style="65"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="89" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="89" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1" s="89" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1" s="89" t="s">
+        <v>77</v>
+      </c>
+      <c r="D1" s="89" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="89" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="65">
+        <v>101</v>
+      </c>
+      <c r="B2" s="65" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="65" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="65">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="65">
+        <v>102</v>
+      </c>
+      <c r="B3" s="65" t="s">
+        <v>290</v>
+      </c>
+      <c r="C3" s="65" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="65" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="65">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="65">
+        <v>103</v>
+      </c>
+      <c r="B4" s="65" t="s">
+        <v>291</v>
+      </c>
+      <c r="C4" s="65" t="s">
+        <v>292</v>
+      </c>
+      <c r="D4" s="65" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="65">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="65">
+        <v>104</v>
+      </c>
+      <c r="B5" s="65" t="s">
+        <v>293</v>
+      </c>
+      <c r="C5" s="65" t="s">
+        <v>292</v>
+      </c>
+      <c r="D5" s="65" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="65">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="65">
+        <v>105</v>
+      </c>
+      <c r="B6" s="65" t="s">
+        <v>81</v>
+      </c>
+      <c r="C6" s="65" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="65">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" s="89" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="89" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" s="89" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="89" t="s">
+        <v>219</v>
+      </c>
+      <c r="B9" s="89" t="s">
+        <v>218</v>
+      </c>
+      <c r="C9" s="89" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="65" t="s">
+        <v>295</v>
+      </c>
+      <c r="B10" s="65">
+        <f>INDEX(E2:E6, MATCH("Phone", B2:B6, 0))</f>
+        <v>3000</v>
+      </c>
+      <c r="C10" s="65">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="65" t="s">
+        <v>296</v>
+      </c>
+      <c r="B11" s="65" t="str">
+        <f>INDEX(D2:D6, MATCH(104, A2:A6, 0))</f>
+        <v>West</v>
+      </c>
+      <c r="C11" s="65" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="65" t="s">
+        <v>297</v>
+      </c>
+      <c r="B12" s="65" t="str">
+        <f>INDEX(C2:C6,MATCH("Monitor",B2:B6,0))</f>
+        <v>Electronics</v>
+      </c>
+      <c r="C12" s="65" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="65" t="s">
+        <v>298</v>
+      </c>
+      <c r="B13" s="65">
+        <f>INDEX(E2:E6,MATCH(101,A2:A6,0))</f>
+        <v>5000</v>
+      </c>
+      <c r="C13" s="65">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="65" t="s">
+        <v>299</v>
+      </c>
+      <c r="B14" s="65" t="str">
+        <f>INDEX(B2:B6,MATCH("East",D2:D6,0))</f>
+        <v>Chair</v>
+      </c>
+      <c r="C14" s="65" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="65" t="s">
+        <v>300</v>
+      </c>
+      <c r="B15" s="65" t="str">
+        <f>INDEX(D2:D6,MATCH("Chair",B2:B6,0))</f>
+        <v>East</v>
+      </c>
+      <c r="C15" s="65" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="65" t="s">
+        <v>301</v>
+      </c>
+      <c r="B16" s="65">
+        <f>INDEX(E2:E6,MATCH(105,A2:A6,0))</f>
+        <v>4000</v>
+      </c>
+      <c r="C16" s="65">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="65" t="s">
+        <v>302</v>
+      </c>
+      <c r="C17" s="65" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="65" t="s">
+        <v>303</v>
+      </c>
+      <c r="C18" s="65" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="65" t="s">
+        <v>304</v>
+      </c>
+      <c r="C19" s="65" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="133" t="s">
+        <v>305</v>
+      </c>
+      <c r="B23" s="134"/>
+      <c r="C23" s="134"/>
+      <c r="D23" s="134"/>
+      <c r="E23" s="134"/>
+      <c r="F23" s="134"/>
+      <c r="G23" s="134"/>
+      <c r="H23" s="134"/>
+      <c r="I23" s="134"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A23:I23"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A23" r:id="rId1" xr:uid="{84AAEC77-B9FF-440B-B977-DC74327C06C7}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D628999E-1101-4859-A1BA-0F620A8FCB3D}">
   <dimension ref="A1:J51"/>
@@ -4684,6 +4969,144 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F45D93C-681F-429B-96D1-BA84CBB212E4}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="16384" width="8.88671875" style="137"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="136" t="s">
+        <v>306</v>
+      </c>
+      <c r="B1" s="136" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="136" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="137" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="137" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="137">
+        <v>500</v>
+      </c>
+      <c r="D2" s="138">
+        <f>AVERAGE((AVERAGEIFS(C2:C11,B2:B11,"Speakers",A2:A11,"South")+AVERAGEIFS(C2:C11,B2:B11,"Speakers",A2:A11,"East"))/2)</f>
+        <v>175</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" s="137" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="137" t="s">
+        <v>290</v>
+      </c>
+      <c r="C3" s="137">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" s="137" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="137" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="137">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" s="137" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="137" t="s">
+        <v>68</v>
+      </c>
+      <c r="C5" s="137">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="137" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="137" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="137">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A7" s="137" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="137" t="s">
+        <v>290</v>
+      </c>
+      <c r="C7" s="137">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A8" s="137" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="137" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" s="137">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A9" s="137" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" s="137" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="137">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A10" s="137" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="137" t="s">
+        <v>68</v>
+      </c>
+      <c r="C10" s="137">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A11" s="137" t="s">
+        <v>26</v>
+      </c>
+      <c r="B11" s="137" t="s">
+        <v>290</v>
+      </c>
+      <c r="C11" s="137">
+        <v>350</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E468253-D8BB-4FA6-816D-27ABA8930A6D}">
   <dimension ref="A1:J24"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -4880,6 +5303,10 @@
       <c r="I8" s="65" t="s">
         <v>202</v>
       </c>
+      <c r="J8" s="65">
+        <f>COUNTIF(C2:C11,"Overdue")</f>
+        <v>5</v>
+      </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="65" t="s">
@@ -4899,6 +5326,10 @@
       </c>
       <c r="I9" s="65" t="s">
         <v>199</v>
+      </c>
+      <c r="J9" s="65">
+        <f>COUNTIFS(B2:B11,"south",C2:C11,"paid")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -5020,7 +5451,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{116B6492-7E8B-47E0-8222-5EB871C51B32}">
   <dimension ref="A1:K25"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -5451,7 +5882,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F9F5792-D527-4DAE-8F40-0C8A70D97254}">
   <dimension ref="A1:Q24"/>
   <sheetFormatPr defaultColWidth="10.33203125" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -5863,267 +6294,4 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B5A70E6-D93D-44C4-88D6-4B03C3177468}">
-  <dimension ref="A1:I23"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="37.109375" style="65" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.21875" style="65" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.33203125" style="65" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.44140625" style="65" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5" style="65" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="65"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" s="89" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="89" t="s">
-        <v>91</v>
-      </c>
-      <c r="B1" s="89" t="s">
-        <v>92</v>
-      </c>
-      <c r="C1" s="89" t="s">
-        <v>77</v>
-      </c>
-      <c r="D1" s="89" t="s">
-        <v>19</v>
-      </c>
-      <c r="E1" s="89" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="65">
-        <v>101</v>
-      </c>
-      <c r="B2" s="65" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" s="65" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="65" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="65">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="65">
-        <v>102</v>
-      </c>
-      <c r="B3" s="65" t="s">
-        <v>290</v>
-      </c>
-      <c r="C3" s="65" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="65" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="65">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="65">
-        <v>103</v>
-      </c>
-      <c r="B4" s="65" t="s">
-        <v>291</v>
-      </c>
-      <c r="C4" s="65" t="s">
-        <v>292</v>
-      </c>
-      <c r="D4" s="65" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4" s="65">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="65">
-        <v>104</v>
-      </c>
-      <c r="B5" s="65" t="s">
-        <v>293</v>
-      </c>
-      <c r="C5" s="65" t="s">
-        <v>292</v>
-      </c>
-      <c r="D5" s="65" t="s">
-        <v>29</v>
-      </c>
-      <c r="E5" s="65">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="65">
-        <v>105</v>
-      </c>
-      <c r="B6" s="65" t="s">
-        <v>81</v>
-      </c>
-      <c r="C6" s="65" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="65" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="65">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" s="89" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="89" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" s="89" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="89" t="s">
-        <v>219</v>
-      </c>
-      <c r="B9" s="89" t="s">
-        <v>218</v>
-      </c>
-      <c r="C9" s="89" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="65" t="s">
-        <v>295</v>
-      </c>
-      <c r="B10" s="65">
-        <f>INDEX(E2:E6, MATCH("Phone", B2:B6, 0))</f>
-        <v>3000</v>
-      </c>
-      <c r="C10" s="65">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="65" t="s">
-        <v>296</v>
-      </c>
-      <c r="B11" s="65" t="str">
-        <f>INDEX(D2:D6, MATCH(104, A2:A6, 0))</f>
-        <v>West</v>
-      </c>
-      <c r="C11" s="65" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="65" t="s">
-        <v>297</v>
-      </c>
-      <c r="B12" s="65" t="str">
-        <f>INDEX(C2:C6,MATCH("Monitor",B2:B6,0))</f>
-        <v>Electronics</v>
-      </c>
-      <c r="C12" s="65" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="65" t="s">
-        <v>298</v>
-      </c>
-      <c r="B13" s="65">
-        <f>INDEX(E2:E6,MATCH(101,A2:A6,0))</f>
-        <v>5000</v>
-      </c>
-      <c r="C13" s="65">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="65" t="s">
-        <v>299</v>
-      </c>
-      <c r="B14" s="65" t="str">
-        <f>INDEX(B2:B6,MATCH("East",D2:D6,0))</f>
-        <v>Chair</v>
-      </c>
-      <c r="C14" s="65" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="65" t="s">
-        <v>300</v>
-      </c>
-      <c r="B15" s="65" t="str">
-        <f>INDEX(D2:D6,MATCH("Chair",B2:B6,0))</f>
-        <v>East</v>
-      </c>
-      <c r="C15" s="65" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="65" t="s">
-        <v>301</v>
-      </c>
-      <c r="B16" s="65">
-        <f>INDEX(E2:E6,MATCH(105,A2:A6,0))</f>
-        <v>4000</v>
-      </c>
-      <c r="C16" s="65">
-        <v>4000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A17" s="65" t="s">
-        <v>302</v>
-      </c>
-      <c r="C17" s="65" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A18" s="65" t="s">
-        <v>303</v>
-      </c>
-      <c r="C18" s="65" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="65" t="s">
-        <v>304</v>
-      </c>
-      <c r="C19" s="65" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="133" t="s">
-        <v>305</v>
-      </c>
-      <c r="B23" s="134"/>
-      <c r="C23" s="134"/>
-      <c r="D23" s="134"/>
-      <c r="E23" s="134"/>
-      <c r="F23" s="134"/>
-      <c r="G23" s="134"/>
-      <c r="H23" s="134"/>
-      <c r="I23" s="134"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A23:I23"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="A23" r:id="rId1" xr:uid="{84AAEC77-B9FF-440B-B977-DC74327C06C7}"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Practice_file.xlsx
+++ b/Practice_file.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d58d4d655bee1e81/Desktop/Github/Practice_Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="275" documentId="11_F25DC773A252ABDACC1048BD89DC52D45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A04277C-047F-45F8-991E-0578B4C89E0E}"/>
+  <xr:revisionPtr revIDLastSave="330" documentId="11_F25DC773A252ABDACC1048BD89DC52D45ADE58EF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF570768-13B8-4F89-9332-554FF5D17C10}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SUMIF,AVGIF" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,8 @@
     <sheet name="VLOOKUP" sheetId="7" r:id="rId8"/>
     <sheet name="HLOOKUP" sheetId="8" r:id="rId9"/>
     <sheet name="INDEXMATCH" sheetId="9" r:id="rId10"/>
+    <sheet name="Practice1" sheetId="13" r:id="rId11"/>
+    <sheet name="Practice2" sheetId="14" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -70,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1130" uniqueCount="608">
   <si>
     <t>Data for Practice</t>
   </si>
@@ -994,6 +996,952 @@
   </si>
   <si>
     <t xml:space="preserve">Sales </t>
+  </si>
+  <si>
+    <t>Employee ID</t>
+  </si>
+  <si>
+    <t>Years at Company</t>
+  </si>
+  <si>
+    <t>Amy Johnson</t>
+  </si>
+  <si>
+    <t>Task1</t>
+  </si>
+  <si>
+    <t>Christopher Craig</t>
+  </si>
+  <si>
+    <t>CEO Office</t>
+  </si>
+  <si>
+    <t>Task2</t>
+  </si>
+  <si>
+    <t>Daniel Ellis</t>
+  </si>
+  <si>
+    <t>Task3</t>
+  </si>
+  <si>
+    <t>Luke Smith</t>
+  </si>
+  <si>
+    <t>Michelle Herrera</t>
+  </si>
+  <si>
+    <t>Data</t>
+  </si>
+  <si>
+    <t>William Larson</t>
+  </si>
+  <si>
+    <t>Christopher Carr</t>
+  </si>
+  <si>
+    <t>Amanda Rodriguez</t>
+  </si>
+  <si>
+    <t>Ryan Martinez</t>
+  </si>
+  <si>
+    <t>Victoria Moran</t>
+  </si>
+  <si>
+    <t>Tyler Cook</t>
+  </si>
+  <si>
+    <t>Belinda Austin</t>
+  </si>
+  <si>
+    <t>Barry Figueroa</t>
+  </si>
+  <si>
+    <t>Taylor Schmidt</t>
+  </si>
+  <si>
+    <t>Jennifer Brown</t>
+  </si>
+  <si>
+    <t>Angel Adams</t>
+  </si>
+  <si>
+    <t>Gabrielle Evans</t>
+  </si>
+  <si>
+    <t>Ashley Hammond</t>
+  </si>
+  <si>
+    <t>Anthony Miller</t>
+  </si>
+  <si>
+    <t>Janet Nelson</t>
+  </si>
+  <si>
+    <t>Michael Brady</t>
+  </si>
+  <si>
+    <t>Theresa Tanner</t>
+  </si>
+  <si>
+    <t>Denise Richards</t>
+  </si>
+  <si>
+    <t>Jermaine Anderson</t>
+  </si>
+  <si>
+    <t>John Roberts</t>
+  </si>
+  <si>
+    <t>Victor Williams</t>
+  </si>
+  <si>
+    <t>Paul Palmer</t>
+  </si>
+  <si>
+    <t>Glenn Burch</t>
+  </si>
+  <si>
+    <t>Carla Taylor</t>
+  </si>
+  <si>
+    <t>William Harris</t>
+  </si>
+  <si>
+    <t>Kelly Davis</t>
+  </si>
+  <si>
+    <t>Sandra Johns DDS</t>
+  </si>
+  <si>
+    <t>Katherine Howe</t>
+  </si>
+  <si>
+    <t>Jamie Joyce</t>
+  </si>
+  <si>
+    <t>Meredith Johnson</t>
+  </si>
+  <si>
+    <t>Marisa May</t>
+  </si>
+  <si>
+    <t>Morgan Wise</t>
+  </si>
+  <si>
+    <t>Diana Munoz</t>
+  </si>
+  <si>
+    <t>Bryce Blake</t>
+  </si>
+  <si>
+    <t>Kevin Woods</t>
+  </si>
+  <si>
+    <t>Richard Romero</t>
+  </si>
+  <si>
+    <t>Kimberly Alexander</t>
+  </si>
+  <si>
+    <t>Megan Barr</t>
+  </si>
+  <si>
+    <t>Roberta Wilson</t>
+  </si>
+  <si>
+    <t>Peggy Smith</t>
+  </si>
+  <si>
+    <t>Lisa Torres</t>
+  </si>
+  <si>
+    <t>Sheila Strong</t>
+  </si>
+  <si>
+    <t>John Ramirez</t>
+  </si>
+  <si>
+    <t>Ms. Karen Hurley MD</t>
+  </si>
+  <si>
+    <t>Tina Miller</t>
+  </si>
+  <si>
+    <t>Latoya Montgomery</t>
+  </si>
+  <si>
+    <t>John Butler</t>
+  </si>
+  <si>
+    <t>Cheryl Myers</t>
+  </si>
+  <si>
+    <t>David Smith</t>
+  </si>
+  <si>
+    <t>Lauren Thomas</t>
+  </si>
+  <si>
+    <t>Michael Thompson</t>
+  </si>
+  <si>
+    <t>Don Warren</t>
+  </si>
+  <si>
+    <t>Megan Miller</t>
+  </si>
+  <si>
+    <t>Carolyn Walker</t>
+  </si>
+  <si>
+    <t>Bailey Jacobson</t>
+  </si>
+  <si>
+    <t>Amber Benitez</t>
+  </si>
+  <si>
+    <t>Paul Mullen</t>
+  </si>
+  <si>
+    <t>Steven Peterson</t>
+  </si>
+  <si>
+    <t>Barbara Hendricks</t>
+  </si>
+  <si>
+    <t>Karen Fuentes</t>
+  </si>
+  <si>
+    <t>Dana Johnson</t>
+  </si>
+  <si>
+    <t>Misty Gould</t>
+  </si>
+  <si>
+    <t>Ana Juarez</t>
+  </si>
+  <si>
+    <t>Erin Tran</t>
+  </si>
+  <si>
+    <t>Melissa Brown</t>
+  </si>
+  <si>
+    <t>John Berry</t>
+  </si>
+  <si>
+    <t>Ruth Sandoval</t>
+  </si>
+  <si>
+    <t>Andrew Harrison</t>
+  </si>
+  <si>
+    <t>Cesar Rowland</t>
+  </si>
+  <si>
+    <t>Richard Murphy</t>
+  </si>
+  <si>
+    <t>Craig Valdez</t>
+  </si>
+  <si>
+    <t>Wesley Reyes</t>
+  </si>
+  <si>
+    <t>Andrea Ford</t>
+  </si>
+  <si>
+    <t>Steve Robles</t>
+  </si>
+  <si>
+    <t>David Taylor</t>
+  </si>
+  <si>
+    <t>Paige Navarro</t>
+  </si>
+  <si>
+    <r>
+      <t>Find the salary of "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1" tint="4.9989318521683403E-2"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Cesar Rowland</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1" tint="4.9989318521683403E-2"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>" If the employee is not found, return "Not Available."</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Calculate the total salary of employees who are older than 30 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>and</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t> have worked for more than 5 years.</t>
+    </r>
+  </si>
+  <si>
+    <t>Calculate the average salary of employees older than 30 if their salary is above the median salary of the entire dataset. If the condition is not met, return "N/A."</t>
+  </si>
+  <si>
+    <t>Customer ID</t>
+  </si>
+  <si>
+    <t>Unit Price</t>
+  </si>
+  <si>
+    <t>Purchase Date</t>
+  </si>
+  <si>
+    <t>C004</t>
+  </si>
+  <si>
+    <t>Razer Blade Stealth</t>
+  </si>
+  <si>
+    <t>3/26/2024</t>
+  </si>
+  <si>
+    <t>C063</t>
+  </si>
+  <si>
+    <t>Dyson Hair Dryer</t>
+  </si>
+  <si>
+    <t>4/15/2024</t>
+  </si>
+  <si>
+    <t>C041</t>
+  </si>
+  <si>
+    <t>Amazon Echo Dot</t>
+  </si>
+  <si>
+    <t>C031</t>
+  </si>
+  <si>
+    <t>Logitech Wireless Mouse</t>
+  </si>
+  <si>
+    <t>3/25/2024</t>
+  </si>
+  <si>
+    <t>C067</t>
+  </si>
+  <si>
+    <t>LG Gram Laptop</t>
+  </si>
+  <si>
+    <t>C052</t>
+  </si>
+  <si>
+    <t>HP Pavilion Desktop</t>
+  </si>
+  <si>
+    <t>C112</t>
+  </si>
+  <si>
+    <t>Xiaomi Mi Band</t>
+  </si>
+  <si>
+    <t>C027</t>
+  </si>
+  <si>
+    <t>Samsung Smart Fridge</t>
+  </si>
+  <si>
+    <t>2/17/2024</t>
+  </si>
+  <si>
+    <t>C017</t>
+  </si>
+  <si>
+    <t>Canon Pixma Printer</t>
+  </si>
+  <si>
+    <t>2/25/2024</t>
+  </si>
+  <si>
+    <t>C043</t>
+  </si>
+  <si>
+    <t>Sony WH-1000XM4 Headphones</t>
+  </si>
+  <si>
+    <t>3/15/2024</t>
+  </si>
+  <si>
+    <t>C120</t>
+  </si>
+  <si>
+    <t>Anker Power Bank</t>
+  </si>
+  <si>
+    <t>4/13/2024</t>
+  </si>
+  <si>
+    <t>C113</t>
+  </si>
+  <si>
+    <t>Alienware Gaming PC</t>
+  </si>
+  <si>
+    <t>C079</t>
+  </si>
+  <si>
+    <t>Polaroid Instant Camera</t>
+  </si>
+  <si>
+    <t>4/17/2024</t>
+  </si>
+  <si>
+    <t>C009</t>
+  </si>
+  <si>
+    <t>Apple iPhone</t>
+  </si>
+  <si>
+    <t>C108</t>
+  </si>
+  <si>
+    <t>Philips Hue Smart Lights</t>
+  </si>
+  <si>
+    <t>C084</t>
+  </si>
+  <si>
+    <t>Canon EOS Camera</t>
+  </si>
+  <si>
+    <t>C085</t>
+  </si>
+  <si>
+    <t>Garmin Fenix 6</t>
+  </si>
+  <si>
+    <t>3/24/2024</t>
+  </si>
+  <si>
+    <t>C044</t>
+  </si>
+  <si>
+    <t>Ninja Blender</t>
+  </si>
+  <si>
+    <t>3/21/2024</t>
+  </si>
+  <si>
+    <t>C095</t>
+  </si>
+  <si>
+    <t>Bose Soundbar</t>
+  </si>
+  <si>
+    <t>3/22/2024</t>
+  </si>
+  <si>
+    <t>C056</t>
+  </si>
+  <si>
+    <t>Samsung QLED TV</t>
+  </si>
+  <si>
+    <t>C100</t>
+  </si>
+  <si>
+    <t>Philips Sonicare Toothbrush</t>
+  </si>
+  <si>
+    <t>3/20/2024</t>
+  </si>
+  <si>
+    <t>C096</t>
+  </si>
+  <si>
+    <t>Dyson Vacuum Cleaner</t>
+  </si>
+  <si>
+    <t>2/19/2024</t>
+  </si>
+  <si>
+    <t>C018</t>
+  </si>
+  <si>
+    <t>Motorola Moto G</t>
+  </si>
+  <si>
+    <t>C105</t>
+  </si>
+  <si>
+    <t>Breville Espresso Machine</t>
+  </si>
+  <si>
+    <t>C082</t>
+  </si>
+  <si>
+    <t>Bose SoundLink Speaker</t>
+  </si>
+  <si>
+    <t>2/24/2024</t>
+  </si>
+  <si>
+    <t>C022</t>
+  </si>
+  <si>
+    <t>Garmin GPS Navigator</t>
+  </si>
+  <si>
+    <t>4/14/2024</t>
+  </si>
+  <si>
+    <t>C058</t>
+  </si>
+  <si>
+    <t>Bose Headphones</t>
+  </si>
+  <si>
+    <t>3/27/2024</t>
+  </si>
+  <si>
+    <t>C094</t>
+  </si>
+  <si>
+    <t>Apple AirPods</t>
+  </si>
+  <si>
+    <t>3/16/2024</t>
+  </si>
+  <si>
+    <t>C051</t>
+  </si>
+  <si>
+    <t>Lenovo ThinkPad</t>
+  </si>
+  <si>
+    <t>4/19/2024</t>
+  </si>
+  <si>
+    <t>C019</t>
+  </si>
+  <si>
+    <t>Logitech G Pro X Headset</t>
+  </si>
+  <si>
+    <t>C065</t>
+  </si>
+  <si>
+    <t>Sony PlayStation</t>
+  </si>
+  <si>
+    <t>4/18/2024</t>
+  </si>
+  <si>
+    <t>C008</t>
+  </si>
+  <si>
+    <t>Acer Predator Monitor</t>
+  </si>
+  <si>
+    <t>2/16/2024</t>
+  </si>
+  <si>
+    <t>C126</t>
+  </si>
+  <si>
+    <t>Apple iMac</t>
+  </si>
+  <si>
+    <t>4/16/2024</t>
+  </si>
+  <si>
+    <t>C021</t>
+  </si>
+  <si>
+    <t>Fitbit Versa Smartwatch</t>
+  </si>
+  <si>
+    <t>C106</t>
+  </si>
+  <si>
+    <t>Nikon D3500 Camera</t>
+  </si>
+  <si>
+    <t>C046</t>
+  </si>
+  <si>
+    <t>Toshiba External Hard Drive</t>
+  </si>
+  <si>
+    <t>3/29/2024</t>
+  </si>
+  <si>
+    <t>C010</t>
+  </si>
+  <si>
+    <t>Casio G-Shock Watch</t>
+  </si>
+  <si>
+    <t>C087</t>
+  </si>
+  <si>
+    <t>Dell XPS Laptop</t>
+  </si>
+  <si>
+    <t>C015</t>
+  </si>
+  <si>
+    <t>LG 4K Monitor</t>
+  </si>
+  <si>
+    <t>C081</t>
+  </si>
+  <si>
+    <t>Shark Steam Mop</t>
+  </si>
+  <si>
+    <t>C026</t>
+  </si>
+  <si>
+    <t>Samsung Mobile</t>
+  </si>
+  <si>
+    <t>3/13/2024</t>
+  </si>
+  <si>
+    <t>C025</t>
+  </si>
+  <si>
+    <t>Google Nest Thermostat</t>
+  </si>
+  <si>
+    <t>C089</t>
+  </si>
+  <si>
+    <t>LG Washing Machine</t>
+  </si>
+  <si>
+    <t>2/22/2024</t>
+  </si>
+  <si>
+    <t>C036</t>
+  </si>
+  <si>
+    <t>Sony Xperia Smartphone</t>
+  </si>
+  <si>
+    <t>C006</t>
+  </si>
+  <si>
+    <t>iRobot Roomba</t>
+  </si>
+  <si>
+    <t>C127</t>
+  </si>
+  <si>
+    <t>Fitbit Inspire</t>
+  </si>
+  <si>
+    <t>3/18/2024</t>
+  </si>
+  <si>
+    <t>C001</t>
+  </si>
+  <si>
+    <t>Samsung Galaxy Tablet</t>
+  </si>
+  <si>
+    <t>2/15/2024</t>
+  </si>
+  <si>
+    <t>C055</t>
+  </si>
+  <si>
+    <t>GoPro Hero Camera</t>
+  </si>
+  <si>
+    <t>2/26/2024</t>
+  </si>
+  <si>
+    <t>C075</t>
+  </si>
+  <si>
+    <t>Sennheiser Wireless Headphones</t>
+  </si>
+  <si>
+    <t>C111</t>
+  </si>
+  <si>
+    <t>JBL Portable Speaker</t>
+  </si>
+  <si>
+    <t>C077</t>
+  </si>
+  <si>
+    <t>Huawei P40 Pro</t>
+  </si>
+  <si>
+    <t>2/23/2024</t>
+  </si>
+  <si>
+    <t>C074</t>
+  </si>
+  <si>
+    <t>HP Spectre x360</t>
+  </si>
+  <si>
+    <t>3/17/2024</t>
+  </si>
+  <si>
+    <t>C060</t>
+  </si>
+  <si>
+    <t>Sony 4K TV</t>
+  </si>
+  <si>
+    <t>C047</t>
+  </si>
+  <si>
+    <t>iPad Mini</t>
+  </si>
+  <si>
+    <t>3/28/2024</t>
+  </si>
+  <si>
+    <t>C073</t>
+  </si>
+  <si>
+    <t>Sonos One Smart Speaker</t>
+  </si>
+  <si>
+    <t>2/27/2024</t>
+  </si>
+  <si>
+    <t>C049</t>
+  </si>
+  <si>
+    <t>HP Omen Gaming Laptop</t>
+  </si>
+  <si>
+    <t>2/20/2024</t>
+  </si>
+  <si>
+    <t>C088</t>
+  </si>
+  <si>
+    <t>Microsoft Xbox</t>
+  </si>
+  <si>
+    <t>C030</t>
+  </si>
+  <si>
+    <t>Fitbit Charge</t>
+  </si>
+  <si>
+    <t>2/21/2024</t>
+  </si>
+  <si>
+    <t>C023</t>
+  </si>
+  <si>
+    <t>Jabra Elite Wireless Earbuds</t>
+  </si>
+  <si>
+    <t>C050</t>
+  </si>
+  <si>
+    <t>Sony Smartwatch</t>
+  </si>
+  <si>
+    <t>3/14/2024</t>
+  </si>
+  <si>
+    <t>C099</t>
+  </si>
+  <si>
+    <t>Apple MacBook Pro</t>
+  </si>
+  <si>
+    <t>C042</t>
+  </si>
+  <si>
+    <t>Nintendo Switch</t>
+  </si>
+  <si>
+    <t>2/18/2024</t>
+  </si>
+  <si>
+    <t>C068</t>
+  </si>
+  <si>
+    <t>Samsung Smartwatch Active</t>
+  </si>
+  <si>
+    <t>2/14/2024</t>
+  </si>
+  <si>
+    <t>C128</t>
+  </si>
+  <si>
+    <t>Apple Magic Mouse</t>
+  </si>
+  <si>
+    <t>3/23/2024</t>
+  </si>
+  <si>
+    <t>C040</t>
+  </si>
+  <si>
+    <t>Bose QuietComfort Headphones</t>
+  </si>
+  <si>
+    <t>3/30/2024</t>
+  </si>
+  <si>
+    <t>C011</t>
+  </si>
+  <si>
+    <t>HP Envy Printer</t>
+  </si>
+  <si>
+    <t>C054</t>
+  </si>
+  <si>
+    <t>Razer Gaming Mouse</t>
+  </si>
+  <si>
+    <t>C032</t>
+  </si>
+  <si>
+    <t>Canon Rebel DSLR Camera</t>
+  </si>
+  <si>
+    <t>C048</t>
+  </si>
+  <si>
+    <t>Nespresso Vertuo Coffee Maker</t>
+  </si>
+  <si>
+    <t>C107</t>
+  </si>
+  <si>
+    <t>Apple iPad Pro</t>
+  </si>
+  <si>
+    <t>C061</t>
+  </si>
+  <si>
+    <t>Dell Inspiron Laptop</t>
+  </si>
+  <si>
+    <t>3/31/2024</t>
+  </si>
+  <si>
+    <t>C072</t>
+  </si>
+  <si>
+    <t>LG OLED TV</t>
+  </si>
+  <si>
+    <t>2/28/2024</t>
+  </si>
+  <si>
+    <t>C098</t>
+  </si>
+  <si>
+    <t>GoPro Max Camera</t>
+  </si>
+  <si>
+    <t>C086</t>
+  </si>
+  <si>
+    <t>Samsung Galaxy Watch</t>
+  </si>
+  <si>
+    <t>3/19/2024</t>
+  </si>
+  <si>
+    <t>C024</t>
+  </si>
+  <si>
+    <t>KitchenAid Mixer</t>
+  </si>
+  <si>
+    <t>C076</t>
+  </si>
+  <si>
+    <t>Fitbit Sense</t>
+  </si>
+  <si>
+    <t>C007</t>
+  </si>
+  <si>
+    <t>Gala Mop</t>
+  </si>
+  <si>
+    <t>2/13/2024</t>
+  </si>
+  <si>
+    <t>C097</t>
+  </si>
+  <si>
+    <t>Asus ROG Laptop</t>
+  </si>
+  <si>
+    <t>C003</t>
+  </si>
+  <si>
+    <t>Samsung 65-inch TV</t>
+  </si>
+  <si>
+    <t>C034</t>
+  </si>
+  <si>
+    <t>KitchenAid Stand Mixer</t>
+  </si>
+  <si>
+    <t>C013</t>
+  </si>
+  <si>
+    <t>Microsoft Surface Laptop</t>
+  </si>
+  <si>
+    <t>2/29/2024</t>
+  </si>
+  <si>
+    <t>Find the product purchased by the customer with ID "C003" If the customer is not found, return "Customer Not Found."</t>
   </si>
 </sst>
 </file>
@@ -1003,7 +1951,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yy;@"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1112,8 +2060,44 @@
       <name val="Courier New"/>
       <family val="3"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1" tint="4.9989318521683403E-2"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1" tint="4.9989318521683403E-2"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1" tint="4.9989318521683403E-2"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF333B48"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1171,6 +2155,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="-0.499984740745262"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1502,7 +2492,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="139">
+  <cellXfs count="156">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1799,6 +2789,9 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1808,6 +2801,44 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2806,6 +3837,4697 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DAB66E3-D8B3-4864-9195-145E9212AB0D}">
+  <dimension ref="A1:S82"/>
+  <sheetFormatPr defaultColWidth="11.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.6640625" style="144"/>
+    <col min="2" max="2" width="17.6640625" style="144" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="11.6640625" style="144"/>
+    <col min="6" max="6" width="17.21875" style="144" customWidth="1"/>
+    <col min="7" max="7" width="1.6640625" style="144" customWidth="1"/>
+    <col min="8" max="8" width="11.6640625" style="144"/>
+    <col min="9" max="9" width="17.6640625" style="144" customWidth="1"/>
+    <col min="10" max="16" width="12.6640625" style="144" customWidth="1"/>
+    <col min="17" max="16384" width="11.6640625" style="144"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="140" t="s">
+        <v>308</v>
+      </c>
+      <c r="B1" s="140" t="s">
+        <v>226</v>
+      </c>
+      <c r="C1" s="140" t="s">
+        <v>42</v>
+      </c>
+      <c r="D1" s="140" t="s">
+        <v>228</v>
+      </c>
+      <c r="E1" s="140" t="s">
+        <v>41</v>
+      </c>
+      <c r="F1" s="140" t="s">
+        <v>309</v>
+      </c>
+      <c r="G1" s="140"/>
+      <c r="H1" s="141" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="141" t="s">
+        <v>4</v>
+      </c>
+      <c r="J1" s="142"/>
+      <c r="K1" s="143"/>
+      <c r="L1" s="143"/>
+      <c r="M1" s="143"/>
+      <c r="N1" s="143"/>
+      <c r="O1" s="143"/>
+      <c r="P1" s="143"/>
+      <c r="Q1" s="143"/>
+      <c r="R1" s="143"/>
+      <c r="S1" s="143"/>
+    </row>
+    <row r="2" spans="1:19" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="143">
+        <v>118</v>
+      </c>
+      <c r="B2" s="143" t="s">
+        <v>310</v>
+      </c>
+      <c r="C2" s="143" t="s">
+        <v>46</v>
+      </c>
+      <c r="D2" s="143">
+        <v>81151</v>
+      </c>
+      <c r="E2" s="143">
+        <v>28</v>
+      </c>
+      <c r="F2" s="143">
+        <v>5</v>
+      </c>
+      <c r="G2" s="143"/>
+      <c r="H2" s="145" t="s">
+        <v>311</v>
+      </c>
+      <c r="I2" s="145">
+        <f>_xlfn.XLOOKUP("Cesar Rowland",B2:B82,D2:D82,"Not Avaliable")</f>
+        <v>62420</v>
+      </c>
+      <c r="J2" s="148" t="s">
+        <v>396</v>
+      </c>
+      <c r="K2" s="149"/>
+      <c r="L2" s="149"/>
+      <c r="M2" s="149"/>
+      <c r="N2" s="149"/>
+      <c r="O2" s="149"/>
+      <c r="P2" s="149"/>
+      <c r="Q2" s="143"/>
+      <c r="R2" s="143"/>
+      <c r="S2" s="143"/>
+    </row>
+    <row r="3" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="143">
+        <v>144</v>
+      </c>
+      <c r="B3" s="143" t="s">
+        <v>312</v>
+      </c>
+      <c r="C3" s="143" t="s">
+        <v>313</v>
+      </c>
+      <c r="D3" s="143">
+        <v>44236</v>
+      </c>
+      <c r="E3" s="143">
+        <v>32</v>
+      </c>
+      <c r="F3" s="143">
+        <v>6</v>
+      </c>
+      <c r="G3" s="143"/>
+      <c r="H3" s="145" t="s">
+        <v>314</v>
+      </c>
+      <c r="I3" s="145">
+        <f>SUMIFS(D2:D82,E2:E82,"&gt;30",F2:F82,"&gt;5")</f>
+        <v>2381346</v>
+      </c>
+      <c r="J3" s="150" t="s">
+        <v>397</v>
+      </c>
+      <c r="K3" s="136"/>
+      <c r="L3" s="136"/>
+      <c r="M3" s="136"/>
+      <c r="N3" s="136"/>
+      <c r="O3" s="136"/>
+      <c r="P3" s="136"/>
+      <c r="Q3" s="143"/>
+      <c r="R3" s="143"/>
+      <c r="S3" s="143"/>
+    </row>
+    <row r="4" spans="1:19" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="143">
+        <v>160</v>
+      </c>
+      <c r="B4" s="143" t="s">
+        <v>315</v>
+      </c>
+      <c r="C4" s="143" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="143">
+        <v>67386</v>
+      </c>
+      <c r="E4" s="143">
+        <v>25</v>
+      </c>
+      <c r="F4" s="143">
+        <v>3</v>
+      </c>
+      <c r="G4" s="143"/>
+      <c r="H4" s="145" t="s">
+        <v>316</v>
+      </c>
+      <c r="I4" s="145">
+        <f>IFERROR(AVERAGEIFS($D$2:$D$84,$E$2:$E$84,"&gt;30",$D$2:$D$84,"&gt;"&amp;MEDIAN(D2:D84)),"N/A")</f>
+        <v>97550.965517241377</v>
+      </c>
+      <c r="J4" s="147" t="s">
+        <v>398</v>
+      </c>
+      <c r="K4" s="147"/>
+      <c r="L4" s="147"/>
+      <c r="M4" s="147"/>
+      <c r="N4" s="147"/>
+      <c r="O4" s="147"/>
+      <c r="P4" s="147"/>
+      <c r="Q4" s="143"/>
+      <c r="R4" s="143"/>
+      <c r="S4" s="143"/>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A5" s="143">
+        <v>155</v>
+      </c>
+      <c r="B5" s="143" t="s">
+        <v>317</v>
+      </c>
+      <c r="C5" s="143" t="s">
+        <v>313</v>
+      </c>
+      <c r="D5" s="143">
+        <v>46337</v>
+      </c>
+      <c r="E5" s="143">
+        <v>28</v>
+      </c>
+      <c r="F5" s="143">
+        <v>7</v>
+      </c>
+      <c r="G5" s="143"/>
+      <c r="H5" s="146"/>
+      <c r="I5" s="146"/>
+      <c r="J5" s="147"/>
+      <c r="K5" s="147"/>
+      <c r="L5" s="147"/>
+      <c r="M5" s="147"/>
+      <c r="N5" s="147"/>
+      <c r="O5" s="147"/>
+      <c r="P5" s="147"/>
+      <c r="Q5" s="143"/>
+      <c r="R5" s="143"/>
+      <c r="S5" s="143"/>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A6" s="143">
+        <v>133</v>
+      </c>
+      <c r="B6" s="143" t="s">
+        <v>318</v>
+      </c>
+      <c r="C6" s="143" t="s">
+        <v>319</v>
+      </c>
+      <c r="D6" s="143">
+        <v>70319</v>
+      </c>
+      <c r="E6" s="143">
+        <v>52</v>
+      </c>
+      <c r="F6" s="143">
+        <v>6</v>
+      </c>
+      <c r="G6" s="143"/>
+      <c r="H6" s="143"/>
+      <c r="I6" s="151"/>
+      <c r="J6" s="143"/>
+      <c r="K6" s="143"/>
+      <c r="L6" s="143"/>
+      <c r="M6" s="143"/>
+      <c r="N6" s="143"/>
+      <c r="O6" s="143"/>
+      <c r="P6" s="143"/>
+      <c r="Q6" s="143"/>
+      <c r="R6" s="143"/>
+      <c r="S6" s="143"/>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A7" s="143">
+        <v>141</v>
+      </c>
+      <c r="B7" s="143" t="s">
+        <v>320</v>
+      </c>
+      <c r="C7" s="143" t="s">
+        <v>313</v>
+      </c>
+      <c r="D7" s="143">
+        <v>84019</v>
+      </c>
+      <c r="E7" s="143">
+        <v>30</v>
+      </c>
+      <c r="F7" s="143">
+        <v>5</v>
+      </c>
+      <c r="G7" s="143"/>
+      <c r="H7" s="143"/>
+      <c r="I7" s="143"/>
+      <c r="J7" s="143"/>
+      <c r="K7" s="143"/>
+      <c r="L7" s="143"/>
+      <c r="M7" s="143"/>
+      <c r="N7" s="143"/>
+      <c r="O7" s="143"/>
+      <c r="P7" s="143"/>
+      <c r="Q7" s="143"/>
+      <c r="R7" s="143"/>
+      <c r="S7" s="143"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A8" s="143">
+        <v>143</v>
+      </c>
+      <c r="B8" s="143" t="s">
+        <v>321</v>
+      </c>
+      <c r="C8" s="143" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="143">
+        <v>106197</v>
+      </c>
+      <c r="E8" s="143">
+        <v>25</v>
+      </c>
+      <c r="F8" s="143">
+        <v>6</v>
+      </c>
+      <c r="G8" s="143"/>
+      <c r="H8" s="143"/>
+      <c r="I8" s="143"/>
+      <c r="J8" s="143"/>
+      <c r="K8" s="143"/>
+      <c r="L8" s="143"/>
+      <c r="M8" s="143"/>
+      <c r="N8" s="143"/>
+      <c r="O8" s="143"/>
+      <c r="P8" s="143"/>
+      <c r="Q8" s="143"/>
+      <c r="R8" s="143"/>
+      <c r="S8" s="143"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A9" s="143">
+        <v>165</v>
+      </c>
+      <c r="B9" s="143" t="s">
+        <v>322</v>
+      </c>
+      <c r="C9" s="143" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="143">
+        <v>81150</v>
+      </c>
+      <c r="E9" s="143">
+        <v>50</v>
+      </c>
+      <c r="F9" s="143">
+        <v>10</v>
+      </c>
+      <c r="G9" s="143"/>
+      <c r="H9" s="143"/>
+      <c r="I9" s="143"/>
+      <c r="J9" s="143"/>
+      <c r="K9" s="143"/>
+      <c r="L9" s="143"/>
+      <c r="M9" s="143"/>
+      <c r="N9" s="143"/>
+      <c r="O9" s="143"/>
+      <c r="P9" s="143"/>
+      <c r="Q9" s="143"/>
+      <c r="R9" s="143"/>
+      <c r="S9" s="143"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A10" s="143">
+        <v>119</v>
+      </c>
+      <c r="B10" s="143" t="s">
+        <v>323</v>
+      </c>
+      <c r="C10" s="143" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="143">
+        <v>60458</v>
+      </c>
+      <c r="E10" s="143">
+        <v>30</v>
+      </c>
+      <c r="F10" s="143">
+        <v>12</v>
+      </c>
+      <c r="G10" s="143"/>
+      <c r="H10" s="143"/>
+      <c r="I10" s="152"/>
+      <c r="J10" s="152"/>
+      <c r="K10" s="152"/>
+      <c r="L10" s="152"/>
+      <c r="M10" s="152"/>
+      <c r="N10" s="152"/>
+      <c r="O10" s="143"/>
+      <c r="P10" s="143"/>
+      <c r="Q10" s="143"/>
+      <c r="R10" s="143"/>
+      <c r="S10" s="143"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A11" s="143">
+        <v>162</v>
+      </c>
+      <c r="B11" s="143" t="s">
+        <v>324</v>
+      </c>
+      <c r="C11" s="143" t="s">
+        <v>232</v>
+      </c>
+      <c r="D11" s="143">
+        <v>50880</v>
+      </c>
+      <c r="E11" s="143">
+        <v>42</v>
+      </c>
+      <c r="F11" s="143">
+        <v>3</v>
+      </c>
+      <c r="G11" s="143"/>
+      <c r="H11" s="143"/>
+      <c r="I11" s="143"/>
+      <c r="J11" s="143"/>
+      <c r="K11" s="143"/>
+      <c r="L11" s="143"/>
+      <c r="M11" s="143"/>
+      <c r="N11" s="143"/>
+      <c r="O11" s="143"/>
+      <c r="P11" s="143"/>
+      <c r="Q11" s="143"/>
+      <c r="R11" s="143"/>
+      <c r="S11" s="143"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A12" s="143">
+        <v>153</v>
+      </c>
+      <c r="B12" s="143" t="s">
+        <v>325</v>
+      </c>
+      <c r="C12" s="143" t="s">
+        <v>319</v>
+      </c>
+      <c r="D12" s="143">
+        <v>116406</v>
+      </c>
+      <c r="E12" s="143">
+        <v>30</v>
+      </c>
+      <c r="F12" s="143">
+        <v>3</v>
+      </c>
+      <c r="G12" s="143"/>
+      <c r="H12" s="143"/>
+      <c r="I12" s="143"/>
+      <c r="J12" s="143"/>
+      <c r="K12" s="143"/>
+      <c r="L12" s="143"/>
+      <c r="M12" s="143"/>
+      <c r="N12" s="143"/>
+      <c r="O12" s="143"/>
+      <c r="P12" s="143"/>
+      <c r="Q12" s="143"/>
+      <c r="R12" s="143"/>
+      <c r="S12" s="143"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A13" s="143">
+        <v>180</v>
+      </c>
+      <c r="B13" s="143" t="s">
+        <v>326</v>
+      </c>
+      <c r="C13" s="143" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="143">
+        <v>49898</v>
+      </c>
+      <c r="E13" s="143">
+        <v>41</v>
+      </c>
+      <c r="F13" s="143">
+        <v>3</v>
+      </c>
+      <c r="G13" s="143"/>
+      <c r="H13" s="143"/>
+      <c r="I13" s="143"/>
+      <c r="J13" s="143"/>
+      <c r="K13" s="143"/>
+      <c r="L13" s="143"/>
+      <c r="M13" s="143"/>
+      <c r="N13" s="143"/>
+      <c r="O13" s="143"/>
+      <c r="P13" s="143"/>
+      <c r="Q13" s="143"/>
+      <c r="R13" s="143"/>
+      <c r="S13" s="143"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A14" s="143">
+        <v>168</v>
+      </c>
+      <c r="B14" s="143" t="s">
+        <v>327</v>
+      </c>
+      <c r="C14" s="143" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="143">
+        <v>72278</v>
+      </c>
+      <c r="E14" s="143">
+        <v>27</v>
+      </c>
+      <c r="F14" s="143">
+        <v>1</v>
+      </c>
+      <c r="G14" s="143"/>
+      <c r="H14" s="143"/>
+      <c r="I14" s="143"/>
+      <c r="J14" s="143"/>
+      <c r="K14" s="143"/>
+      <c r="L14" s="143"/>
+      <c r="M14" s="143"/>
+      <c r="N14" s="143"/>
+      <c r="O14" s="143"/>
+      <c r="P14" s="143"/>
+      <c r="Q14" s="143"/>
+      <c r="R14" s="143"/>
+      <c r="S14" s="143"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A15" s="143">
+        <v>102</v>
+      </c>
+      <c r="B15" s="143" t="s">
+        <v>328</v>
+      </c>
+      <c r="C15" s="143" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" s="143">
+        <v>81112</v>
+      </c>
+      <c r="E15" s="143">
+        <v>50</v>
+      </c>
+      <c r="F15" s="143">
+        <v>4</v>
+      </c>
+      <c r="G15" s="143"/>
+      <c r="H15" s="143"/>
+      <c r="I15" s="143"/>
+      <c r="J15" s="143"/>
+      <c r="K15" s="143"/>
+      <c r="L15" s="143"/>
+      <c r="M15" s="143"/>
+      <c r="N15" s="143"/>
+      <c r="O15" s="143"/>
+      <c r="P15" s="143"/>
+      <c r="Q15" s="143"/>
+      <c r="R15" s="143"/>
+      <c r="S15" s="143"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A16" s="143">
+        <v>126</v>
+      </c>
+      <c r="B16" s="143" t="s">
+        <v>329</v>
+      </c>
+      <c r="C16" s="143" t="s">
+        <v>313</v>
+      </c>
+      <c r="D16" s="143">
+        <v>66131</v>
+      </c>
+      <c r="E16" s="143">
+        <v>42</v>
+      </c>
+      <c r="F16" s="143">
+        <v>11</v>
+      </c>
+      <c r="G16" s="143"/>
+      <c r="H16" s="143"/>
+      <c r="I16" s="143"/>
+      <c r="J16" s="143"/>
+      <c r="K16" s="143"/>
+      <c r="L16" s="143"/>
+      <c r="M16" s="143"/>
+      <c r="N16" s="143"/>
+      <c r="O16" s="143"/>
+      <c r="P16" s="143"/>
+      <c r="Q16" s="143"/>
+      <c r="R16" s="143"/>
+      <c r="S16" s="143"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A17" s="143">
+        <v>124</v>
+      </c>
+      <c r="B17" s="143" t="s">
+        <v>330</v>
+      </c>
+      <c r="C17" s="143" t="s">
+        <v>319</v>
+      </c>
+      <c r="D17" s="143">
+        <v>93953</v>
+      </c>
+      <c r="E17" s="143">
+        <v>47</v>
+      </c>
+      <c r="F17" s="143">
+        <v>8</v>
+      </c>
+      <c r="G17" s="143"/>
+      <c r="H17" s="143"/>
+      <c r="I17" s="143"/>
+      <c r="J17" s="143"/>
+      <c r="K17" s="143"/>
+      <c r="L17" s="143"/>
+      <c r="M17" s="143"/>
+      <c r="N17" s="143"/>
+      <c r="O17" s="143"/>
+      <c r="P17" s="143"/>
+      <c r="Q17" s="143"/>
+      <c r="R17" s="143"/>
+      <c r="S17" s="143"/>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A18" s="143">
+        <v>164</v>
+      </c>
+      <c r="B18" s="143" t="s">
+        <v>331</v>
+      </c>
+      <c r="C18" s="143" t="s">
+        <v>319</v>
+      </c>
+      <c r="D18" s="143">
+        <v>55232</v>
+      </c>
+      <c r="E18" s="143">
+        <v>44</v>
+      </c>
+      <c r="F18" s="143">
+        <v>8</v>
+      </c>
+      <c r="G18" s="143"/>
+      <c r="H18" s="143"/>
+      <c r="I18" s="143"/>
+      <c r="J18" s="143"/>
+      <c r="K18" s="143"/>
+      <c r="L18" s="143"/>
+      <c r="M18" s="143"/>
+      <c r="N18" s="143"/>
+      <c r="O18" s="143"/>
+      <c r="P18" s="143"/>
+      <c r="Q18" s="143"/>
+      <c r="R18" s="143"/>
+      <c r="S18" s="143"/>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A19" s="143">
+        <v>156</v>
+      </c>
+      <c r="B19" s="143" t="s">
+        <v>332</v>
+      </c>
+      <c r="C19" s="143" t="s">
+        <v>319</v>
+      </c>
+      <c r="D19" s="143">
+        <v>111172</v>
+      </c>
+      <c r="E19" s="143">
+        <v>22</v>
+      </c>
+      <c r="F19" s="143">
+        <v>5</v>
+      </c>
+      <c r="G19" s="143"/>
+      <c r="H19" s="143"/>
+      <c r="I19" s="143"/>
+      <c r="J19" s="143"/>
+      <c r="K19" s="143"/>
+      <c r="L19" s="143"/>
+      <c r="M19" s="143"/>
+      <c r="N19" s="143"/>
+      <c r="O19" s="143"/>
+      <c r="P19" s="143"/>
+      <c r="Q19" s="143"/>
+      <c r="R19" s="143"/>
+      <c r="S19" s="143"/>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A20" s="143">
+        <v>132</v>
+      </c>
+      <c r="B20" s="143" t="s">
+        <v>333</v>
+      </c>
+      <c r="C20" s="143" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="143">
+        <v>51277</v>
+      </c>
+      <c r="E20" s="143">
+        <v>47</v>
+      </c>
+      <c r="F20" s="143">
+        <v>12</v>
+      </c>
+      <c r="G20" s="143"/>
+      <c r="H20" s="143"/>
+      <c r="I20" s="143"/>
+      <c r="J20" s="143"/>
+      <c r="K20" s="143"/>
+      <c r="L20" s="143"/>
+      <c r="M20" s="143"/>
+      <c r="N20" s="143"/>
+      <c r="O20" s="143"/>
+      <c r="P20" s="143"/>
+      <c r="Q20" s="143"/>
+      <c r="R20" s="143"/>
+      <c r="S20" s="143"/>
+    </row>
+    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A21" s="143">
+        <v>125</v>
+      </c>
+      <c r="B21" s="143" t="s">
+        <v>334</v>
+      </c>
+      <c r="C21" s="143" t="s">
+        <v>232</v>
+      </c>
+      <c r="D21" s="143">
+        <v>77762</v>
+      </c>
+      <c r="E21" s="143">
+        <v>51</v>
+      </c>
+      <c r="F21" s="143">
+        <v>5</v>
+      </c>
+      <c r="G21" s="143"/>
+      <c r="H21" s="143"/>
+      <c r="I21" s="143"/>
+      <c r="J21" s="143"/>
+      <c r="K21" s="143"/>
+      <c r="L21" s="143"/>
+      <c r="M21" s="143"/>
+      <c r="N21" s="143"/>
+      <c r="O21" s="143"/>
+      <c r="P21" s="143"/>
+      <c r="Q21" s="143"/>
+      <c r="R21" s="143"/>
+      <c r="S21" s="143"/>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A22" s="143">
+        <v>157</v>
+      </c>
+      <c r="B22" s="143" t="s">
+        <v>335</v>
+      </c>
+      <c r="C22" s="143" t="s">
+        <v>46</v>
+      </c>
+      <c r="D22" s="143">
+        <v>107035</v>
+      </c>
+      <c r="E22" s="143">
+        <v>48</v>
+      </c>
+      <c r="F22" s="143">
+        <v>4</v>
+      </c>
+      <c r="G22" s="143"/>
+      <c r="H22" s="143"/>
+      <c r="I22" s="143"/>
+      <c r="J22" s="143"/>
+      <c r="K22" s="143"/>
+      <c r="L22" s="143"/>
+      <c r="M22" s="143"/>
+      <c r="N22" s="143"/>
+      <c r="O22" s="143"/>
+      <c r="P22" s="143"/>
+      <c r="Q22" s="143"/>
+      <c r="R22" s="143"/>
+      <c r="S22" s="143"/>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A23" s="143">
+        <v>146</v>
+      </c>
+      <c r="B23" s="143" t="s">
+        <v>336</v>
+      </c>
+      <c r="C23" s="143" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="143">
+        <v>118921</v>
+      </c>
+      <c r="E23" s="143">
+        <v>35</v>
+      </c>
+      <c r="F23" s="143">
+        <v>10</v>
+      </c>
+      <c r="G23" s="143"/>
+      <c r="H23" s="143"/>
+      <c r="I23" s="143"/>
+      <c r="J23" s="143"/>
+      <c r="K23" s="143"/>
+      <c r="L23" s="143"/>
+      <c r="M23" s="143"/>
+      <c r="N23" s="143"/>
+      <c r="O23" s="143"/>
+      <c r="P23" s="143"/>
+      <c r="Q23" s="143"/>
+      <c r="R23" s="143"/>
+      <c r="S23" s="143"/>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A24" s="143">
+        <v>140</v>
+      </c>
+      <c r="B24" s="143" t="s">
+        <v>337</v>
+      </c>
+      <c r="C24" s="143" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" s="143">
+        <v>42469</v>
+      </c>
+      <c r="E24" s="143">
+        <v>25</v>
+      </c>
+      <c r="F24" s="143">
+        <v>2</v>
+      </c>
+      <c r="G24" s="143"/>
+      <c r="H24" s="143"/>
+      <c r="I24" s="143"/>
+      <c r="J24" s="143"/>
+      <c r="K24" s="143"/>
+      <c r="L24" s="143"/>
+      <c r="M24" s="143"/>
+      <c r="N24" s="143"/>
+      <c r="O24" s="143"/>
+      <c r="P24" s="143"/>
+      <c r="Q24" s="143"/>
+      <c r="R24" s="143"/>
+      <c r="S24" s="143"/>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A25" s="143">
+        <v>147</v>
+      </c>
+      <c r="B25" s="143" t="s">
+        <v>338</v>
+      </c>
+      <c r="C25" s="143" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" s="143">
+        <v>69352</v>
+      </c>
+      <c r="E25" s="143">
+        <v>37</v>
+      </c>
+      <c r="F25" s="143">
+        <v>8</v>
+      </c>
+      <c r="G25" s="143"/>
+      <c r="H25" s="143"/>
+      <c r="I25" s="143"/>
+      <c r="J25" s="143"/>
+      <c r="K25" s="143"/>
+      <c r="L25" s="143"/>
+      <c r="M25" s="143"/>
+      <c r="N25" s="143"/>
+      <c r="O25" s="143"/>
+      <c r="P25" s="143"/>
+      <c r="Q25" s="143"/>
+      <c r="R25" s="143"/>
+      <c r="S25" s="143"/>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A26" s="143">
+        <v>151</v>
+      </c>
+      <c r="B26" s="143" t="s">
+        <v>339</v>
+      </c>
+      <c r="C26" s="143" t="s">
+        <v>232</v>
+      </c>
+      <c r="D26" s="143">
+        <v>64642</v>
+      </c>
+      <c r="E26" s="143">
+        <v>45</v>
+      </c>
+      <c r="F26" s="143">
+        <v>3</v>
+      </c>
+      <c r="G26" s="143"/>
+      <c r="H26" s="143"/>
+      <c r="I26" s="143"/>
+      <c r="J26" s="143"/>
+      <c r="K26" s="143"/>
+      <c r="L26" s="143"/>
+      <c r="M26" s="143"/>
+      <c r="N26" s="143"/>
+      <c r="O26" s="143"/>
+      <c r="P26" s="143"/>
+      <c r="Q26" s="143"/>
+      <c r="R26" s="143"/>
+      <c r="S26" s="143"/>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A27" s="143">
+        <v>134</v>
+      </c>
+      <c r="B27" s="143" t="s">
+        <v>340</v>
+      </c>
+      <c r="C27" s="143" t="s">
+        <v>319</v>
+      </c>
+      <c r="D27" s="143">
+        <v>107700</v>
+      </c>
+      <c r="E27" s="143">
+        <v>38</v>
+      </c>
+      <c r="F27" s="143">
+        <v>1</v>
+      </c>
+      <c r="G27" s="143"/>
+      <c r="H27" s="143"/>
+      <c r="I27" s="143"/>
+      <c r="J27" s="143"/>
+      <c r="K27" s="143"/>
+      <c r="L27" s="143"/>
+      <c r="M27" s="143"/>
+      <c r="N27" s="143"/>
+      <c r="O27" s="143"/>
+      <c r="P27" s="143"/>
+      <c r="Q27" s="143"/>
+      <c r="R27" s="143"/>
+      <c r="S27" s="143"/>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A28" s="143">
+        <v>121</v>
+      </c>
+      <c r="B28" s="143" t="s">
+        <v>341</v>
+      </c>
+      <c r="C28" s="143" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="143">
+        <v>86458</v>
+      </c>
+      <c r="E28" s="143">
+        <v>32</v>
+      </c>
+      <c r="F28" s="143">
+        <v>5</v>
+      </c>
+      <c r="G28" s="143"/>
+      <c r="H28" s="143"/>
+      <c r="I28" s="143"/>
+      <c r="J28" s="143"/>
+      <c r="K28" s="143"/>
+      <c r="L28" s="143"/>
+      <c r="M28" s="143"/>
+      <c r="N28" s="143"/>
+      <c r="O28" s="143"/>
+      <c r="P28" s="143"/>
+      <c r="Q28" s="143"/>
+      <c r="R28" s="143"/>
+      <c r="S28" s="143"/>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A29" s="143">
+        <v>148</v>
+      </c>
+      <c r="B29" s="143" t="s">
+        <v>342</v>
+      </c>
+      <c r="C29" s="143" t="s">
+        <v>232</v>
+      </c>
+      <c r="D29" s="143">
+        <v>72126</v>
+      </c>
+      <c r="E29" s="143">
+        <v>42</v>
+      </c>
+      <c r="F29" s="143">
+        <v>10</v>
+      </c>
+      <c r="G29" s="143"/>
+      <c r="H29" s="143"/>
+      <c r="I29" s="143"/>
+      <c r="J29" s="143"/>
+      <c r="K29" s="143"/>
+      <c r="L29" s="143"/>
+      <c r="M29" s="143"/>
+      <c r="N29" s="143"/>
+      <c r="O29" s="143"/>
+      <c r="P29" s="143"/>
+      <c r="Q29" s="143"/>
+      <c r="R29" s="143"/>
+      <c r="S29" s="143"/>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A30" s="143">
+        <v>129</v>
+      </c>
+      <c r="B30" s="143" t="s">
+        <v>343</v>
+      </c>
+      <c r="C30" s="143" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="143">
+        <v>119319</v>
+      </c>
+      <c r="E30" s="143">
+        <v>45</v>
+      </c>
+      <c r="F30" s="143">
+        <v>10</v>
+      </c>
+      <c r="G30" s="143"/>
+      <c r="H30" s="143"/>
+      <c r="I30" s="143"/>
+      <c r="J30" s="143"/>
+      <c r="K30" s="143"/>
+      <c r="L30" s="143"/>
+      <c r="M30" s="143"/>
+      <c r="N30" s="143"/>
+      <c r="O30" s="143"/>
+      <c r="P30" s="143"/>
+      <c r="Q30" s="143"/>
+      <c r="R30" s="143"/>
+      <c r="S30" s="143"/>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A31" s="143">
+        <v>110</v>
+      </c>
+      <c r="B31" s="143" t="s">
+        <v>344</v>
+      </c>
+      <c r="C31" s="143" t="s">
+        <v>45</v>
+      </c>
+      <c r="D31" s="143">
+        <v>101162</v>
+      </c>
+      <c r="E31" s="143">
+        <v>33</v>
+      </c>
+      <c r="F31" s="143">
+        <v>4</v>
+      </c>
+      <c r="G31" s="143"/>
+      <c r="H31" s="143"/>
+      <c r="I31" s="143"/>
+      <c r="J31" s="143"/>
+      <c r="K31" s="143"/>
+      <c r="L31" s="143"/>
+      <c r="M31" s="143"/>
+      <c r="N31" s="143"/>
+      <c r="O31" s="143"/>
+      <c r="P31" s="143"/>
+      <c r="Q31" s="143"/>
+      <c r="R31" s="143"/>
+      <c r="S31" s="143"/>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A32" s="143">
+        <v>150</v>
+      </c>
+      <c r="B32" s="143" t="s">
+        <v>345</v>
+      </c>
+      <c r="C32" s="143" t="s">
+        <v>46</v>
+      </c>
+      <c r="D32" s="143">
+        <v>75000</v>
+      </c>
+      <c r="E32" s="143">
+        <v>32</v>
+      </c>
+      <c r="F32" s="143">
+        <v>12</v>
+      </c>
+      <c r="G32" s="143"/>
+      <c r="H32" s="143"/>
+      <c r="I32" s="143"/>
+      <c r="J32" s="143"/>
+      <c r="K32" s="143"/>
+      <c r="L32" s="143"/>
+      <c r="M32" s="143"/>
+      <c r="N32" s="143"/>
+      <c r="O32" s="143"/>
+      <c r="P32" s="143"/>
+      <c r="Q32" s="143"/>
+      <c r="R32" s="143"/>
+      <c r="S32" s="143"/>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A33" s="143">
+        <v>117</v>
+      </c>
+      <c r="B33" s="143" t="s">
+        <v>346</v>
+      </c>
+      <c r="C33" s="143" t="s">
+        <v>20</v>
+      </c>
+      <c r="D33" s="143">
+        <v>81912</v>
+      </c>
+      <c r="E33" s="143">
+        <v>38</v>
+      </c>
+      <c r="F33" s="143">
+        <v>9</v>
+      </c>
+      <c r="G33" s="143"/>
+      <c r="H33" s="143"/>
+      <c r="I33" s="143"/>
+      <c r="J33" s="143"/>
+      <c r="K33" s="143"/>
+      <c r="L33" s="143"/>
+      <c r="M33" s="143"/>
+      <c r="N33" s="143"/>
+      <c r="O33" s="143"/>
+      <c r="P33" s="143"/>
+      <c r="Q33" s="143"/>
+      <c r="R33" s="143"/>
+      <c r="S33" s="143"/>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A34" s="143">
+        <v>122</v>
+      </c>
+      <c r="B34" s="143" t="s">
+        <v>347</v>
+      </c>
+      <c r="C34" s="143" t="s">
+        <v>319</v>
+      </c>
+      <c r="D34" s="143">
+        <v>111337</v>
+      </c>
+      <c r="E34" s="143">
+        <v>50</v>
+      </c>
+      <c r="F34" s="143">
+        <v>8</v>
+      </c>
+      <c r="G34" s="143"/>
+      <c r="H34" s="143"/>
+      <c r="I34" s="143"/>
+      <c r="J34" s="143"/>
+      <c r="K34" s="143"/>
+      <c r="L34" s="143"/>
+      <c r="M34" s="143"/>
+      <c r="N34" s="143"/>
+      <c r="O34" s="143"/>
+      <c r="P34" s="143"/>
+      <c r="Q34" s="143"/>
+      <c r="R34" s="143"/>
+      <c r="S34" s="143"/>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A35" s="143">
+        <v>101</v>
+      </c>
+      <c r="B35" s="143" t="s">
+        <v>348</v>
+      </c>
+      <c r="C35" s="143" t="s">
+        <v>20</v>
+      </c>
+      <c r="D35" s="143">
+        <v>53517</v>
+      </c>
+      <c r="E35" s="143">
+        <v>44</v>
+      </c>
+      <c r="F35" s="143">
+        <v>4</v>
+      </c>
+      <c r="G35" s="143"/>
+      <c r="H35" s="143"/>
+      <c r="I35" s="143"/>
+      <c r="J35" s="143"/>
+      <c r="K35" s="143"/>
+      <c r="L35" s="143"/>
+      <c r="M35" s="143"/>
+      <c r="N35" s="143"/>
+      <c r="O35" s="143"/>
+      <c r="P35" s="143"/>
+      <c r="Q35" s="143"/>
+      <c r="R35" s="143"/>
+      <c r="S35" s="143"/>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A36" s="143">
+        <v>131</v>
+      </c>
+      <c r="B36" s="143" t="s">
+        <v>349</v>
+      </c>
+      <c r="C36" s="143" t="s">
+        <v>319</v>
+      </c>
+      <c r="D36" s="143">
+        <v>96166</v>
+      </c>
+      <c r="E36" s="143">
+        <v>29</v>
+      </c>
+      <c r="F36" s="143">
+        <v>2</v>
+      </c>
+      <c r="G36" s="143"/>
+      <c r="H36" s="143"/>
+      <c r="I36" s="143"/>
+      <c r="J36" s="143"/>
+      <c r="K36" s="143"/>
+      <c r="L36" s="143"/>
+      <c r="M36" s="143"/>
+      <c r="N36" s="143"/>
+      <c r="O36" s="143"/>
+      <c r="P36" s="143"/>
+      <c r="Q36" s="143"/>
+      <c r="R36" s="143"/>
+      <c r="S36" s="143"/>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A37" s="143">
+        <v>111</v>
+      </c>
+      <c r="B37" s="143" t="s">
+        <v>350</v>
+      </c>
+      <c r="C37" s="143" t="s">
+        <v>232</v>
+      </c>
+      <c r="D37" s="143">
+        <v>115444</v>
+      </c>
+      <c r="E37" s="143">
+        <v>27</v>
+      </c>
+      <c r="F37" s="143">
+        <v>2</v>
+      </c>
+      <c r="G37" s="143"/>
+      <c r="H37" s="143"/>
+      <c r="I37" s="143"/>
+      <c r="J37" s="143"/>
+      <c r="K37" s="143"/>
+      <c r="L37" s="143"/>
+      <c r="M37" s="143"/>
+      <c r="N37" s="143"/>
+      <c r="O37" s="143"/>
+      <c r="P37" s="143"/>
+      <c r="Q37" s="143"/>
+      <c r="R37" s="143"/>
+      <c r="S37" s="143"/>
+    </row>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A38" s="143">
+        <v>154</v>
+      </c>
+      <c r="B38" s="143" t="s">
+        <v>351</v>
+      </c>
+      <c r="C38" s="143" t="s">
+        <v>20</v>
+      </c>
+      <c r="D38" s="143">
+        <v>65000</v>
+      </c>
+      <c r="E38" s="143">
+        <v>23</v>
+      </c>
+      <c r="F38" s="143">
+        <v>11</v>
+      </c>
+      <c r="G38" s="143"/>
+      <c r="H38" s="143"/>
+      <c r="I38" s="143"/>
+      <c r="J38" s="143"/>
+      <c r="K38" s="143"/>
+      <c r="L38" s="143"/>
+      <c r="M38" s="143"/>
+      <c r="N38" s="143"/>
+      <c r="O38" s="143"/>
+      <c r="P38" s="143"/>
+      <c r="Q38" s="143"/>
+      <c r="R38" s="143"/>
+      <c r="S38" s="143"/>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A39" s="143">
+        <v>177</v>
+      </c>
+      <c r="B39" s="143" t="s">
+        <v>352</v>
+      </c>
+      <c r="C39" s="143" t="s">
+        <v>313</v>
+      </c>
+      <c r="D39" s="143">
+        <v>44179</v>
+      </c>
+      <c r="E39" s="143">
+        <v>49</v>
+      </c>
+      <c r="F39" s="143">
+        <v>8</v>
+      </c>
+      <c r="G39" s="143"/>
+      <c r="H39" s="143"/>
+      <c r="I39" s="143"/>
+      <c r="J39" s="143"/>
+      <c r="K39" s="143"/>
+      <c r="L39" s="143"/>
+      <c r="M39" s="143"/>
+      <c r="N39" s="143"/>
+      <c r="O39" s="143"/>
+      <c r="P39" s="143"/>
+      <c r="Q39" s="143"/>
+      <c r="R39" s="143"/>
+      <c r="S39" s="143"/>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A40" s="143">
+        <v>120</v>
+      </c>
+      <c r="B40" s="143" t="s">
+        <v>353</v>
+      </c>
+      <c r="C40" s="143" t="s">
+        <v>319</v>
+      </c>
+      <c r="D40" s="143">
+        <v>108533</v>
+      </c>
+      <c r="E40" s="143">
+        <v>35</v>
+      </c>
+      <c r="F40" s="143">
+        <v>1</v>
+      </c>
+      <c r="G40" s="143"/>
+      <c r="H40" s="143"/>
+      <c r="I40" s="143"/>
+      <c r="J40" s="143"/>
+      <c r="K40" s="143"/>
+      <c r="L40" s="143"/>
+      <c r="M40" s="143"/>
+      <c r="N40" s="143"/>
+      <c r="O40" s="143"/>
+      <c r="P40" s="143"/>
+      <c r="Q40" s="143"/>
+      <c r="R40" s="143"/>
+      <c r="S40" s="143"/>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A41" s="143">
+        <v>123</v>
+      </c>
+      <c r="B41" s="143" t="s">
+        <v>354</v>
+      </c>
+      <c r="C41" s="143" t="s">
+        <v>45</v>
+      </c>
+      <c r="D41" s="143">
+        <v>49685</v>
+      </c>
+      <c r="E41" s="143">
+        <v>43</v>
+      </c>
+      <c r="F41" s="143">
+        <v>10</v>
+      </c>
+      <c r="G41" s="143"/>
+      <c r="H41" s="143"/>
+      <c r="I41" s="143"/>
+      <c r="J41" s="143"/>
+      <c r="K41" s="143"/>
+      <c r="L41" s="143"/>
+      <c r="M41" s="143"/>
+      <c r="N41" s="143"/>
+      <c r="O41" s="143"/>
+      <c r="P41" s="143"/>
+      <c r="Q41" s="143"/>
+      <c r="R41" s="143"/>
+      <c r="S41" s="143"/>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A42" s="143">
+        <v>173</v>
+      </c>
+      <c r="B42" s="143" t="s">
+        <v>355</v>
+      </c>
+      <c r="C42" s="143" t="s">
+        <v>232</v>
+      </c>
+      <c r="D42" s="143">
+        <v>65893</v>
+      </c>
+      <c r="E42" s="143">
+        <v>35</v>
+      </c>
+      <c r="F42" s="143">
+        <v>12</v>
+      </c>
+      <c r="G42" s="143"/>
+      <c r="H42" s="143"/>
+      <c r="I42" s="143"/>
+      <c r="J42" s="143"/>
+      <c r="K42" s="143"/>
+      <c r="L42" s="143"/>
+      <c r="M42" s="143"/>
+      <c r="N42" s="143"/>
+      <c r="O42" s="143"/>
+      <c r="P42" s="143"/>
+      <c r="Q42" s="143"/>
+      <c r="R42" s="143"/>
+      <c r="S42" s="143"/>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A43" s="143">
+        <v>115</v>
+      </c>
+      <c r="B43" s="143" t="s">
+        <v>356</v>
+      </c>
+      <c r="C43" s="143" t="s">
+        <v>46</v>
+      </c>
+      <c r="D43" s="143">
+        <v>95842</v>
+      </c>
+      <c r="E43" s="143">
+        <v>49</v>
+      </c>
+      <c r="F43" s="143">
+        <v>11</v>
+      </c>
+      <c r="G43" s="143"/>
+      <c r="H43" s="143"/>
+      <c r="I43" s="143"/>
+      <c r="J43" s="143"/>
+      <c r="K43" s="143"/>
+      <c r="L43" s="143"/>
+      <c r="M43" s="143"/>
+      <c r="N43" s="143"/>
+      <c r="O43" s="143"/>
+      <c r="P43" s="143"/>
+      <c r="Q43" s="143"/>
+      <c r="R43" s="143"/>
+      <c r="S43" s="143"/>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A44" s="143">
+        <v>170</v>
+      </c>
+      <c r="B44" s="143" t="s">
+        <v>357</v>
+      </c>
+      <c r="C44" s="143" t="s">
+        <v>20</v>
+      </c>
+      <c r="D44" s="143">
+        <v>103228</v>
+      </c>
+      <c r="E44" s="143">
+        <v>33</v>
+      </c>
+      <c r="F44" s="143">
+        <v>10</v>
+      </c>
+      <c r="G44" s="143"/>
+      <c r="H44" s="143"/>
+      <c r="I44" s="143"/>
+      <c r="J44" s="143"/>
+      <c r="K44" s="143"/>
+      <c r="L44" s="143"/>
+      <c r="M44" s="143"/>
+      <c r="N44" s="143"/>
+      <c r="O44" s="143"/>
+      <c r="P44" s="143"/>
+      <c r="Q44" s="143"/>
+      <c r="R44" s="143"/>
+      <c r="S44" s="143"/>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A45" s="143">
+        <v>135</v>
+      </c>
+      <c r="B45" s="143" t="s">
+        <v>358</v>
+      </c>
+      <c r="C45" s="143" t="s">
+        <v>45</v>
+      </c>
+      <c r="D45" s="143">
+        <v>50441</v>
+      </c>
+      <c r="E45" s="143">
+        <v>28</v>
+      </c>
+      <c r="F45" s="143">
+        <v>6</v>
+      </c>
+      <c r="G45" s="143"/>
+      <c r="H45" s="143"/>
+      <c r="I45" s="143"/>
+      <c r="J45" s="143"/>
+      <c r="K45" s="143"/>
+      <c r="L45" s="143"/>
+      <c r="M45" s="143"/>
+      <c r="N45" s="143"/>
+      <c r="O45" s="143"/>
+      <c r="P45" s="143"/>
+      <c r="Q45" s="143"/>
+      <c r="R45" s="143"/>
+      <c r="S45" s="143"/>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A46" s="143">
+        <v>174</v>
+      </c>
+      <c r="B46" s="143" t="s">
+        <v>359</v>
+      </c>
+      <c r="C46" s="143" t="s">
+        <v>46</v>
+      </c>
+      <c r="D46" s="143">
+        <v>59472</v>
+      </c>
+      <c r="E46" s="143">
+        <v>26</v>
+      </c>
+      <c r="F46" s="143">
+        <v>10</v>
+      </c>
+      <c r="G46" s="143"/>
+      <c r="H46" s="143"/>
+      <c r="I46" s="143"/>
+      <c r="J46" s="143"/>
+      <c r="K46" s="143"/>
+      <c r="L46" s="143"/>
+      <c r="M46" s="143"/>
+      <c r="N46" s="143"/>
+      <c r="O46" s="143"/>
+      <c r="P46" s="143"/>
+      <c r="Q46" s="143"/>
+      <c r="R46" s="143"/>
+      <c r="S46" s="143"/>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A47" s="143">
+        <v>103</v>
+      </c>
+      <c r="B47" s="143" t="s">
+        <v>360</v>
+      </c>
+      <c r="C47" s="143" t="s">
+        <v>20</v>
+      </c>
+      <c r="D47" s="143">
+        <v>71452</v>
+      </c>
+      <c r="E47" s="143">
+        <v>34</v>
+      </c>
+      <c r="F47" s="143">
+        <v>12</v>
+      </c>
+      <c r="G47" s="143"/>
+      <c r="H47" s="143"/>
+      <c r="I47" s="143"/>
+      <c r="J47" s="143"/>
+      <c r="K47" s="143"/>
+      <c r="L47" s="143"/>
+      <c r="M47" s="143"/>
+      <c r="N47" s="143"/>
+      <c r="O47" s="143"/>
+      <c r="P47" s="143"/>
+      <c r="Q47" s="143"/>
+      <c r="R47" s="143"/>
+      <c r="S47" s="143"/>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A48" s="143">
+        <v>149</v>
+      </c>
+      <c r="B48" s="143" t="s">
+        <v>361</v>
+      </c>
+      <c r="C48" s="143" t="s">
+        <v>45</v>
+      </c>
+      <c r="D48" s="143">
+        <v>46918</v>
+      </c>
+      <c r="E48" s="143">
+        <v>50</v>
+      </c>
+      <c r="F48" s="143">
+        <v>3</v>
+      </c>
+      <c r="G48" s="143"/>
+      <c r="H48" s="143"/>
+      <c r="I48" s="143"/>
+      <c r="J48" s="143"/>
+      <c r="K48" s="143"/>
+      <c r="L48" s="143"/>
+      <c r="M48" s="143"/>
+      <c r="N48" s="143"/>
+      <c r="O48" s="143"/>
+      <c r="P48" s="143"/>
+      <c r="Q48" s="143"/>
+      <c r="R48" s="143"/>
+      <c r="S48" s="143"/>
+    </row>
+    <row r="49" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A49" s="143">
+        <v>171</v>
+      </c>
+      <c r="B49" s="143" t="s">
+        <v>362</v>
+      </c>
+      <c r="C49" s="143" t="s">
+        <v>46</v>
+      </c>
+      <c r="D49" s="143">
+        <v>65133</v>
+      </c>
+      <c r="E49" s="143">
+        <v>41</v>
+      </c>
+      <c r="F49" s="143">
+        <v>9</v>
+      </c>
+      <c r="G49" s="143"/>
+      <c r="H49" s="143"/>
+      <c r="I49" s="143"/>
+      <c r="J49" s="143"/>
+      <c r="K49" s="143"/>
+      <c r="L49" s="143"/>
+      <c r="M49" s="143"/>
+      <c r="N49" s="143"/>
+      <c r="O49" s="143"/>
+      <c r="P49" s="143"/>
+      <c r="Q49" s="143"/>
+      <c r="R49" s="143"/>
+      <c r="S49" s="143"/>
+    </row>
+    <row r="50" spans="1:19" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A50" s="143">
+        <v>159</v>
+      </c>
+      <c r="B50" s="143" t="s">
+        <v>363</v>
+      </c>
+      <c r="C50" s="143" t="s">
+        <v>232</v>
+      </c>
+      <c r="D50" s="143">
+        <v>112870</v>
+      </c>
+      <c r="E50" s="143">
+        <v>41</v>
+      </c>
+      <c r="F50" s="143">
+        <v>1</v>
+      </c>
+      <c r="G50" s="143"/>
+      <c r="H50" s="143"/>
+      <c r="I50" s="143"/>
+      <c r="J50" s="143"/>
+      <c r="K50" s="143"/>
+      <c r="L50" s="143"/>
+      <c r="M50" s="143"/>
+      <c r="N50" s="143"/>
+      <c r="O50" s="143"/>
+      <c r="P50" s="143"/>
+      <c r="Q50" s="143"/>
+      <c r="R50" s="143"/>
+      <c r="S50" s="143"/>
+    </row>
+    <row r="51" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A51" s="143">
+        <v>107</v>
+      </c>
+      <c r="B51" s="143" t="s">
+        <v>364</v>
+      </c>
+      <c r="C51" s="143" t="s">
+        <v>313</v>
+      </c>
+      <c r="D51" s="143">
+        <v>62176</v>
+      </c>
+      <c r="E51" s="143">
+        <v>40</v>
+      </c>
+      <c r="F51" s="143">
+        <v>11</v>
+      </c>
+      <c r="G51" s="143"/>
+      <c r="H51" s="143"/>
+      <c r="I51" s="143"/>
+      <c r="J51" s="143"/>
+      <c r="K51" s="143"/>
+      <c r="L51" s="143"/>
+      <c r="M51" s="143"/>
+      <c r="N51" s="143"/>
+      <c r="O51" s="143"/>
+      <c r="P51" s="143"/>
+      <c r="Q51" s="143"/>
+      <c r="R51" s="143"/>
+      <c r="S51" s="143"/>
+    </row>
+    <row r="52" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A52" s="143">
+        <v>158</v>
+      </c>
+      <c r="B52" s="143" t="s">
+        <v>365</v>
+      </c>
+      <c r="C52" s="143" t="s">
+        <v>45</v>
+      </c>
+      <c r="D52" s="143">
+        <v>53061</v>
+      </c>
+      <c r="E52" s="143">
+        <v>32</v>
+      </c>
+      <c r="F52" s="143">
+        <v>7</v>
+      </c>
+      <c r="G52" s="143"/>
+      <c r="H52" s="143"/>
+      <c r="I52" s="143"/>
+      <c r="J52" s="143"/>
+      <c r="K52" s="143"/>
+      <c r="L52" s="143"/>
+      <c r="M52" s="143"/>
+      <c r="N52" s="143"/>
+      <c r="O52" s="143"/>
+      <c r="P52" s="143"/>
+      <c r="Q52" s="143"/>
+      <c r="R52" s="143"/>
+      <c r="S52" s="143"/>
+    </row>
+    <row r="53" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A53" s="143">
+        <v>142</v>
+      </c>
+      <c r="B53" s="143" t="s">
+        <v>366</v>
+      </c>
+      <c r="C53" s="143" t="s">
+        <v>313</v>
+      </c>
+      <c r="D53" s="143">
+        <v>94691</v>
+      </c>
+      <c r="E53" s="143">
+        <v>41</v>
+      </c>
+      <c r="F53" s="143">
+        <v>4</v>
+      </c>
+      <c r="G53" s="143"/>
+      <c r="H53" s="143"/>
+      <c r="I53" s="143"/>
+      <c r="J53" s="143"/>
+      <c r="K53" s="143"/>
+      <c r="L53" s="143"/>
+      <c r="M53" s="143"/>
+      <c r="N53" s="143"/>
+      <c r="O53" s="143"/>
+      <c r="P53" s="143"/>
+      <c r="Q53" s="143"/>
+      <c r="R53" s="143"/>
+      <c r="S53" s="143"/>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A54" s="143">
+        <v>178</v>
+      </c>
+      <c r="B54" s="143" t="s">
+        <v>367</v>
+      </c>
+      <c r="C54" s="143" t="s">
+        <v>232</v>
+      </c>
+      <c r="D54" s="143">
+        <v>63352</v>
+      </c>
+      <c r="E54" s="143">
+        <v>28</v>
+      </c>
+      <c r="F54" s="143">
+        <v>3</v>
+      </c>
+      <c r="G54" s="143"/>
+      <c r="H54" s="143"/>
+      <c r="I54" s="143"/>
+      <c r="J54" s="143"/>
+      <c r="K54" s="143"/>
+      <c r="L54" s="143"/>
+      <c r="M54" s="143"/>
+      <c r="N54" s="143"/>
+      <c r="O54" s="143"/>
+      <c r="P54" s="143"/>
+      <c r="Q54" s="143"/>
+      <c r="R54" s="143"/>
+      <c r="S54" s="143"/>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A55" s="143">
+        <v>127</v>
+      </c>
+      <c r="B55" s="143" t="s">
+        <v>368</v>
+      </c>
+      <c r="C55" s="143" t="s">
+        <v>313</v>
+      </c>
+      <c r="D55" s="143">
+        <v>43124</v>
+      </c>
+      <c r="E55" s="143">
+        <v>24</v>
+      </c>
+      <c r="F55" s="143">
+        <v>3</v>
+      </c>
+      <c r="G55" s="143"/>
+      <c r="H55" s="143"/>
+      <c r="I55" s="143"/>
+      <c r="J55" s="143"/>
+      <c r="K55" s="143"/>
+      <c r="L55" s="143"/>
+      <c r="M55" s="143"/>
+      <c r="N55" s="143"/>
+      <c r="O55" s="143"/>
+      <c r="P55" s="143"/>
+      <c r="Q55" s="143"/>
+      <c r="R55" s="143"/>
+      <c r="S55" s="143"/>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A56" s="143">
+        <v>116</v>
+      </c>
+      <c r="B56" s="143" t="s">
+        <v>369</v>
+      </c>
+      <c r="C56" s="143" t="s">
+        <v>46</v>
+      </c>
+      <c r="D56" s="143">
+        <v>40700</v>
+      </c>
+      <c r="E56" s="143">
+        <v>32</v>
+      </c>
+      <c r="F56" s="143">
+        <v>4</v>
+      </c>
+      <c r="G56" s="143"/>
+      <c r="H56" s="143"/>
+      <c r="I56" s="143"/>
+      <c r="J56" s="143"/>
+      <c r="K56" s="143"/>
+      <c r="L56" s="143"/>
+      <c r="M56" s="143"/>
+      <c r="N56" s="143"/>
+      <c r="O56" s="143"/>
+      <c r="P56" s="143"/>
+      <c r="Q56" s="143"/>
+      <c r="R56" s="143"/>
+      <c r="S56" s="143"/>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A57" s="143">
+        <v>114</v>
+      </c>
+      <c r="B57" s="143" t="s">
+        <v>370</v>
+      </c>
+      <c r="C57" s="143" t="s">
+        <v>45</v>
+      </c>
+      <c r="D57" s="143">
+        <v>104015</v>
+      </c>
+      <c r="E57" s="143">
+        <v>40</v>
+      </c>
+      <c r="F57" s="143">
+        <v>1</v>
+      </c>
+      <c r="G57" s="143"/>
+      <c r="H57" s="143"/>
+      <c r="I57" s="143"/>
+      <c r="J57" s="143"/>
+      <c r="K57" s="143"/>
+      <c r="L57" s="143"/>
+      <c r="M57" s="143"/>
+      <c r="N57" s="143"/>
+      <c r="O57" s="143"/>
+      <c r="P57" s="143"/>
+      <c r="Q57" s="143"/>
+      <c r="R57" s="143"/>
+      <c r="S57" s="143"/>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A58" s="143">
+        <v>137</v>
+      </c>
+      <c r="B58" s="143" t="s">
+        <v>371</v>
+      </c>
+      <c r="C58" s="143" t="s">
+        <v>45</v>
+      </c>
+      <c r="D58" s="143">
+        <v>55000</v>
+      </c>
+      <c r="E58" s="143">
+        <v>38</v>
+      </c>
+      <c r="F58" s="143">
+        <v>3</v>
+      </c>
+      <c r="G58" s="143"/>
+      <c r="H58" s="143"/>
+      <c r="I58" s="143"/>
+      <c r="J58" s="143"/>
+      <c r="K58" s="143"/>
+      <c r="L58" s="143"/>
+      <c r="M58" s="143"/>
+      <c r="N58" s="143"/>
+      <c r="O58" s="143"/>
+      <c r="P58" s="143"/>
+      <c r="Q58" s="143"/>
+      <c r="R58" s="143"/>
+      <c r="S58" s="143"/>
+    </row>
+    <row r="59" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A59" s="143">
+        <v>161</v>
+      </c>
+      <c r="B59" s="143" t="s">
+        <v>372</v>
+      </c>
+      <c r="C59" s="143" t="s">
+        <v>232</v>
+      </c>
+      <c r="D59" s="143">
+        <v>75486</v>
+      </c>
+      <c r="E59" s="143">
+        <v>38</v>
+      </c>
+      <c r="F59" s="143">
+        <v>2</v>
+      </c>
+      <c r="G59" s="143"/>
+      <c r="H59" s="143"/>
+      <c r="I59" s="143"/>
+      <c r="J59" s="143"/>
+      <c r="K59" s="143"/>
+      <c r="L59" s="143"/>
+      <c r="M59" s="143"/>
+      <c r="N59" s="143"/>
+      <c r="O59" s="143"/>
+      <c r="P59" s="143"/>
+      <c r="Q59" s="143"/>
+      <c r="R59" s="143"/>
+      <c r="S59" s="143"/>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A60" s="143">
+        <v>128</v>
+      </c>
+      <c r="B60" s="143" t="s">
+        <v>373</v>
+      </c>
+      <c r="C60" s="143" t="s">
+        <v>46</v>
+      </c>
+      <c r="D60" s="143">
+        <v>105503</v>
+      </c>
+      <c r="E60" s="143">
+        <v>46</v>
+      </c>
+      <c r="F60" s="143">
+        <v>3</v>
+      </c>
+      <c r="G60" s="143"/>
+      <c r="H60" s="143"/>
+      <c r="I60" s="143"/>
+      <c r="J60" s="143"/>
+      <c r="K60" s="143"/>
+      <c r="L60" s="143"/>
+      <c r="M60" s="143"/>
+      <c r="N60" s="143"/>
+      <c r="O60" s="143"/>
+      <c r="P60" s="143"/>
+      <c r="Q60" s="143"/>
+      <c r="R60" s="143"/>
+      <c r="S60" s="143"/>
+    </row>
+    <row r="61" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A61" s="143">
+        <v>167</v>
+      </c>
+      <c r="B61" s="143" t="s">
+        <v>374</v>
+      </c>
+      <c r="C61" s="143" t="s">
+        <v>319</v>
+      </c>
+      <c r="D61" s="143">
+        <v>117330</v>
+      </c>
+      <c r="E61" s="143">
+        <v>47</v>
+      </c>
+      <c r="F61" s="143">
+        <v>11</v>
+      </c>
+      <c r="G61" s="143"/>
+      <c r="H61" s="143"/>
+      <c r="I61" s="143"/>
+      <c r="J61" s="143"/>
+      <c r="K61" s="143"/>
+      <c r="L61" s="143"/>
+      <c r="M61" s="143"/>
+      <c r="N61" s="143"/>
+      <c r="O61" s="143"/>
+      <c r="P61" s="143"/>
+      <c r="Q61" s="143"/>
+      <c r="R61" s="143"/>
+      <c r="S61" s="143"/>
+    </row>
+    <row r="62" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A62" s="143">
+        <v>172</v>
+      </c>
+      <c r="B62" s="143" t="s">
+        <v>375</v>
+      </c>
+      <c r="C62" s="143" t="s">
+        <v>313</v>
+      </c>
+      <c r="D62" s="143">
+        <v>87168</v>
+      </c>
+      <c r="E62" s="143">
+        <v>36</v>
+      </c>
+      <c r="F62" s="143">
+        <v>2</v>
+      </c>
+      <c r="G62" s="143"/>
+      <c r="H62" s="143"/>
+      <c r="I62" s="143"/>
+      <c r="J62" s="143"/>
+      <c r="K62" s="143"/>
+      <c r="L62" s="143"/>
+      <c r="M62" s="143"/>
+      <c r="N62" s="143"/>
+      <c r="O62" s="143"/>
+      <c r="P62" s="143"/>
+      <c r="Q62" s="143"/>
+      <c r="R62" s="143"/>
+      <c r="S62" s="143"/>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A63" s="143">
+        <v>169</v>
+      </c>
+      <c r="B63" s="143" t="s">
+        <v>376</v>
+      </c>
+      <c r="C63" s="143" t="s">
+        <v>46</v>
+      </c>
+      <c r="D63" s="143">
+        <v>113106</v>
+      </c>
+      <c r="E63" s="143">
+        <v>46</v>
+      </c>
+      <c r="F63" s="143">
+        <v>2</v>
+      </c>
+      <c r="G63" s="143"/>
+      <c r="H63" s="143"/>
+      <c r="I63" s="143"/>
+      <c r="J63" s="143"/>
+      <c r="K63" s="143"/>
+      <c r="L63" s="143"/>
+      <c r="M63" s="143"/>
+      <c r="N63" s="143"/>
+      <c r="O63" s="143"/>
+      <c r="P63" s="143"/>
+      <c r="Q63" s="143"/>
+      <c r="R63" s="143"/>
+      <c r="S63" s="143"/>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A64" s="143">
+        <v>152</v>
+      </c>
+      <c r="B64" s="143" t="s">
+        <v>377</v>
+      </c>
+      <c r="C64" s="143" t="s">
+        <v>232</v>
+      </c>
+      <c r="D64" s="143">
+        <v>100483</v>
+      </c>
+      <c r="E64" s="143">
+        <v>35</v>
+      </c>
+      <c r="F64" s="143">
+        <v>10</v>
+      </c>
+      <c r="G64" s="143"/>
+      <c r="H64" s="143"/>
+      <c r="I64" s="143"/>
+      <c r="J64" s="143"/>
+      <c r="K64" s="143"/>
+      <c r="L64" s="143"/>
+      <c r="M64" s="143"/>
+      <c r="N64" s="143"/>
+      <c r="O64" s="143"/>
+      <c r="P64" s="143"/>
+      <c r="Q64" s="143"/>
+      <c r="R64" s="143"/>
+      <c r="S64" s="143"/>
+    </row>
+    <row r="65" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A65" s="143">
+        <v>179</v>
+      </c>
+      <c r="B65" s="143" t="s">
+        <v>378</v>
+      </c>
+      <c r="C65" s="143" t="s">
+        <v>319</v>
+      </c>
+      <c r="D65" s="143">
+        <v>62841</v>
+      </c>
+      <c r="E65" s="143">
+        <v>33</v>
+      </c>
+      <c r="F65" s="143">
+        <v>10</v>
+      </c>
+      <c r="G65" s="143"/>
+      <c r="H65" s="143"/>
+      <c r="I65" s="143"/>
+      <c r="J65" s="143"/>
+      <c r="K65" s="143"/>
+      <c r="L65" s="143"/>
+      <c r="M65" s="143"/>
+      <c r="N65" s="143"/>
+      <c r="O65" s="143"/>
+      <c r="P65" s="143"/>
+      <c r="Q65" s="143"/>
+      <c r="R65" s="143"/>
+      <c r="S65" s="143"/>
+    </row>
+    <row r="66" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A66" s="143">
+        <v>104</v>
+      </c>
+      <c r="B66" s="143" t="s">
+        <v>379</v>
+      </c>
+      <c r="C66" s="143" t="s">
+        <v>45</v>
+      </c>
+      <c r="D66" s="143">
+        <v>72493</v>
+      </c>
+      <c r="E66" s="143">
+        <v>36</v>
+      </c>
+      <c r="F66" s="143">
+        <v>2</v>
+      </c>
+      <c r="G66" s="143"/>
+      <c r="H66" s="143"/>
+      <c r="I66" s="143"/>
+      <c r="J66" s="143"/>
+      <c r="K66" s="143"/>
+      <c r="L66" s="143"/>
+      <c r="M66" s="143"/>
+      <c r="N66" s="143"/>
+      <c r="O66" s="143"/>
+      <c r="P66" s="143"/>
+      <c r="Q66" s="143"/>
+      <c r="R66" s="143"/>
+      <c r="S66" s="143"/>
+    </row>
+    <row r="67" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A67" s="143">
+        <v>181</v>
+      </c>
+      <c r="B67" s="143" t="s">
+        <v>380</v>
+      </c>
+      <c r="C67" s="143" t="s">
+        <v>45</v>
+      </c>
+      <c r="D67" s="143">
+        <v>110158</v>
+      </c>
+      <c r="E67" s="143">
+        <v>22</v>
+      </c>
+      <c r="F67" s="143">
+        <v>11</v>
+      </c>
+      <c r="G67" s="143"/>
+      <c r="H67" s="143"/>
+      <c r="I67" s="143"/>
+      <c r="J67" s="143"/>
+      <c r="K67" s="143"/>
+      <c r="L67" s="143"/>
+      <c r="M67" s="143"/>
+      <c r="N67" s="143"/>
+      <c r="O67" s="143"/>
+      <c r="P67" s="143"/>
+      <c r="Q67" s="143"/>
+      <c r="R67" s="143"/>
+      <c r="S67" s="143"/>
+    </row>
+    <row r="68" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A68" s="143">
+        <v>176</v>
+      </c>
+      <c r="B68" s="143" t="s">
+        <v>381</v>
+      </c>
+      <c r="C68" s="143" t="s">
+        <v>45</v>
+      </c>
+      <c r="D68" s="143">
+        <v>40278</v>
+      </c>
+      <c r="E68" s="143">
+        <v>28</v>
+      </c>
+      <c r="F68" s="143">
+        <v>5</v>
+      </c>
+      <c r="G68" s="143"/>
+      <c r="H68" s="143"/>
+      <c r="I68" s="143"/>
+      <c r="J68" s="143"/>
+      <c r="K68" s="143"/>
+      <c r="L68" s="143"/>
+      <c r="M68" s="143"/>
+      <c r="N68" s="143"/>
+      <c r="O68" s="143"/>
+      <c r="P68" s="143"/>
+      <c r="Q68" s="143"/>
+      <c r="R68" s="143"/>
+      <c r="S68" s="143"/>
+    </row>
+    <row r="69" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A69" s="143">
+        <v>139</v>
+      </c>
+      <c r="B69" s="143" t="s">
+        <v>382</v>
+      </c>
+      <c r="C69" s="143" t="s">
+        <v>46</v>
+      </c>
+      <c r="D69" s="143">
+        <v>83229</v>
+      </c>
+      <c r="E69" s="143">
+        <v>45</v>
+      </c>
+      <c r="F69" s="143">
+        <v>4</v>
+      </c>
+      <c r="G69" s="143"/>
+      <c r="H69" s="143"/>
+      <c r="I69" s="143"/>
+      <c r="J69" s="143"/>
+      <c r="K69" s="143"/>
+      <c r="L69" s="143"/>
+      <c r="M69" s="143"/>
+      <c r="N69" s="143"/>
+      <c r="O69" s="143"/>
+      <c r="P69" s="143"/>
+      <c r="Q69" s="143"/>
+      <c r="R69" s="143"/>
+      <c r="S69" s="143"/>
+    </row>
+    <row r="70" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A70" s="143">
+        <v>166</v>
+      </c>
+      <c r="B70" s="143" t="s">
+        <v>383</v>
+      </c>
+      <c r="C70" s="143" t="s">
+        <v>313</v>
+      </c>
+      <c r="D70" s="143">
+        <v>61845</v>
+      </c>
+      <c r="E70" s="143">
+        <v>43</v>
+      </c>
+      <c r="F70" s="143">
+        <v>8</v>
+      </c>
+      <c r="G70" s="143"/>
+      <c r="H70" s="143"/>
+      <c r="I70" s="143"/>
+      <c r="J70" s="143"/>
+      <c r="K70" s="143"/>
+      <c r="L70" s="143"/>
+      <c r="M70" s="143"/>
+      <c r="N70" s="143"/>
+      <c r="O70" s="143"/>
+      <c r="P70" s="143"/>
+      <c r="Q70" s="143"/>
+      <c r="R70" s="143"/>
+      <c r="S70" s="143"/>
+    </row>
+    <row r="71" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A71" s="143">
+        <v>109</v>
+      </c>
+      <c r="B71" s="143" t="s">
+        <v>384</v>
+      </c>
+      <c r="C71" s="143" t="s">
+        <v>313</v>
+      </c>
+      <c r="D71" s="143">
+        <v>113709</v>
+      </c>
+      <c r="E71" s="143">
+        <v>26</v>
+      </c>
+      <c r="F71" s="143">
+        <v>9</v>
+      </c>
+      <c r="G71" s="143"/>
+      <c r="H71" s="143"/>
+      <c r="I71" s="143"/>
+      <c r="J71" s="143"/>
+      <c r="K71" s="143"/>
+      <c r="L71" s="143"/>
+      <c r="M71" s="143"/>
+      <c r="N71" s="143"/>
+      <c r="O71" s="143"/>
+      <c r="P71" s="143"/>
+      <c r="Q71" s="143"/>
+      <c r="R71" s="143"/>
+      <c r="S71" s="143"/>
+    </row>
+    <row r="72" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A72" s="143">
+        <v>105</v>
+      </c>
+      <c r="B72" s="143" t="s">
+        <v>385</v>
+      </c>
+      <c r="C72" s="143" t="s">
+        <v>46</v>
+      </c>
+      <c r="D72" s="143">
+        <v>73996</v>
+      </c>
+      <c r="E72" s="143">
+        <v>29</v>
+      </c>
+      <c r="F72" s="143">
+        <v>11</v>
+      </c>
+      <c r="G72" s="143"/>
+      <c r="H72" s="143"/>
+      <c r="I72" s="143"/>
+      <c r="J72" s="143"/>
+      <c r="K72" s="143"/>
+      <c r="L72" s="143"/>
+      <c r="M72" s="143"/>
+      <c r="N72" s="143"/>
+      <c r="O72" s="143"/>
+      <c r="P72" s="143"/>
+      <c r="Q72" s="143"/>
+      <c r="R72" s="143"/>
+      <c r="S72" s="143"/>
+    </row>
+    <row r="73" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A73" s="143">
+        <v>108</v>
+      </c>
+      <c r="B73" s="143" t="s">
+        <v>386</v>
+      </c>
+      <c r="C73" s="143" t="s">
+        <v>20</v>
+      </c>
+      <c r="D73" s="143">
+        <v>83372</v>
+      </c>
+      <c r="E73" s="143">
+        <v>33</v>
+      </c>
+      <c r="F73" s="143">
+        <v>5</v>
+      </c>
+      <c r="G73" s="143"/>
+      <c r="H73" s="143"/>
+      <c r="I73" s="143"/>
+      <c r="J73" s="143"/>
+      <c r="K73" s="143"/>
+      <c r="L73" s="143"/>
+      <c r="M73" s="143"/>
+      <c r="N73" s="143"/>
+      <c r="O73" s="143"/>
+      <c r="P73" s="143"/>
+      <c r="Q73" s="143"/>
+      <c r="R73" s="143"/>
+      <c r="S73" s="143"/>
+    </row>
+    <row r="74" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A74" s="143">
+        <v>145</v>
+      </c>
+      <c r="B74" s="143" t="s">
+        <v>387</v>
+      </c>
+      <c r="C74" s="143" t="s">
+        <v>313</v>
+      </c>
+      <c r="D74" s="143">
+        <v>43137</v>
+      </c>
+      <c r="E74" s="143">
+        <v>36</v>
+      </c>
+      <c r="F74" s="143">
+        <v>11</v>
+      </c>
+      <c r="G74" s="143"/>
+      <c r="H74" s="143"/>
+      <c r="I74" s="143"/>
+      <c r="J74" s="143"/>
+      <c r="K74" s="143"/>
+      <c r="L74" s="143"/>
+      <c r="M74" s="143"/>
+      <c r="N74" s="143"/>
+      <c r="O74" s="143"/>
+      <c r="P74" s="143"/>
+      <c r="Q74" s="143"/>
+      <c r="R74" s="143"/>
+      <c r="S74" s="143"/>
+    </row>
+    <row r="75" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A75" s="143">
+        <v>113</v>
+      </c>
+      <c r="B75" s="143" t="s">
+        <v>388</v>
+      </c>
+      <c r="C75" s="143" t="s">
+        <v>232</v>
+      </c>
+      <c r="D75" s="143">
+        <v>62420</v>
+      </c>
+      <c r="E75" s="143">
+        <v>27</v>
+      </c>
+      <c r="F75" s="143">
+        <v>5</v>
+      </c>
+      <c r="G75" s="143"/>
+      <c r="H75" s="143"/>
+      <c r="I75" s="143"/>
+      <c r="J75" s="143"/>
+      <c r="K75" s="143"/>
+      <c r="L75" s="143"/>
+      <c r="M75" s="143"/>
+      <c r="N75" s="143"/>
+      <c r="O75" s="143"/>
+      <c r="P75" s="143"/>
+      <c r="Q75" s="143"/>
+      <c r="R75" s="143"/>
+      <c r="S75" s="143"/>
+    </row>
+    <row r="76" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A76" s="143">
+        <v>163</v>
+      </c>
+      <c r="B76" s="143" t="s">
+        <v>389</v>
+      </c>
+      <c r="C76" s="143" t="s">
+        <v>319</v>
+      </c>
+      <c r="D76" s="143">
+        <v>67321</v>
+      </c>
+      <c r="E76" s="143">
+        <v>46</v>
+      </c>
+      <c r="F76" s="143">
+        <v>4</v>
+      </c>
+      <c r="G76" s="143"/>
+      <c r="H76" s="143"/>
+      <c r="I76" s="143"/>
+      <c r="J76" s="143"/>
+      <c r="K76" s="143"/>
+      <c r="L76" s="143"/>
+      <c r="M76" s="143"/>
+      <c r="N76" s="143"/>
+      <c r="O76" s="143"/>
+      <c r="P76" s="143"/>
+      <c r="Q76" s="143"/>
+      <c r="R76" s="143"/>
+      <c r="S76" s="143"/>
+    </row>
+    <row r="77" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A77" s="143">
+        <v>130</v>
+      </c>
+      <c r="B77" s="143" t="s">
+        <v>390</v>
+      </c>
+      <c r="C77" s="143" t="s">
+        <v>319</v>
+      </c>
+      <c r="D77" s="143">
+        <v>46890</v>
+      </c>
+      <c r="E77" s="143">
+        <v>34</v>
+      </c>
+      <c r="F77" s="143">
+        <v>3</v>
+      </c>
+      <c r="G77" s="143"/>
+      <c r="H77" s="143"/>
+      <c r="I77" s="143"/>
+      <c r="J77" s="143"/>
+      <c r="K77" s="143"/>
+      <c r="L77" s="143"/>
+      <c r="M77" s="143"/>
+      <c r="N77" s="143"/>
+      <c r="O77" s="143"/>
+      <c r="P77" s="143"/>
+      <c r="Q77" s="143"/>
+      <c r="R77" s="143"/>
+      <c r="S77" s="143"/>
+    </row>
+    <row r="78" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A78" s="143">
+        <v>138</v>
+      </c>
+      <c r="B78" s="143" t="s">
+        <v>391</v>
+      </c>
+      <c r="C78" s="143" t="s">
+        <v>232</v>
+      </c>
+      <c r="D78" s="143">
+        <v>96858</v>
+      </c>
+      <c r="E78" s="143">
+        <v>36</v>
+      </c>
+      <c r="F78" s="143">
+        <v>11</v>
+      </c>
+      <c r="G78" s="143"/>
+      <c r="H78" s="143"/>
+      <c r="I78" s="143"/>
+      <c r="J78" s="143"/>
+      <c r="K78" s="143"/>
+      <c r="L78" s="143"/>
+      <c r="M78" s="143"/>
+      <c r="N78" s="143"/>
+      <c r="O78" s="143"/>
+      <c r="P78" s="143"/>
+      <c r="Q78" s="143"/>
+      <c r="R78" s="143"/>
+      <c r="S78" s="143"/>
+    </row>
+    <row r="79" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A79" s="143">
+        <v>106</v>
+      </c>
+      <c r="B79" s="143" t="s">
+        <v>392</v>
+      </c>
+      <c r="C79" s="143" t="s">
+        <v>232</v>
+      </c>
+      <c r="D79" s="143">
+        <v>104443</v>
+      </c>
+      <c r="E79" s="143">
+        <v>52</v>
+      </c>
+      <c r="F79" s="143">
+        <v>6</v>
+      </c>
+      <c r="G79" s="143"/>
+      <c r="H79" s="143"/>
+      <c r="I79" s="143"/>
+      <c r="J79" s="143"/>
+      <c r="K79" s="143"/>
+      <c r="L79" s="143"/>
+      <c r="M79" s="143"/>
+      <c r="N79" s="143"/>
+      <c r="O79" s="143"/>
+      <c r="P79" s="143"/>
+      <c r="Q79" s="143"/>
+      <c r="R79" s="143"/>
+      <c r="S79" s="143"/>
+    </row>
+    <row r="80" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A80" s="143">
+        <v>175</v>
+      </c>
+      <c r="B80" s="143" t="s">
+        <v>393</v>
+      </c>
+      <c r="C80" s="143" t="s">
+        <v>232</v>
+      </c>
+      <c r="D80" s="143">
+        <v>73495</v>
+      </c>
+      <c r="E80" s="143">
+        <v>51</v>
+      </c>
+      <c r="F80" s="143">
+        <v>7</v>
+      </c>
+      <c r="G80" s="143"/>
+      <c r="H80" s="143"/>
+      <c r="I80" s="143"/>
+      <c r="J80" s="143"/>
+      <c r="K80" s="143"/>
+      <c r="L80" s="143"/>
+      <c r="M80" s="143"/>
+      <c r="N80" s="143"/>
+      <c r="O80" s="143"/>
+      <c r="P80" s="143"/>
+      <c r="Q80" s="143"/>
+      <c r="R80" s="143"/>
+      <c r="S80" s="143"/>
+    </row>
+    <row r="81" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A81" s="143">
+        <v>112</v>
+      </c>
+      <c r="B81" s="143" t="s">
+        <v>394</v>
+      </c>
+      <c r="C81" s="143" t="s">
+        <v>313</v>
+      </c>
+      <c r="D81" s="143">
+        <v>73577</v>
+      </c>
+      <c r="E81" s="143">
+        <v>24</v>
+      </c>
+      <c r="F81" s="143">
+        <v>4</v>
+      </c>
+      <c r="G81" s="143"/>
+      <c r="H81" s="143"/>
+      <c r="I81" s="143"/>
+      <c r="J81" s="143"/>
+      <c r="K81" s="143"/>
+      <c r="L81" s="143"/>
+      <c r="M81" s="143"/>
+      <c r="N81" s="143"/>
+      <c r="O81" s="143"/>
+      <c r="P81" s="143"/>
+      <c r="Q81" s="143"/>
+      <c r="R81" s="143"/>
+      <c r="S81" s="143"/>
+    </row>
+    <row r="82" spans="1:19" x14ac:dyDescent="0.3">
+      <c r="A82" s="143">
+        <v>136</v>
+      </c>
+      <c r="B82" s="143" t="s">
+        <v>395</v>
+      </c>
+      <c r="C82" s="143" t="s">
+        <v>45</v>
+      </c>
+      <c r="D82" s="143">
+        <v>71474</v>
+      </c>
+      <c r="E82" s="143">
+        <v>30</v>
+      </c>
+      <c r="F82" s="143">
+        <v>2</v>
+      </c>
+      <c r="G82" s="143"/>
+      <c r="H82" s="143"/>
+      <c r="I82" s="143"/>
+      <c r="J82" s="143"/>
+      <c r="K82" s="143"/>
+      <c r="L82" s="143"/>
+      <c r="M82" s="143"/>
+      <c r="N82" s="143"/>
+      <c r="O82" s="143"/>
+      <c r="P82" s="143"/>
+      <c r="Q82" s="143"/>
+      <c r="R82" s="143"/>
+      <c r="S82" s="143"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="I10:N10"/>
+    <mergeCell ref="J2:P2"/>
+    <mergeCell ref="J4:P5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F4BA1CB-F4D8-4448-91F0-155160A6A3B9}">
+  <dimension ref="A1:P82"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.5546875" style="65" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.77734375" style="65" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27" style="65" customWidth="1"/>
+    <col min="4" max="4" width="7.77734375" style="65" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.109375" style="65" customWidth="1"/>
+    <col min="6" max="6" width="17.21875" style="65" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" style="65"/>
+    <col min="8" max="8" width="13.88671875" style="65" customWidth="1"/>
+    <col min="9" max="9" width="20.33203125" style="65" customWidth="1"/>
+    <col min="10" max="10" width="13.88671875" style="65" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="65"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" ht="14.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="153" t="s">
+        <v>399</v>
+      </c>
+      <c r="B1" s="153" t="s">
+        <v>226</v>
+      </c>
+      <c r="C1" s="153" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="153" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="153" t="s">
+        <v>400</v>
+      </c>
+      <c r="F1" s="153" t="s">
+        <v>401</v>
+      </c>
+      <c r="G1" s="59"/>
+      <c r="H1" s="154" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="154" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="153" t="s">
+        <v>402</v>
+      </c>
+      <c r="B2" s="153" t="s">
+        <v>358</v>
+      </c>
+      <c r="C2" s="153" t="s">
+        <v>403</v>
+      </c>
+      <c r="D2" s="153">
+        <v>5</v>
+      </c>
+      <c r="E2" s="153">
+        <v>3393</v>
+      </c>
+      <c r="F2" s="153" t="s">
+        <v>404</v>
+      </c>
+      <c r="G2" s="59"/>
+      <c r="H2" s="61" t="s">
+        <v>311</v>
+      </c>
+      <c r="I2" s="61" t="str">
+        <f>_xlfn.XLOOKUP("C003",A2:A82,C2:C82,"Customer not found")</f>
+        <v>Samsung 65-inch TV</v>
+      </c>
+      <c r="J2" s="153" t="s">
+        <v>607</v>
+      </c>
+      <c r="K2" s="153"/>
+      <c r="L2" s="153"/>
+      <c r="M2" s="153"/>
+      <c r="N2" s="153"/>
+      <c r="O2" s="153"/>
+      <c r="P2" s="153"/>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A3" s="153" t="s">
+        <v>405</v>
+      </c>
+      <c r="B3" s="153" t="s">
+        <v>353</v>
+      </c>
+      <c r="C3" s="153" t="s">
+        <v>406</v>
+      </c>
+      <c r="D3" s="153">
+        <v>8</v>
+      </c>
+      <c r="E3" s="153">
+        <v>28829</v>
+      </c>
+      <c r="F3" s="153" t="s">
+        <v>407</v>
+      </c>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
+      <c r="J3" s="153"/>
+      <c r="K3" s="153"/>
+      <c r="L3" s="153"/>
+      <c r="M3" s="153"/>
+      <c r="N3" s="153"/>
+      <c r="O3" s="153"/>
+      <c r="P3" s="153"/>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4" s="153" t="s">
+        <v>408</v>
+      </c>
+      <c r="B4" s="153" t="s">
+        <v>359</v>
+      </c>
+      <c r="C4" s="153" t="s">
+        <v>409</v>
+      </c>
+      <c r="D4" s="153">
+        <v>14</v>
+      </c>
+      <c r="E4" s="153">
+        <v>1332</v>
+      </c>
+      <c r="F4" s="155">
+        <v>45507</v>
+      </c>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A5" s="153" t="s">
+        <v>410</v>
+      </c>
+      <c r="B5" s="153" t="s">
+        <v>371</v>
+      </c>
+      <c r="C5" s="153" t="s">
+        <v>411</v>
+      </c>
+      <c r="D5" s="153">
+        <v>6</v>
+      </c>
+      <c r="E5" s="153">
+        <v>6398</v>
+      </c>
+      <c r="F5" s="153" t="s">
+        <v>412</v>
+      </c>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A6" s="153" t="s">
+        <v>413</v>
+      </c>
+      <c r="B6" s="153" t="s">
+        <v>373</v>
+      </c>
+      <c r="C6" s="153" t="s">
+        <v>414</v>
+      </c>
+      <c r="D6" s="153">
+        <v>21</v>
+      </c>
+      <c r="E6" s="153">
+        <v>13559</v>
+      </c>
+      <c r="F6" s="155">
+        <v>45539</v>
+      </c>
+      <c r="G6" s="59"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A7" s="153" t="s">
+        <v>415</v>
+      </c>
+      <c r="B7" s="153" t="s">
+        <v>340</v>
+      </c>
+      <c r="C7" s="153" t="s">
+        <v>416</v>
+      </c>
+      <c r="D7" s="153">
+        <v>2</v>
+      </c>
+      <c r="E7" s="153">
+        <v>11857</v>
+      </c>
+      <c r="F7" s="155">
+        <v>45630</v>
+      </c>
+      <c r="G7" s="59"/>
+      <c r="H7" s="59"/>
+      <c r="I7" s="59"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A8" s="153" t="s">
+        <v>417</v>
+      </c>
+      <c r="B8" s="153" t="s">
+        <v>325</v>
+      </c>
+      <c r="C8" s="153" t="s">
+        <v>418</v>
+      </c>
+      <c r="D8" s="153">
+        <v>20</v>
+      </c>
+      <c r="E8" s="153">
+        <v>22158</v>
+      </c>
+      <c r="F8" s="155">
+        <v>45600</v>
+      </c>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A9" s="153" t="s">
+        <v>419</v>
+      </c>
+      <c r="B9" s="153" t="s">
+        <v>334</v>
+      </c>
+      <c r="C9" s="153" t="s">
+        <v>420</v>
+      </c>
+      <c r="D9" s="153">
+        <v>14</v>
+      </c>
+      <c r="E9" s="153">
+        <v>8930</v>
+      </c>
+      <c r="F9" s="153" t="s">
+        <v>421</v>
+      </c>
+      <c r="G9" s="59"/>
+      <c r="H9" s="59"/>
+      <c r="I9" s="59"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A10" s="153" t="s">
+        <v>422</v>
+      </c>
+      <c r="B10" s="153" t="s">
+        <v>337</v>
+      </c>
+      <c r="C10" s="153" t="s">
+        <v>423</v>
+      </c>
+      <c r="D10" s="153">
+        <v>23</v>
+      </c>
+      <c r="E10" s="153">
+        <v>20775</v>
+      </c>
+      <c r="F10" s="153" t="s">
+        <v>424</v>
+      </c>
+      <c r="G10" s="59"/>
+      <c r="H10" s="59"/>
+      <c r="I10" s="59"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A11" s="153" t="s">
+        <v>425</v>
+      </c>
+      <c r="B11" s="153" t="s">
+        <v>348</v>
+      </c>
+      <c r="C11" s="153" t="s">
+        <v>426</v>
+      </c>
+      <c r="D11" s="153">
+        <v>8</v>
+      </c>
+      <c r="E11" s="153">
+        <v>26866</v>
+      </c>
+      <c r="F11" s="153" t="s">
+        <v>427</v>
+      </c>
+      <c r="G11" s="59"/>
+      <c r="H11" s="59"/>
+      <c r="I11" s="59"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A12" s="153" t="s">
+        <v>428</v>
+      </c>
+      <c r="B12" s="153" t="s">
+        <v>332</v>
+      </c>
+      <c r="C12" s="153" t="s">
+        <v>429</v>
+      </c>
+      <c r="D12" s="153">
+        <v>20</v>
+      </c>
+      <c r="E12" s="153">
+        <v>14951</v>
+      </c>
+      <c r="F12" s="153" t="s">
+        <v>430</v>
+      </c>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A13" s="153" t="s">
+        <v>431</v>
+      </c>
+      <c r="B13" s="153" t="s">
+        <v>376</v>
+      </c>
+      <c r="C13" s="153" t="s">
+        <v>432</v>
+      </c>
+      <c r="D13" s="153">
+        <v>14</v>
+      </c>
+      <c r="E13" s="153">
+        <v>16791</v>
+      </c>
+      <c r="F13" s="155">
+        <v>45567</v>
+      </c>
+      <c r="G13" s="59"/>
+      <c r="H13" s="59"/>
+      <c r="I13" s="59"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A14" s="153" t="s">
+        <v>433</v>
+      </c>
+      <c r="B14" s="153" t="s">
+        <v>369</v>
+      </c>
+      <c r="C14" s="153" t="s">
+        <v>434</v>
+      </c>
+      <c r="D14" s="153">
+        <v>13</v>
+      </c>
+      <c r="E14" s="153">
+        <v>6393</v>
+      </c>
+      <c r="F14" s="153" t="s">
+        <v>435</v>
+      </c>
+      <c r="G14" s="59"/>
+      <c r="H14" s="59"/>
+      <c r="I14" s="59"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A15" s="153" t="s">
+        <v>436</v>
+      </c>
+      <c r="B15" s="153" t="s">
+        <v>391</v>
+      </c>
+      <c r="C15" s="153" t="s">
+        <v>437</v>
+      </c>
+      <c r="D15" s="153">
+        <v>16</v>
+      </c>
+      <c r="E15" s="153">
+        <v>8469</v>
+      </c>
+      <c r="F15" s="155">
+        <v>45353</v>
+      </c>
+      <c r="G15" s="59"/>
+      <c r="H15" s="59"/>
+      <c r="I15" s="59"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A16" s="153" t="s">
+        <v>438</v>
+      </c>
+      <c r="B16" s="153" t="s">
+        <v>336</v>
+      </c>
+      <c r="C16" s="153" t="s">
+        <v>439</v>
+      </c>
+      <c r="D16" s="153">
+        <v>21</v>
+      </c>
+      <c r="E16" s="153">
+        <v>17287</v>
+      </c>
+      <c r="F16" s="155">
+        <v>45475</v>
+      </c>
+      <c r="G16" s="59"/>
+      <c r="H16" s="59"/>
+      <c r="I16" s="59"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="153" t="s">
+        <v>440</v>
+      </c>
+      <c r="B17" s="153" t="s">
+        <v>362</v>
+      </c>
+      <c r="C17" s="153" t="s">
+        <v>441</v>
+      </c>
+      <c r="D17" s="153">
+        <v>22</v>
+      </c>
+      <c r="E17" s="153">
+        <v>7660</v>
+      </c>
+      <c r="F17" s="155">
+        <v>45506</v>
+      </c>
+      <c r="G17" s="59"/>
+      <c r="H17" s="59"/>
+      <c r="I17" s="59"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="153" t="s">
+        <v>442</v>
+      </c>
+      <c r="B18" s="153" t="s">
+        <v>372</v>
+      </c>
+      <c r="C18" s="153" t="s">
+        <v>443</v>
+      </c>
+      <c r="D18" s="153">
+        <v>25</v>
+      </c>
+      <c r="E18" s="153">
+        <v>2615</v>
+      </c>
+      <c r="F18" s="153" t="s">
+        <v>444</v>
+      </c>
+      <c r="G18" s="59"/>
+      <c r="H18" s="59"/>
+      <c r="I18" s="59"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="153" t="s">
+        <v>445</v>
+      </c>
+      <c r="B19" s="153" t="s">
+        <v>386</v>
+      </c>
+      <c r="C19" s="153" t="s">
+        <v>446</v>
+      </c>
+      <c r="D19" s="153">
+        <v>10</v>
+      </c>
+      <c r="E19" s="153">
+        <v>16667</v>
+      </c>
+      <c r="F19" s="153" t="s">
+        <v>447</v>
+      </c>
+      <c r="G19" s="59"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="59"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="153" t="s">
+        <v>448</v>
+      </c>
+      <c r="B20" s="153" t="s">
+        <v>347</v>
+      </c>
+      <c r="C20" s="153" t="s">
+        <v>449</v>
+      </c>
+      <c r="D20" s="153">
+        <v>14</v>
+      </c>
+      <c r="E20" s="153">
+        <v>13823</v>
+      </c>
+      <c r="F20" s="153" t="s">
+        <v>450</v>
+      </c>
+      <c r="G20" s="59"/>
+      <c r="H20" s="59"/>
+      <c r="I20" s="59"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="153" t="s">
+        <v>451</v>
+      </c>
+      <c r="B21" s="153" t="s">
+        <v>350</v>
+      </c>
+      <c r="C21" s="153" t="s">
+        <v>452</v>
+      </c>
+      <c r="D21" s="153">
+        <v>10</v>
+      </c>
+      <c r="E21" s="153">
+        <v>6081</v>
+      </c>
+      <c r="F21" s="155">
+        <v>45537</v>
+      </c>
+      <c r="G21" s="59"/>
+      <c r="H21" s="59"/>
+      <c r="I21" s="59"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="153" t="s">
+        <v>453</v>
+      </c>
+      <c r="B22" s="153" t="s">
+        <v>323</v>
+      </c>
+      <c r="C22" s="153" t="s">
+        <v>454</v>
+      </c>
+      <c r="D22" s="153">
+        <v>12</v>
+      </c>
+      <c r="E22" s="153">
+        <v>19808</v>
+      </c>
+      <c r="F22" s="153" t="s">
+        <v>455</v>
+      </c>
+      <c r="G22" s="59"/>
+      <c r="H22" s="59"/>
+      <c r="I22" s="59"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="153" t="s">
+        <v>456</v>
+      </c>
+      <c r="B23" s="153" t="s">
+        <v>389</v>
+      </c>
+      <c r="C23" s="153" t="s">
+        <v>457</v>
+      </c>
+      <c r="D23" s="153">
+        <v>14</v>
+      </c>
+      <c r="E23" s="153">
+        <v>23866</v>
+      </c>
+      <c r="F23" s="153" t="s">
+        <v>458</v>
+      </c>
+      <c r="G23" s="59"/>
+      <c r="H23" s="59"/>
+      <c r="I23" s="59"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="153" t="s">
+        <v>459</v>
+      </c>
+      <c r="B24" s="153" t="s">
+        <v>326</v>
+      </c>
+      <c r="C24" s="153" t="s">
+        <v>460</v>
+      </c>
+      <c r="D24" s="153">
+        <v>1</v>
+      </c>
+      <c r="E24" s="153">
+        <v>21287</v>
+      </c>
+      <c r="F24" s="155">
+        <v>45294</v>
+      </c>
+      <c r="G24" s="59"/>
+      <c r="H24" s="59"/>
+      <c r="I24" s="59"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="153" t="s">
+        <v>461</v>
+      </c>
+      <c r="B25" s="153" t="s">
+        <v>329</v>
+      </c>
+      <c r="C25" s="153" t="s">
+        <v>462</v>
+      </c>
+      <c r="D25" s="153">
+        <v>5</v>
+      </c>
+      <c r="E25" s="153">
+        <v>18203</v>
+      </c>
+      <c r="F25" s="155">
+        <v>45628</v>
+      </c>
+      <c r="G25" s="59"/>
+      <c r="H25" s="59"/>
+      <c r="I25" s="59"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" s="153" t="s">
+        <v>463</v>
+      </c>
+      <c r="B26" s="153" t="s">
+        <v>374</v>
+      </c>
+      <c r="C26" s="153" t="s">
+        <v>464</v>
+      </c>
+      <c r="D26" s="153">
+        <v>23</v>
+      </c>
+      <c r="E26" s="153">
+        <v>29230</v>
+      </c>
+      <c r="F26" s="153" t="s">
+        <v>465</v>
+      </c>
+      <c r="G26" s="59"/>
+      <c r="H26" s="59"/>
+      <c r="I26" s="59"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A27" s="153" t="s">
+        <v>466</v>
+      </c>
+      <c r="B27" s="153" t="s">
+        <v>387</v>
+      </c>
+      <c r="C27" s="153" t="s">
+        <v>467</v>
+      </c>
+      <c r="D27" s="153">
+        <v>23</v>
+      </c>
+      <c r="E27" s="153">
+        <v>26283</v>
+      </c>
+      <c r="F27" s="153" t="s">
+        <v>468</v>
+      </c>
+      <c r="G27" s="59"/>
+      <c r="H27" s="59"/>
+      <c r="I27" s="59"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="153" t="s">
+        <v>469</v>
+      </c>
+      <c r="B28" s="153" t="s">
+        <v>342</v>
+      </c>
+      <c r="C28" s="153" t="s">
+        <v>470</v>
+      </c>
+      <c r="D28" s="153">
+        <v>10</v>
+      </c>
+      <c r="E28" s="153">
+        <v>28667</v>
+      </c>
+      <c r="F28" s="153" t="s">
+        <v>471</v>
+      </c>
+      <c r="G28" s="59"/>
+      <c r="H28" s="59"/>
+      <c r="I28" s="59"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" s="153" t="s">
+        <v>472</v>
+      </c>
+      <c r="B29" s="153" t="s">
+        <v>356</v>
+      </c>
+      <c r="C29" s="153" t="s">
+        <v>473</v>
+      </c>
+      <c r="D29" s="153">
+        <v>22</v>
+      </c>
+      <c r="E29" s="153">
+        <v>26382</v>
+      </c>
+      <c r="F29" s="153" t="s">
+        <v>474</v>
+      </c>
+      <c r="G29" s="59"/>
+      <c r="H29" s="59"/>
+      <c r="I29" s="59"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" s="153" t="s">
+        <v>475</v>
+      </c>
+      <c r="B30" s="153" t="s">
+        <v>382</v>
+      </c>
+      <c r="C30" s="153" t="s">
+        <v>476</v>
+      </c>
+      <c r="D30" s="153">
+        <v>10</v>
+      </c>
+      <c r="E30" s="153">
+        <v>28268</v>
+      </c>
+      <c r="F30" s="153" t="s">
+        <v>477</v>
+      </c>
+      <c r="G30" s="59"/>
+      <c r="H30" s="59"/>
+      <c r="I30" s="59"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" s="153" t="s">
+        <v>478</v>
+      </c>
+      <c r="B31" s="153" t="s">
+        <v>310</v>
+      </c>
+      <c r="C31" s="153" t="s">
+        <v>479</v>
+      </c>
+      <c r="D31" s="153">
+        <v>5</v>
+      </c>
+      <c r="E31" s="153">
+        <v>8044</v>
+      </c>
+      <c r="F31" s="155">
+        <v>45416</v>
+      </c>
+      <c r="G31" s="59"/>
+      <c r="H31" s="59"/>
+      <c r="I31" s="59"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" s="153" t="s">
+        <v>480</v>
+      </c>
+      <c r="B32" s="153" t="s">
+        <v>378</v>
+      </c>
+      <c r="C32" s="153" t="s">
+        <v>481</v>
+      </c>
+      <c r="D32" s="153">
+        <v>10</v>
+      </c>
+      <c r="E32" s="153">
+        <v>9183</v>
+      </c>
+      <c r="F32" s="153" t="s">
+        <v>482</v>
+      </c>
+      <c r="G32" s="59"/>
+      <c r="H32" s="59"/>
+      <c r="I32" s="59"/>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A33" s="153" t="s">
+        <v>483</v>
+      </c>
+      <c r="B33" s="153" t="s">
+        <v>317</v>
+      </c>
+      <c r="C33" s="153" t="s">
+        <v>484</v>
+      </c>
+      <c r="D33" s="153">
+        <v>13</v>
+      </c>
+      <c r="E33" s="153">
+        <v>15304</v>
+      </c>
+      <c r="F33" s="153" t="s">
+        <v>485</v>
+      </c>
+      <c r="G33" s="59"/>
+      <c r="H33" s="59"/>
+      <c r="I33" s="59"/>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" s="153" t="s">
+        <v>486</v>
+      </c>
+      <c r="B34" s="153" t="s">
+        <v>312</v>
+      </c>
+      <c r="C34" s="153" t="s">
+        <v>487</v>
+      </c>
+      <c r="D34" s="153">
+        <v>15</v>
+      </c>
+      <c r="E34" s="153">
+        <v>11735</v>
+      </c>
+      <c r="F34" s="153" t="s">
+        <v>488</v>
+      </c>
+      <c r="G34" s="59"/>
+      <c r="H34" s="59"/>
+      <c r="I34" s="59"/>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35" s="153" t="s">
+        <v>489</v>
+      </c>
+      <c r="B35" s="153" t="s">
+        <v>366</v>
+      </c>
+      <c r="C35" s="153" t="s">
+        <v>490</v>
+      </c>
+      <c r="D35" s="153">
+        <v>5</v>
+      </c>
+      <c r="E35" s="153">
+        <v>27314</v>
+      </c>
+      <c r="F35" s="155">
+        <v>45295</v>
+      </c>
+      <c r="G35" s="59"/>
+      <c r="H35" s="59"/>
+      <c r="I35" s="59"/>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A36" s="153" t="s">
+        <v>491</v>
+      </c>
+      <c r="B36" s="153" t="s">
+        <v>324</v>
+      </c>
+      <c r="C36" s="153" t="s">
+        <v>492</v>
+      </c>
+      <c r="D36" s="153">
+        <v>21</v>
+      </c>
+      <c r="E36" s="153">
+        <v>1208</v>
+      </c>
+      <c r="F36" s="155">
+        <v>45566</v>
+      </c>
+      <c r="G36" s="59"/>
+      <c r="H36" s="59"/>
+      <c r="I36" s="59"/>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" s="153" t="s">
+        <v>493</v>
+      </c>
+      <c r="B37" s="153" t="s">
+        <v>318</v>
+      </c>
+      <c r="C37" s="153" t="s">
+        <v>494</v>
+      </c>
+      <c r="D37" s="153">
+        <v>11</v>
+      </c>
+      <c r="E37" s="153">
+        <v>5059</v>
+      </c>
+      <c r="F37" s="153" t="s">
+        <v>495</v>
+      </c>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59"/>
+      <c r="I37" s="59"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38" s="153" t="s">
+        <v>496</v>
+      </c>
+      <c r="B38" s="153" t="s">
+        <v>383</v>
+      </c>
+      <c r="C38" s="153" t="s">
+        <v>497</v>
+      </c>
+      <c r="D38" s="153">
+        <v>21</v>
+      </c>
+      <c r="E38" s="153">
+        <v>24766</v>
+      </c>
+      <c r="F38" s="155">
+        <v>45355</v>
+      </c>
+      <c r="G38" s="59"/>
+      <c r="H38" s="59"/>
+      <c r="I38" s="59"/>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" s="153" t="s">
+        <v>498</v>
+      </c>
+      <c r="B39" s="153" t="s">
+        <v>320</v>
+      </c>
+      <c r="C39" s="153" t="s">
+        <v>499</v>
+      </c>
+      <c r="D39" s="153">
+        <v>9</v>
+      </c>
+      <c r="E39" s="153">
+        <v>25536</v>
+      </c>
+      <c r="F39" s="155">
+        <v>45568</v>
+      </c>
+      <c r="G39" s="59"/>
+      <c r="H39" s="59"/>
+      <c r="I39" s="59"/>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40" s="153" t="s">
+        <v>500</v>
+      </c>
+      <c r="B40" s="153" t="s">
+        <v>330</v>
+      </c>
+      <c r="C40" s="153" t="s">
+        <v>501</v>
+      </c>
+      <c r="D40" s="153">
+        <v>23</v>
+      </c>
+      <c r="E40" s="153">
+        <v>25939</v>
+      </c>
+      <c r="F40" s="155">
+        <v>45538</v>
+      </c>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A41" s="153" t="s">
+        <v>502</v>
+      </c>
+      <c r="B41" s="153" t="s">
+        <v>327</v>
+      </c>
+      <c r="C41" s="153" t="s">
+        <v>503</v>
+      </c>
+      <c r="D41" s="153">
+        <v>22</v>
+      </c>
+      <c r="E41" s="153">
+        <v>9644</v>
+      </c>
+      <c r="F41" s="155">
+        <v>45414</v>
+      </c>
+      <c r="G41" s="59"/>
+      <c r="H41" s="59"/>
+      <c r="I41" s="59"/>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A42" s="153" t="s">
+        <v>504</v>
+      </c>
+      <c r="B42" s="153" t="s">
+        <v>331</v>
+      </c>
+      <c r="C42" s="153" t="s">
+        <v>505</v>
+      </c>
+      <c r="D42" s="153">
+        <v>12</v>
+      </c>
+      <c r="E42" s="153">
+        <v>17402</v>
+      </c>
+      <c r="F42" s="153" t="s">
+        <v>506</v>
+      </c>
+      <c r="G42" s="59"/>
+      <c r="H42" s="59"/>
+      <c r="I42" s="59"/>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A43" s="153" t="s">
+        <v>507</v>
+      </c>
+      <c r="B43" s="153" t="s">
+        <v>321</v>
+      </c>
+      <c r="C43" s="153" t="s">
+        <v>508</v>
+      </c>
+      <c r="D43" s="153">
+        <v>12</v>
+      </c>
+      <c r="E43" s="153">
+        <v>15486</v>
+      </c>
+      <c r="F43" s="155">
+        <v>45569</v>
+      </c>
+      <c r="G43" s="59"/>
+      <c r="H43" s="59"/>
+      <c r="I43" s="59"/>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A44" s="153" t="s">
+        <v>509</v>
+      </c>
+      <c r="B44" s="153" t="s">
+        <v>346</v>
+      </c>
+      <c r="C44" s="153" t="s">
+        <v>510</v>
+      </c>
+      <c r="D44" s="153">
+        <v>1</v>
+      </c>
+      <c r="E44" s="153">
+        <v>8298</v>
+      </c>
+      <c r="F44" s="153" t="s">
+        <v>511</v>
+      </c>
+      <c r="G44" s="59"/>
+      <c r="H44" s="59"/>
+      <c r="I44" s="59"/>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A45" s="153" t="s">
+        <v>512</v>
+      </c>
+      <c r="B45" s="153" t="s">
+        <v>355</v>
+      </c>
+      <c r="C45" s="153" t="s">
+        <v>513</v>
+      </c>
+      <c r="D45" s="153">
+        <v>10</v>
+      </c>
+      <c r="E45" s="153">
+        <v>11697</v>
+      </c>
+      <c r="F45" s="155">
+        <v>45386</v>
+      </c>
+      <c r="G45" s="59"/>
+      <c r="H45" s="59"/>
+      <c r="I45" s="59"/>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A46" s="153" t="s">
+        <v>514</v>
+      </c>
+      <c r="B46" s="153" t="s">
+        <v>370</v>
+      </c>
+      <c r="C46" s="153" t="s">
+        <v>515</v>
+      </c>
+      <c r="D46" s="153">
+        <v>7</v>
+      </c>
+      <c r="E46" s="153">
+        <v>16981</v>
+      </c>
+      <c r="F46" s="155">
+        <v>45476</v>
+      </c>
+      <c r="G46" s="59"/>
+      <c r="H46" s="59"/>
+      <c r="I46" s="59"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A47" s="153" t="s">
+        <v>516</v>
+      </c>
+      <c r="B47" s="153" t="s">
+        <v>395</v>
+      </c>
+      <c r="C47" s="153" t="s">
+        <v>517</v>
+      </c>
+      <c r="D47" s="153">
+        <v>24</v>
+      </c>
+      <c r="E47" s="153">
+        <v>21128</v>
+      </c>
+      <c r="F47" s="153" t="s">
+        <v>518</v>
+      </c>
+      <c r="G47" s="59"/>
+      <c r="H47" s="59"/>
+      <c r="I47" s="59"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A48" s="153" t="s">
+        <v>519</v>
+      </c>
+      <c r="B48" s="153" t="s">
+        <v>341</v>
+      </c>
+      <c r="C48" s="153" t="s">
+        <v>520</v>
+      </c>
+      <c r="D48" s="153">
+        <v>2</v>
+      </c>
+      <c r="E48" s="153">
+        <v>24238</v>
+      </c>
+      <c r="F48" s="153" t="s">
+        <v>521</v>
+      </c>
+      <c r="G48" s="59"/>
+      <c r="H48" s="59"/>
+      <c r="I48" s="59"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A49" s="153" t="s">
+        <v>522</v>
+      </c>
+      <c r="B49" s="153" t="s">
+        <v>354</v>
+      </c>
+      <c r="C49" s="153" t="s">
+        <v>523</v>
+      </c>
+      <c r="D49" s="153">
+        <v>9</v>
+      </c>
+      <c r="E49" s="153">
+        <v>10893</v>
+      </c>
+      <c r="F49" s="153" t="s">
+        <v>524</v>
+      </c>
+      <c r="G49" s="59"/>
+      <c r="H49" s="59"/>
+      <c r="I49" s="59"/>
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A50" s="153" t="s">
+        <v>525</v>
+      </c>
+      <c r="B50" s="153" t="s">
+        <v>360</v>
+      </c>
+      <c r="C50" s="153" t="s">
+        <v>526</v>
+      </c>
+      <c r="D50" s="153">
+        <v>21</v>
+      </c>
+      <c r="E50" s="153">
+        <v>21047</v>
+      </c>
+      <c r="F50" s="155">
+        <v>45445</v>
+      </c>
+      <c r="G50" s="59"/>
+      <c r="H50" s="59"/>
+      <c r="I50" s="59"/>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A51" s="153" t="s">
+        <v>527</v>
+      </c>
+      <c r="B51" s="153" t="s">
+        <v>367</v>
+      </c>
+      <c r="C51" s="153" t="s">
+        <v>528</v>
+      </c>
+      <c r="D51" s="153">
+        <v>2</v>
+      </c>
+      <c r="E51" s="153">
+        <v>17418</v>
+      </c>
+      <c r="F51" s="155">
+        <v>45446</v>
+      </c>
+      <c r="G51" s="59"/>
+      <c r="H51" s="59"/>
+      <c r="I51" s="59"/>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A52" s="153" t="s">
+        <v>529</v>
+      </c>
+      <c r="B52" s="153" t="s">
+        <v>393</v>
+      </c>
+      <c r="C52" s="153" t="s">
+        <v>530</v>
+      </c>
+      <c r="D52" s="153">
+        <v>19</v>
+      </c>
+      <c r="E52" s="153">
+        <v>10317</v>
+      </c>
+      <c r="F52" s="153" t="s">
+        <v>531</v>
+      </c>
+      <c r="G52" s="59"/>
+      <c r="H52" s="59"/>
+      <c r="I52" s="59"/>
+    </row>
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A53" s="153" t="s">
+        <v>532</v>
+      </c>
+      <c r="B53" s="153" t="s">
+        <v>357</v>
+      </c>
+      <c r="C53" s="153" t="s">
+        <v>533</v>
+      </c>
+      <c r="D53" s="153">
+        <v>6</v>
+      </c>
+      <c r="E53" s="153">
+        <v>22290</v>
+      </c>
+      <c r="F53" s="153" t="s">
+        <v>534</v>
+      </c>
+      <c r="G53" s="59"/>
+      <c r="H53" s="59"/>
+      <c r="I53" s="59"/>
+    </row>
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A54" s="153" t="s">
+        <v>535</v>
+      </c>
+      <c r="B54" s="153" t="s">
+        <v>394</v>
+      </c>
+      <c r="C54" s="153" t="s">
+        <v>536</v>
+      </c>
+      <c r="D54" s="153">
+        <v>22</v>
+      </c>
+      <c r="E54" s="153">
+        <v>21620</v>
+      </c>
+      <c r="F54" s="155">
+        <v>45447</v>
+      </c>
+      <c r="G54" s="59"/>
+      <c r="H54" s="59"/>
+      <c r="I54" s="59"/>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A55" s="153" t="s">
+        <v>537</v>
+      </c>
+      <c r="B55" s="153" t="s">
+        <v>351</v>
+      </c>
+      <c r="C55" s="153" t="s">
+        <v>538</v>
+      </c>
+      <c r="D55" s="153">
+        <v>14</v>
+      </c>
+      <c r="E55" s="153">
+        <v>19117</v>
+      </c>
+      <c r="F55" s="153" t="s">
+        <v>539</v>
+      </c>
+      <c r="G55" s="59"/>
+      <c r="H55" s="59"/>
+      <c r="I55" s="59"/>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A56" s="153" t="s">
+        <v>540</v>
+      </c>
+      <c r="B56" s="153" t="s">
+        <v>345</v>
+      </c>
+      <c r="C56" s="153" t="s">
+        <v>541</v>
+      </c>
+      <c r="D56" s="153">
+        <v>9</v>
+      </c>
+      <c r="E56" s="153">
+        <v>6241</v>
+      </c>
+      <c r="F56" s="153" t="s">
+        <v>542</v>
+      </c>
+      <c r="G56" s="59"/>
+      <c r="H56" s="59"/>
+      <c r="I56" s="59"/>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A57" s="153" t="s">
+        <v>543</v>
+      </c>
+      <c r="B57" s="153" t="s">
+        <v>352</v>
+      </c>
+      <c r="C57" s="153" t="s">
+        <v>544</v>
+      </c>
+      <c r="D57" s="153">
+        <v>4</v>
+      </c>
+      <c r="E57" s="153">
+        <v>7123</v>
+      </c>
+      <c r="F57" s="153" t="s">
+        <v>545</v>
+      </c>
+      <c r="G57" s="59"/>
+      <c r="H57" s="59"/>
+      <c r="I57" s="59"/>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A58" s="153" t="s">
+        <v>546</v>
+      </c>
+      <c r="B58" s="153" t="s">
+        <v>361</v>
+      </c>
+      <c r="C58" s="153" t="s">
+        <v>547</v>
+      </c>
+      <c r="D58" s="153">
+        <v>17</v>
+      </c>
+      <c r="E58" s="153">
+        <v>18301</v>
+      </c>
+      <c r="F58" s="155">
+        <v>45598</v>
+      </c>
+      <c r="G58" s="59"/>
+      <c r="H58" s="59"/>
+      <c r="I58" s="59"/>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A59" s="153" t="s">
+        <v>548</v>
+      </c>
+      <c r="B59" s="153" t="s">
+        <v>381</v>
+      </c>
+      <c r="C59" s="153" t="s">
+        <v>549</v>
+      </c>
+      <c r="D59" s="153">
+        <v>14</v>
+      </c>
+      <c r="E59" s="153">
+        <v>3322</v>
+      </c>
+      <c r="F59" s="153" t="s">
+        <v>550</v>
+      </c>
+      <c r="G59" s="59"/>
+      <c r="H59" s="59"/>
+      <c r="I59" s="59"/>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A60" s="153" t="s">
+        <v>551</v>
+      </c>
+      <c r="B60" s="153" t="s">
+        <v>384</v>
+      </c>
+      <c r="C60" s="153" t="s">
+        <v>552</v>
+      </c>
+      <c r="D60" s="153">
+        <v>11</v>
+      </c>
+      <c r="E60" s="153">
+        <v>10769</v>
+      </c>
+      <c r="F60" s="155">
+        <v>45326</v>
+      </c>
+      <c r="G60" s="59"/>
+      <c r="H60" s="59"/>
+      <c r="I60" s="59"/>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A61" s="153" t="s">
+        <v>553</v>
+      </c>
+      <c r="B61" s="153" t="s">
+        <v>338</v>
+      </c>
+      <c r="C61" s="153" t="s">
+        <v>554</v>
+      </c>
+      <c r="D61" s="153">
+        <v>16</v>
+      </c>
+      <c r="E61" s="153">
+        <v>24974</v>
+      </c>
+      <c r="F61" s="153" t="s">
+        <v>555</v>
+      </c>
+      <c r="G61" s="59"/>
+      <c r="H61" s="59"/>
+      <c r="I61" s="59"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A62" s="153" t="s">
+        <v>556</v>
+      </c>
+      <c r="B62" s="153" t="s">
+        <v>377</v>
+      </c>
+      <c r="C62" s="153" t="s">
+        <v>557</v>
+      </c>
+      <c r="D62" s="153">
+        <v>17</v>
+      </c>
+      <c r="E62" s="153">
+        <v>24880</v>
+      </c>
+      <c r="F62" s="155">
+        <v>45324</v>
+      </c>
+      <c r="G62" s="59"/>
+      <c r="H62" s="59"/>
+      <c r="I62" s="59"/>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A63" s="153" t="s">
+        <v>558</v>
+      </c>
+      <c r="B63" s="153" t="s">
+        <v>385</v>
+      </c>
+      <c r="C63" s="153" t="s">
+        <v>559</v>
+      </c>
+      <c r="D63" s="153">
+        <v>23</v>
+      </c>
+      <c r="E63" s="153">
+        <v>28952</v>
+      </c>
+      <c r="F63" s="153" t="s">
+        <v>560</v>
+      </c>
+      <c r="G63" s="59"/>
+      <c r="H63" s="59"/>
+      <c r="I63" s="59"/>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A64" s="153" t="s">
+        <v>561</v>
+      </c>
+      <c r="B64" s="153" t="s">
+        <v>343</v>
+      </c>
+      <c r="C64" s="153" t="s">
+        <v>562</v>
+      </c>
+      <c r="D64" s="153">
+        <v>7</v>
+      </c>
+      <c r="E64" s="153">
+        <v>11293</v>
+      </c>
+      <c r="F64" s="153" t="s">
+        <v>563</v>
+      </c>
+      <c r="G64" s="59"/>
+      <c r="H64" s="59"/>
+      <c r="I64" s="59"/>
+    </row>
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A65" s="153" t="s">
+        <v>564</v>
+      </c>
+      <c r="B65" s="153" t="s">
+        <v>344</v>
+      </c>
+      <c r="C65" s="153" t="s">
+        <v>565</v>
+      </c>
+      <c r="D65" s="153">
+        <v>15</v>
+      </c>
+      <c r="E65" s="153">
+        <v>10982</v>
+      </c>
+      <c r="F65" s="153" t="s">
+        <v>566</v>
+      </c>
+      <c r="G65" s="59"/>
+      <c r="H65" s="59"/>
+      <c r="I65" s="59"/>
+    </row>
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A66" s="153" t="s">
+        <v>567</v>
+      </c>
+      <c r="B66" s="153" t="s">
+        <v>322</v>
+      </c>
+      <c r="C66" s="153" t="s">
+        <v>568</v>
+      </c>
+      <c r="D66" s="153">
+        <v>9</v>
+      </c>
+      <c r="E66" s="153">
+        <v>22817</v>
+      </c>
+      <c r="F66" s="153" t="s">
+        <v>569</v>
+      </c>
+      <c r="G66" s="59"/>
+      <c r="H66" s="59"/>
+      <c r="I66" s="59"/>
+    </row>
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A67" s="153" t="s">
+        <v>570</v>
+      </c>
+      <c r="B67" s="153" t="s">
+        <v>390</v>
+      </c>
+      <c r="C67" s="153" t="s">
+        <v>571</v>
+      </c>
+      <c r="D67" s="153">
+        <v>6</v>
+      </c>
+      <c r="E67" s="153">
+        <v>11609</v>
+      </c>
+      <c r="F67" s="155">
+        <v>45413</v>
+      </c>
+      <c r="G67" s="59"/>
+      <c r="H67" s="59"/>
+      <c r="I67" s="59"/>
+    </row>
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A68" s="153" t="s">
+        <v>572</v>
+      </c>
+      <c r="B68" s="153" t="s">
+        <v>315</v>
+      </c>
+      <c r="C68" s="153" t="s">
+        <v>573</v>
+      </c>
+      <c r="D68" s="153">
+        <v>1</v>
+      </c>
+      <c r="E68" s="153">
+        <v>13172</v>
+      </c>
+      <c r="F68" s="155">
+        <v>45325</v>
+      </c>
+      <c r="G68" s="59"/>
+      <c r="H68" s="59"/>
+      <c r="I68" s="59"/>
+    </row>
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A69" s="153" t="s">
+        <v>574</v>
+      </c>
+      <c r="B69" s="153" t="s">
+        <v>333</v>
+      </c>
+      <c r="C69" s="153" t="s">
+        <v>575</v>
+      </c>
+      <c r="D69" s="153">
+        <v>10</v>
+      </c>
+      <c r="E69" s="153">
+        <v>13804</v>
+      </c>
+      <c r="F69" s="155">
+        <v>45293</v>
+      </c>
+      <c r="G69" s="59"/>
+      <c r="H69" s="59"/>
+      <c r="I69" s="59"/>
+    </row>
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A70" s="153" t="s">
+        <v>576</v>
+      </c>
+      <c r="B70" s="153" t="s">
+        <v>364</v>
+      </c>
+      <c r="C70" s="153" t="s">
+        <v>577</v>
+      </c>
+      <c r="D70" s="153">
+        <v>9</v>
+      </c>
+      <c r="E70" s="153">
+        <v>29226</v>
+      </c>
+      <c r="F70" s="155">
+        <v>45385</v>
+      </c>
+      <c r="G70" s="59"/>
+      <c r="H70" s="59"/>
+      <c r="I70" s="59"/>
+    </row>
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A71" s="153" t="s">
+        <v>578</v>
+      </c>
+      <c r="B71" s="153" t="s">
+        <v>392</v>
+      </c>
+      <c r="C71" s="153" t="s">
+        <v>579</v>
+      </c>
+      <c r="D71" s="153">
+        <v>6</v>
+      </c>
+      <c r="E71" s="153">
+        <v>10348</v>
+      </c>
+      <c r="F71" s="155">
+        <v>45477</v>
+      </c>
+      <c r="G71" s="59"/>
+      <c r="H71" s="59"/>
+      <c r="I71" s="59"/>
+    </row>
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A72" s="153" t="s">
+        <v>580</v>
+      </c>
+      <c r="B72" s="153" t="s">
+        <v>328</v>
+      </c>
+      <c r="C72" s="153" t="s">
+        <v>581</v>
+      </c>
+      <c r="D72" s="153">
+        <v>4</v>
+      </c>
+      <c r="E72" s="153">
+        <v>20848</v>
+      </c>
+      <c r="F72" s="153" t="s">
+        <v>582</v>
+      </c>
+      <c r="G72" s="59"/>
+      <c r="H72" s="59"/>
+      <c r="I72" s="59"/>
+    </row>
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A73" s="153" t="s">
+        <v>583</v>
+      </c>
+      <c r="B73" s="153" t="s">
+        <v>339</v>
+      </c>
+      <c r="C73" s="153" t="s">
+        <v>584</v>
+      </c>
+      <c r="D73" s="153">
+        <v>1</v>
+      </c>
+      <c r="E73" s="153">
+        <v>27278</v>
+      </c>
+      <c r="F73" s="153" t="s">
+        <v>585</v>
+      </c>
+      <c r="G73" s="59"/>
+      <c r="H73" s="59"/>
+      <c r="I73" s="59"/>
+    </row>
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A74" s="153" t="s">
+        <v>586</v>
+      </c>
+      <c r="B74" s="153" t="s">
+        <v>375</v>
+      </c>
+      <c r="C74" s="153" t="s">
+        <v>587</v>
+      </c>
+      <c r="D74" s="153">
+        <v>5</v>
+      </c>
+      <c r="E74" s="153">
+        <v>27731</v>
+      </c>
+      <c r="F74" s="155">
+        <v>45599</v>
+      </c>
+      <c r="G74" s="59"/>
+      <c r="H74" s="59"/>
+      <c r="I74" s="59"/>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A75" s="153" t="s">
+        <v>588</v>
+      </c>
+      <c r="B75" s="153" t="s">
+        <v>388</v>
+      </c>
+      <c r="C75" s="153" t="s">
+        <v>589</v>
+      </c>
+      <c r="D75" s="153">
+        <v>16</v>
+      </c>
+      <c r="E75" s="153">
+        <v>15610</v>
+      </c>
+      <c r="F75" s="153" t="s">
+        <v>590</v>
+      </c>
+      <c r="G75" s="59"/>
+      <c r="H75" s="59"/>
+      <c r="I75" s="59"/>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A76" s="153" t="s">
+        <v>591</v>
+      </c>
+      <c r="B76" s="153" t="s">
+        <v>349</v>
+      </c>
+      <c r="C76" s="153" t="s">
+        <v>592</v>
+      </c>
+      <c r="D76" s="153">
+        <v>12</v>
+      </c>
+      <c r="E76" s="153">
+        <v>9642</v>
+      </c>
+      <c r="F76" s="155">
+        <v>45384</v>
+      </c>
+      <c r="G76" s="59"/>
+      <c r="H76" s="59"/>
+      <c r="I76" s="59"/>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A77" s="153" t="s">
+        <v>593</v>
+      </c>
+      <c r="B77" s="153" t="s">
+        <v>379</v>
+      </c>
+      <c r="C77" s="153" t="s">
+        <v>594</v>
+      </c>
+      <c r="D77" s="153">
+        <v>12</v>
+      </c>
+      <c r="E77" s="153">
+        <v>4383</v>
+      </c>
+      <c r="F77" s="155">
+        <v>45629</v>
+      </c>
+      <c r="G77" s="59"/>
+      <c r="H77" s="59"/>
+      <c r="I77" s="59"/>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A78" s="153" t="s">
+        <v>595</v>
+      </c>
+      <c r="B78" s="153" t="s">
+        <v>380</v>
+      </c>
+      <c r="C78" s="153" t="s">
+        <v>596</v>
+      </c>
+      <c r="D78" s="153">
+        <v>15</v>
+      </c>
+      <c r="E78" s="153">
+        <v>23927</v>
+      </c>
+      <c r="F78" s="153" t="s">
+        <v>597</v>
+      </c>
+      <c r="G78" s="59"/>
+      <c r="H78" s="59"/>
+      <c r="I78" s="59"/>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A79" s="153" t="s">
+        <v>598</v>
+      </c>
+      <c r="B79" s="153" t="s">
+        <v>368</v>
+      </c>
+      <c r="C79" s="153" t="s">
+        <v>599</v>
+      </c>
+      <c r="D79" s="153">
+        <v>9</v>
+      </c>
+      <c r="E79" s="153">
+        <v>26247</v>
+      </c>
+      <c r="F79" s="155">
+        <v>45415</v>
+      </c>
+      <c r="G79" s="59"/>
+      <c r="H79" s="59"/>
+      <c r="I79" s="59"/>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A80" s="153" t="s">
+        <v>600</v>
+      </c>
+      <c r="B80" s="153" t="s">
+        <v>365</v>
+      </c>
+      <c r="C80" s="153" t="s">
+        <v>601</v>
+      </c>
+      <c r="D80" s="153">
+        <v>5</v>
+      </c>
+      <c r="E80" s="153">
+        <v>4110</v>
+      </c>
+      <c r="F80" s="155">
+        <v>45354</v>
+      </c>
+      <c r="G80" s="59"/>
+      <c r="H80" s="59"/>
+      <c r="I80" s="59"/>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A81" s="153" t="s">
+        <v>602</v>
+      </c>
+      <c r="B81" s="153" t="s">
+        <v>363</v>
+      </c>
+      <c r="C81" s="153" t="s">
+        <v>603</v>
+      </c>
+      <c r="D81" s="153">
+        <v>15</v>
+      </c>
+      <c r="E81" s="153">
+        <v>6903</v>
+      </c>
+      <c r="F81" s="155">
+        <v>45508</v>
+      </c>
+      <c r="G81" s="59"/>
+      <c r="H81" s="59"/>
+      <c r="I81" s="59"/>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A82" s="153" t="s">
+        <v>604</v>
+      </c>
+      <c r="B82" s="153" t="s">
+        <v>335</v>
+      </c>
+      <c r="C82" s="153" t="s">
+        <v>605</v>
+      </c>
+      <c r="D82" s="153">
+        <v>5</v>
+      </c>
+      <c r="E82" s="153">
+        <v>18943</v>
+      </c>
+      <c r="F82" s="153" t="s">
+        <v>606</v>
+      </c>
+      <c r="G82" s="59"/>
+      <c r="H82" s="59"/>
+      <c r="I82" s="59"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D628999E-1101-4859-A1BA-0F620A8FCB3D}">
   <dimension ref="A1:J51"/>
@@ -4973,131 +10695,131 @@
   <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="8.88671875" style="137"/>
+    <col min="1" max="16384" width="8.88671875" style="138"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="137" t="s">
         <v>306</v>
       </c>
-      <c r="B1" s="136" t="s">
+      <c r="B1" s="137" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="136" t="s">
+      <c r="C1" s="137" t="s">
         <v>307</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="137" t="s">
+      <c r="A2" s="138" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="137" t="s">
+      <c r="B2" s="138" t="s">
         <v>63</v>
       </c>
-      <c r="C2" s="137">
+      <c r="C2" s="138">
         <v>500</v>
       </c>
-      <c r="D2" s="138">
+      <c r="D2" s="139">
         <f>AVERAGE((AVERAGEIFS(C2:C11,B2:B11,"Speakers",A2:A11,"South")+AVERAGEIFS(C2:C11,B2:B11,"Speakers",A2:A11,"East"))/2)</f>
         <v>175</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="137" t="s">
+      <c r="A3" s="138" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="137" t="s">
+      <c r="B3" s="138" t="s">
         <v>290</v>
       </c>
-      <c r="C3" s="137">
+      <c r="C3" s="138">
         <v>300</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="137" t="s">
+      <c r="A4" s="138" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="137" t="s">
+      <c r="B4" s="138" t="s">
         <v>63</v>
       </c>
-      <c r="C4" s="137">
+      <c r="C4" s="138">
         <v>450</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="137" t="s">
+      <c r="A5" s="138" t="s">
         <v>26</v>
       </c>
-      <c r="B5" s="137" t="s">
+      <c r="B5" s="138" t="s">
         <v>68</v>
       </c>
-      <c r="C5" s="137">
+      <c r="C5" s="138">
         <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="137" t="s">
+      <c r="A6" s="138" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="137" t="s">
+      <c r="B6" s="138" t="s">
         <v>63</v>
       </c>
-      <c r="C6" s="137">
+      <c r="C6" s="138">
         <v>600</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="137" t="s">
+      <c r="A7" s="138" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="137" t="s">
+      <c r="B7" s="138" t="s">
         <v>290</v>
       </c>
-      <c r="C7" s="137">
+      <c r="C7" s="138">
         <v>250</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="137" t="s">
+      <c r="A8" s="138" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="137" t="s">
+      <c r="B8" s="138" t="s">
         <v>68</v>
       </c>
-      <c r="C8" s="137">
+      <c r="C8" s="138">
         <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="137" t="s">
+      <c r="A9" s="138" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="137" t="s">
+      <c r="B9" s="138" t="s">
         <v>63</v>
       </c>
-      <c r="C9" s="137">
+      <c r="C9" s="138">
         <v>700</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="137" t="s">
+      <c r="A10" s="138" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="137" t="s">
+      <c r="B10" s="138" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="137">
+      <c r="C10" s="138">
         <v>400</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="137" t="s">
+      <c r="A11" s="138" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="137" t="s">
+      <c r="B11" s="138" t="s">
         <v>290</v>
       </c>
-      <c r="C11" s="137">
+      <c r="C11" s="138">
         <v>350</v>
       </c>
     </row>
